--- a/workbooks/urbanization.xlsx
+++ b/workbooks/urbanization.xlsx
@@ -8,23 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC7209B-F39A-4E77-A78D-871E380E8E76}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C6BAEA-8358-4B05-9308-53BB069095E6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="2670" windowWidth="18900" windowHeight="15885" firstSheet="5" activeTab="5" xr2:uid="{9806A3BC-D491-4476-99E9-37D3951075C7}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="1" xr2:uid="{9806A3BC-D491-4476-99E9-37D3951075C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
-    <sheet name="USSR-1926" sheetId="3" r:id="rId2"/>
-    <sheet name="USSR-1959" sheetId="2" r:id="rId3"/>
-    <sheet name="USSR-1970" sheetId="7" r:id="rId4"/>
-    <sheet name="USSR-1979" sheetId="9" r:id="rId5"/>
-    <sheet name="RSFSR-1926" sheetId="4" r:id="rId6"/>
-    <sheet name="RSFSR-1959" sheetId="6" r:id="rId7"/>
-    <sheet name="RSFSR-1970" sheetId="8" r:id="rId8"/>
-    <sheet name="RSFSR-1979" sheetId="10" r:id="rId9"/>
-    <sheet name="MX-1930" sheetId="13" r:id="rId10"/>
-    <sheet name="MX-1960" sheetId="14" r:id="rId11"/>
-    <sheet name="MX-1970" sheetId="15" r:id="rId12"/>
+    <sheet name="RU-1926" sheetId="17" r:id="rId2"/>
+    <sheet name="USSR-1926" sheetId="3" r:id="rId3"/>
+    <sheet name="USSR-1959" sheetId="2" r:id="rId4"/>
+    <sheet name="USSR-1970" sheetId="7" r:id="rId5"/>
+    <sheet name="USSR-1979" sheetId="9" r:id="rId6"/>
+    <sheet name="RSFSR-1926" sheetId="4" r:id="rId7"/>
+    <sheet name="RSFSR-1959" sheetId="6" r:id="rId8"/>
+    <sheet name="RSFSR-1970" sheetId="8" r:id="rId9"/>
+    <sheet name="RSFSR-1979" sheetId="10" r:id="rId10"/>
+    <sheet name="MX-1930" sheetId="13" r:id="rId11"/>
+    <sheet name="MX-1960" sheetId="14" r:id="rId12"/>
+    <sheet name="MX-1970" sheetId="15" r:id="rId13"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="68">
   <si>
     <t>от</t>
   </si>
@@ -83,12 +84,6 @@
     <t>USSR-1970</t>
   </si>
   <si>
-    <t>"Итоги Всесоюзной переписи населения 1970 года. Том I - Численность населения СССР", стр. 61</t>
-  </si>
-  <si>
-    <t>"Итоги Всесоюзной переписи населения 1970 года. Том I - Численность населения СССР",  стр. 62</t>
-  </si>
-  <si>
     <t>городское население</t>
   </si>
   <si>
@@ -144,6 +139,114 @@
   </si>
   <si>
     <t>см. стр 5</t>
+  </si>
+  <si>
+    <t>ЦСУ СССР, "Всесоюзная перепись населения 17 декабря 1926 года, том XVII, отдел 1, Союз Советских Социалистических Ресупблик",  М. 1929, стр. 4-7</t>
+  </si>
+  <si>
+    <t>ЦСУ СССР, "Всесоюзная перепись населения 17 декабря 1926 года, том XVII, отдел 1, Союз Советских Социалистических Ресупблик",  М. 1929, стр. 6-7</t>
+  </si>
+  <si>
+    <t>гор. жит.</t>
+  </si>
+  <si>
+    <t>сель. жит</t>
+  </si>
+  <si>
+    <t>РСФСР</t>
+  </si>
+  <si>
+    <t>РСФСР городские</t>
+  </si>
+  <si>
+    <t>РСФСР сельские</t>
+  </si>
+  <si>
+    <t>всего</t>
+  </si>
+  <si>
+    <t>мест</t>
+  </si>
+  <si>
+    <t>СССР</t>
+  </si>
+  <si>
+    <t>СССР городские</t>
+  </si>
+  <si>
+    <t>СССР сельские</t>
+  </si>
+  <si>
+    <t>cвыше</t>
+  </si>
+  <si>
+    <t>см. страницу RU-1926</t>
+  </si>
+  <si>
+    <t>численность</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Средняя величина населённого пункта в строке 2000-5000 заметно ближе к 2000, чем к 5000. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Если бы пункты были равномерно распределены по размеру от 2000 до 5000, среднее было бы около 3500, что явно слишком высоко. </t>
+  </si>
+  <si>
+    <t>Значит, внутри интервала масса сильно смещена к нижней границе.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Я применил более правдоподобную интерполяцию: внутри диапазона 2000–5000 предполагается убывающая степенная плотность населённых пунктов, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">отдельно для городских и сельских строк, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">затем городские и сельские оценки складываются. </t>
+  </si>
+  <si>
+    <t>Получается такая оценочная строка:</t>
+  </si>
+  <si>
+    <t>Строка 2500-5000 ниже оценена интерполяцией.</t>
+  </si>
+  <si>
+    <t>Например, для СССР: 20 999 532 / 7 219 ≈ 2 909 жителей на пункт.</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Для получения строки 2500-3000 делаем локальную интерполяцию по двум нижним строкам: </t>
+  </si>
+  <si>
+    <t>менее 3000 и 3000–5000, предполагая гладкое возрастание массы населения по размеру населённого пункта около порога 3000.</t>
+  </si>
+  <si>
+    <t>сельских</t>
+  </si>
+  <si>
+    <t>городских</t>
+  </si>
+  <si>
+    <t>ЦСУ СССР, "Итоги Всесоюзной переписи населения 1959 года. СССР. Сводный том" (1962), стр. 35, 38-39</t>
+  </si>
+  <si>
+    <t>ЦСУ СССР, "Итоги Всесоюзной переписи населения 1959 года. РСФСР", стр. 39, 48-49</t>
+  </si>
+  <si>
+    <t>"Итоги Всесоюзной переписи населения 1970 года. Том I - Численность населения СССР", стр. 61, 146-147</t>
+  </si>
+  <si>
+    <t>"Итоги Всесоюзной переписи населения 1970 года. Том I - Численность населения СССР",  стр. 62, 146-147</t>
+  </si>
+  <si>
+    <t>итого</t>
+  </si>
+  <si>
+    <t>% в более 2500</t>
+  </si>
+  <si>
+    <t>всего в более 2500</t>
   </si>
 </sst>
 </file>
@@ -153,7 +256,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -165,6 +268,21 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="8" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -190,7 +308,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -198,6 +316,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -512,7 +652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BA24E3F-1F27-45F2-85D8-EE2D60E7DC98}">
-  <dimension ref="A3:B25"/>
+  <dimension ref="A3:B26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" customWidth="1"/>
@@ -529,101 +669,107 @@
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="2"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
+      <c r="B7" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="2"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
+      <c r="B9" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="2"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
         <v>18</v>
       </c>
-      <c r="B10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B19" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+      <c r="B22" t="s">
         <v>28</v>
       </c>
-      <c r="B23" t="s">
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -632,6 +778,156 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D70B758-2D8E-4D0F-9152-375389941F4D}">
+  <dimension ref="A3:D15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="22.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1">
+        <v>3000</v>
+      </c>
+      <c r="D4" s="1">
+        <v>970800</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>3000</v>
+      </c>
+      <c r="B5" s="1">
+        <v>5000</v>
+      </c>
+      <c r="D5" s="1">
+        <v>2312878</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5000</v>
+      </c>
+      <c r="B6" s="1">
+        <v>10000</v>
+      </c>
+      <c r="D6" s="1">
+        <v>5385703</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>10000</v>
+      </c>
+      <c r="B7" s="1">
+        <v>20000</v>
+      </c>
+      <c r="D7" s="1">
+        <v>6890054</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>20000</v>
+      </c>
+      <c r="B8" s="1">
+        <v>50000</v>
+      </c>
+      <c r="D8" s="1">
+        <v>11978294</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>50000</v>
+      </c>
+      <c r="B9" s="1">
+        <v>100000</v>
+      </c>
+      <c r="D9" s="1">
+        <v>9081267</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>100000</v>
+      </c>
+      <c r="B10" s="1">
+        <v>250000</v>
+      </c>
+      <c r="D10" s="1">
+        <v>12881225</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>250000</v>
+      </c>
+      <c r="B11" s="1">
+        <v>500000</v>
+      </c>
+      <c r="D11" s="1">
+        <v>14159420</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>500000</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1">
+        <v>31714226</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="1">
+        <f>SUM(D4:D12)</f>
+        <v>95373867</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="1">
+        <v>241720134</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="3">
+        <f>100*D13/D14</f>
+        <v>39.456318934524504</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD1CEBF5-B4BD-4DD1-AC0A-66E7B41EFED5}">
   <dimension ref="A3:H17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -762,19 +1058,19 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D14" s="1">
         <f>SUM(D5:D13)</f>
         <v>8269353</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D15" s="1">
         <f>SUM(D5:D13)</f>
@@ -784,12 +1080,12 @@
         <v>5540631</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D16" s="1">
         <v>16552722</v>
@@ -797,7 +1093,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D17" s="3">
         <f>100*D15/D16</f>
@@ -813,7 +1109,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E93D3E-D80F-423E-BDEC-5E3B3CDBD631}">
   <dimension ref="A3:G23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -989,7 +1285,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C17" s="1">
         <f>SUM(C5:C16)</f>
@@ -997,12 +1293,12 @@
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C18" s="1">
         <f>C17</f>
@@ -1012,12 +1308,12 @@
         <v>17218011</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C19" s="1">
         <v>34923129</v>
@@ -1025,7 +1321,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C20">
         <f>100*C18/C19</f>
@@ -1049,7 +1345,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A2F5240-BC93-4757-9D88-C679B5B701EC}">
   <dimension ref="A3:E26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1212,19 +1508,19 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C17" s="1">
         <f>SUM(C5:C16)</f>
         <v>34674841</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C18" s="1">
         <f>C17</f>
@@ -1237,7 +1533,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C19" s="1">
         <v>48225238</v>
@@ -1245,7 +1541,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C20" s="3">
         <f>100*C18/C19</f>
@@ -1271,7 +1567,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1280,13 +1576,1116 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4D8DB8B-3990-447D-A504-5F100C779FB0}">
+  <dimension ref="A3:N40"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" customWidth="1"/>
+    <col min="8" max="10" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="N3" s="9"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="N4" s="10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1">
+        <v>96806</v>
+      </c>
+      <c r="D5" s="1">
+        <v>537658</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>96806</v>
+      </c>
+      <c r="H5" s="1">
+        <v>537658</v>
+      </c>
+      <c r="I5" s="1">
+        <v>80149</v>
+      </c>
+      <c r="J5" s="1">
+        <v>446099</v>
+      </c>
+      <c r="K5" s="1">
+        <v>0</v>
+      </c>
+      <c r="L5" s="1">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1">
+        <v>80149</v>
+      </c>
+      <c r="N5" s="1">
+        <v>446099</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1">
+        <v>20</v>
+      </c>
+      <c r="C6" s="1">
+        <v>64058</v>
+      </c>
+      <c r="D6" s="1">
+        <v>904107</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>64058</v>
+      </c>
+      <c r="H6" s="1">
+        <v>904107</v>
+      </c>
+      <c r="I6" s="1">
+        <v>54094</v>
+      </c>
+      <c r="J6" s="1">
+        <v>763814</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1">
+        <v>54094</v>
+      </c>
+      <c r="N6" s="1">
+        <v>763814</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>20</v>
+      </c>
+      <c r="B7" s="1">
+        <v>50</v>
+      </c>
+      <c r="C7" s="1">
+        <v>115643</v>
+      </c>
+      <c r="D7" s="1">
+        <v>3841490</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>115643</v>
+      </c>
+      <c r="H7" s="1">
+        <v>3841490</v>
+      </c>
+      <c r="I7" s="1">
+        <v>96670</v>
+      </c>
+      <c r="J7" s="1">
+        <v>3208144</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1">
+        <v>96670</v>
+      </c>
+      <c r="N7" s="1">
+        <v>3208144</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>50</v>
+      </c>
+      <c r="B8" s="1">
+        <v>100</v>
+      </c>
+      <c r="C8" s="1">
+        <v>106480</v>
+      </c>
+      <c r="D8" s="1">
+        <v>7644673</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>106480</v>
+      </c>
+      <c r="H8" s="1">
+        <v>7644673</v>
+      </c>
+      <c r="I8" s="1">
+        <v>87299</v>
+      </c>
+      <c r="J8" s="1">
+        <v>6257750</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
+        <v>87299</v>
+      </c>
+      <c r="N8" s="1">
+        <v>6257750</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>100</v>
+      </c>
+      <c r="B9" s="1">
+        <v>200</v>
+      </c>
+      <c r="C9" s="1">
+        <v>96975</v>
+      </c>
+      <c r="D9" s="1">
+        <v>13738630</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>96975</v>
+      </c>
+      <c r="H9" s="1">
+        <v>13738630</v>
+      </c>
+      <c r="I9" s="1">
+        <v>76812</v>
+      </c>
+      <c r="J9" s="1">
+        <v>10850499</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>76812</v>
+      </c>
+      <c r="N9" s="1">
+        <v>10850499</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>200</v>
+      </c>
+      <c r="B10" s="1">
+        <v>500</v>
+      </c>
+      <c r="C10" s="1">
+        <v>80471</v>
+      </c>
+      <c r="D10" s="1">
+        <v>24872184</v>
+      </c>
+      <c r="E10" s="1">
+        <v>3</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1229</v>
+      </c>
+      <c r="G10" s="1">
+        <v>80468</v>
+      </c>
+      <c r="H10" s="1">
+        <v>24870955</v>
+      </c>
+      <c r="I10" s="1">
+        <v>59131</v>
+      </c>
+      <c r="J10" s="1">
+        <v>18144846</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1</v>
+      </c>
+      <c r="L10" s="1">
+        <v>415</v>
+      </c>
+      <c r="M10" s="1">
+        <v>59130</v>
+      </c>
+      <c r="N10" s="1">
+        <v>18144431</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>500</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C11" s="1">
+        <v>30381</v>
+      </c>
+      <c r="D11" s="1">
+        <v>21094938</v>
+      </c>
+      <c r="E11" s="1">
+        <v>176</v>
+      </c>
+      <c r="F11" s="1">
+        <v>134714</v>
+      </c>
+      <c r="G11" s="1">
+        <v>30205</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20960224</v>
+      </c>
+      <c r="I11" s="1">
+        <v>21052</v>
+      </c>
+      <c r="J11" s="1">
+        <v>14578685</v>
+      </c>
+      <c r="K11" s="1">
+        <v>103</v>
+      </c>
+      <c r="L11" s="1">
+        <v>80433</v>
+      </c>
+      <c r="M11" s="1">
+        <v>20949</v>
+      </c>
+      <c r="N11" s="1">
+        <v>14498252</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B12" s="1">
+        <v>2000</v>
+      </c>
+      <c r="C12" s="1">
+        <v>15547</v>
+      </c>
+      <c r="D12" s="1">
+        <v>21410126</v>
+      </c>
+      <c r="E12" s="1">
+        <v>330</v>
+      </c>
+      <c r="F12" s="1">
+        <v>482417</v>
+      </c>
+      <c r="G12" s="1">
+        <v>15217</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20927709</v>
+      </c>
+      <c r="I12" s="1">
+        <v>10019</v>
+      </c>
+      <c r="J12" s="1">
+        <v>13728623</v>
+      </c>
+      <c r="K12" s="1">
+        <v>219</v>
+      </c>
+      <c r="L12" s="1">
+        <v>320966</v>
+      </c>
+      <c r="M12" s="1">
+        <v>9800</v>
+      </c>
+      <c r="N12" s="1">
+        <v>13407657</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>2000</v>
+      </c>
+      <c r="B13" s="1">
+        <v>5000</v>
+      </c>
+      <c r="C13" s="1">
+        <v>7219</v>
+      </c>
+      <c r="D13" s="1">
+        <v>20999532</v>
+      </c>
+      <c r="E13" s="1">
+        <v>559</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1844645</v>
+      </c>
+      <c r="G13" s="1">
+        <v>6660</v>
+      </c>
+      <c r="H13" s="1">
+        <v>19154887</v>
+      </c>
+      <c r="I13" s="1">
+        <v>4218</v>
+      </c>
+      <c r="J13" s="1">
+        <v>12184306</v>
+      </c>
+      <c r="K13" s="1">
+        <v>362</v>
+      </c>
+      <c r="L13" s="1">
+        <v>1198303</v>
+      </c>
+      <c r="M13" s="1">
+        <v>3856</v>
+      </c>
+      <c r="N13" s="1">
+        <v>10986003</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>5000</v>
+      </c>
+      <c r="B14" s="1">
+        <v>10000</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1280</v>
+      </c>
+      <c r="D14" s="1">
+        <v>8557326</v>
+      </c>
+      <c r="E14" s="1">
+        <v>378</v>
+      </c>
+      <c r="F14" s="1">
+        <v>2688102</v>
+      </c>
+      <c r="G14" s="1">
+        <v>902</v>
+      </c>
+      <c r="H14" s="1">
+        <v>5869224</v>
+      </c>
+      <c r="I14" s="1">
+        <v>721</v>
+      </c>
+      <c r="J14" s="1">
+        <v>4861267</v>
+      </c>
+      <c r="K14" s="1">
+        <v>243</v>
+      </c>
+      <c r="L14" s="1">
+        <v>1727240</v>
+      </c>
+      <c r="M14" s="1">
+        <v>478</v>
+      </c>
+      <c r="N14" s="1">
+        <v>3134027</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>10000</v>
+      </c>
+      <c r="B15" s="1">
+        <v>20000</v>
+      </c>
+      <c r="C15" s="1">
+        <v>421</v>
+      </c>
+      <c r="D15" s="1">
+        <v>5620665</v>
+      </c>
+      <c r="E15" s="1">
+        <v>253</v>
+      </c>
+      <c r="F15" s="1">
+        <v>3522846</v>
+      </c>
+      <c r="G15" s="1">
+        <v>168</v>
+      </c>
+      <c r="H15" s="1">
+        <v>2097819</v>
+      </c>
+      <c r="I15" s="1">
+        <v>292</v>
+      </c>
+      <c r="J15" s="1">
+        <v>3907710</v>
+      </c>
+      <c r="K15" s="1">
+        <v>161</v>
+      </c>
+      <c r="L15" s="1">
+        <v>2276487</v>
+      </c>
+      <c r="M15" s="1">
+        <v>131</v>
+      </c>
+      <c r="N15" s="1">
+        <v>1631223</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>20000</v>
+      </c>
+      <c r="B16" s="1">
+        <v>50000</v>
+      </c>
+      <c r="C16" s="1">
+        <v>140</v>
+      </c>
+      <c r="D16" s="1">
+        <v>4093873</v>
+      </c>
+      <c r="E16" s="1">
+        <v>135</v>
+      </c>
+      <c r="F16" s="1">
+        <v>3982819</v>
+      </c>
+      <c r="G16" s="1">
+        <v>5</v>
+      </c>
+      <c r="H16" s="1">
+        <v>111054</v>
+      </c>
+      <c r="I16" s="1">
+        <v>93</v>
+      </c>
+      <c r="J16" s="1">
+        <v>2670393</v>
+      </c>
+      <c r="K16" s="1">
+        <v>90</v>
+      </c>
+      <c r="L16" s="1">
+        <v>2605731</v>
+      </c>
+      <c r="M16" s="1">
+        <v>3</v>
+      </c>
+      <c r="N16" s="1">
+        <v>64662</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>50000</v>
+      </c>
+      <c r="B17" s="1">
+        <v>100000</v>
+      </c>
+      <c r="C17" s="1">
+        <v>60</v>
+      </c>
+      <c r="D17" s="1">
+        <v>4108692</v>
+      </c>
+      <c r="E17" s="1">
+        <v>60</v>
+      </c>
+      <c r="F17" s="1">
+        <v>4108692</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <v>40</v>
+      </c>
+      <c r="J17" s="1">
+        <v>2786535</v>
+      </c>
+      <c r="K17" s="1">
+        <v>40</v>
+      </c>
+      <c r="L17" s="1">
+        <v>2786535</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+      <c r="N17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="1">
+        <v>100000</v>
+      </c>
+      <c r="C18" s="1">
+        <v>32</v>
+      </c>
+      <c r="D18" s="1">
+        <v>9550941</v>
+      </c>
+      <c r="E18" s="1">
+        <v>32</v>
+      </c>
+      <c r="F18" s="1">
+        <v>9550941</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="I18" s="1">
+        <v>20</v>
+      </c>
+      <c r="J18" s="1">
+        <v>6447410</v>
+      </c>
+      <c r="K18" s="1">
+        <v>20</v>
+      </c>
+      <c r="L18" s="1">
+        <v>6447410</v>
+      </c>
+      <c r="M18" s="1">
+        <v>0</v>
+      </c>
+      <c r="N18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="1">
+        <v>615513</v>
+      </c>
+      <c r="D19" s="1">
+        <v>146974835</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1926</v>
+      </c>
+      <c r="F19" s="1">
+        <v>26316405</v>
+      </c>
+      <c r="G19" s="1">
+        <v>613587</v>
+      </c>
+      <c r="H19" s="1">
+        <v>120658430</v>
+      </c>
+      <c r="I19" s="1">
+        <v>490610</v>
+      </c>
+      <c r="J19" s="1">
+        <v>100836081</v>
+      </c>
+      <c r="K19" s="1">
+        <v>1239</v>
+      </c>
+      <c r="L19" s="1">
+        <v>17443520</v>
+      </c>
+      <c r="M19" s="1">
+        <v>489371</v>
+      </c>
+      <c r="N19" s="1">
+        <v>83392561</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>2500</v>
+      </c>
+      <c r="B32" s="1">
+        <v>5000</v>
+      </c>
+      <c r="C32" s="1">
+        <v>4300</v>
+      </c>
+      <c r="D32" s="1">
+        <v>14506569</v>
+      </c>
+      <c r="E32" s="1">
+        <v>428</v>
+      </c>
+      <c r="F32" s="1">
+        <v>1551432</v>
+      </c>
+      <c r="G32" s="1">
+        <v>3871</v>
+      </c>
+      <c r="H32" s="1">
+        <v>12955137</v>
+      </c>
+      <c r="I32" s="1">
+        <v>2466</v>
+      </c>
+      <c r="J32" s="1">
+        <v>8289401</v>
+      </c>
+      <c r="K32" s="1">
+        <v>279</v>
+      </c>
+      <c r="L32" s="1">
+        <v>1011440</v>
+      </c>
+      <c r="M32" s="1">
+        <v>2187</v>
+      </c>
+      <c r="N32" s="1">
+        <v>7277961</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>5000</v>
+      </c>
+      <c r="B33" s="1">
+        <v>10000</v>
+      </c>
+      <c r="C33" s="1">
+        <v>1280</v>
+      </c>
+      <c r="D33" s="1">
+        <v>8557326</v>
+      </c>
+      <c r="E33" s="1">
+        <v>378</v>
+      </c>
+      <c r="F33" s="1">
+        <v>2688102</v>
+      </c>
+      <c r="G33" s="1">
+        <v>902</v>
+      </c>
+      <c r="H33" s="1">
+        <v>5869224</v>
+      </c>
+      <c r="I33" s="1">
+        <v>721</v>
+      </c>
+      <c r="J33" s="1">
+        <v>4861267</v>
+      </c>
+      <c r="K33" s="1">
+        <v>243</v>
+      </c>
+      <c r="L33" s="1">
+        <v>1727240</v>
+      </c>
+      <c r="M33" s="1">
+        <v>478</v>
+      </c>
+      <c r="N33" s="1">
+        <v>3134027</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>10000</v>
+      </c>
+      <c r="B34" s="1">
+        <v>20000</v>
+      </c>
+      <c r="C34" s="1">
+        <v>421</v>
+      </c>
+      <c r="D34" s="1">
+        <v>5620665</v>
+      </c>
+      <c r="E34" s="1">
+        <v>253</v>
+      </c>
+      <c r="F34" s="1">
+        <v>3522846</v>
+      </c>
+      <c r="G34" s="1">
+        <v>168</v>
+      </c>
+      <c r="H34" s="1">
+        <v>2097819</v>
+      </c>
+      <c r="I34" s="1">
+        <v>292</v>
+      </c>
+      <c r="J34" s="1">
+        <v>3907710</v>
+      </c>
+      <c r="K34" s="1">
+        <v>161</v>
+      </c>
+      <c r="L34" s="1">
+        <v>2276487</v>
+      </c>
+      <c r="M34" s="1">
+        <v>131</v>
+      </c>
+      <c r="N34" s="1">
+        <v>1631223</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>20000</v>
+      </c>
+      <c r="B35" s="1">
+        <v>50000</v>
+      </c>
+      <c r="C35" s="1">
+        <v>140</v>
+      </c>
+      <c r="D35" s="1">
+        <v>4093873</v>
+      </c>
+      <c r="E35" s="1">
+        <v>135</v>
+      </c>
+      <c r="F35" s="1">
+        <v>3982819</v>
+      </c>
+      <c r="G35" s="1">
+        <v>5</v>
+      </c>
+      <c r="H35" s="1">
+        <v>111054</v>
+      </c>
+      <c r="I35" s="1">
+        <v>93</v>
+      </c>
+      <c r="J35" s="1">
+        <v>2670393</v>
+      </c>
+      <c r="K35" s="1">
+        <v>90</v>
+      </c>
+      <c r="L35" s="1">
+        <v>2605731</v>
+      </c>
+      <c r="M35" s="1">
+        <v>3</v>
+      </c>
+      <c r="N35" s="1">
+        <v>64662</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>50000</v>
+      </c>
+      <c r="B36" s="1">
+        <v>100000</v>
+      </c>
+      <c r="C36" s="1">
+        <v>60</v>
+      </c>
+      <c r="D36" s="1">
+        <v>4108692</v>
+      </c>
+      <c r="E36" s="1">
+        <v>60</v>
+      </c>
+      <c r="F36" s="1">
+        <v>4108692</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0</v>
+      </c>
+      <c r="H36" s="1">
+        <v>0</v>
+      </c>
+      <c r="I36" s="1">
+        <v>40</v>
+      </c>
+      <c r="J36" s="1">
+        <v>2786535</v>
+      </c>
+      <c r="K36" s="1">
+        <v>40</v>
+      </c>
+      <c r="L36" s="1">
+        <v>2786535</v>
+      </c>
+      <c r="M36" s="1">
+        <v>0</v>
+      </c>
+      <c r="N36" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1">
+        <v>100000</v>
+      </c>
+      <c r="C37" s="1">
+        <v>32</v>
+      </c>
+      <c r="D37" s="1">
+        <v>9550941</v>
+      </c>
+      <c r="E37" s="1">
+        <v>32</v>
+      </c>
+      <c r="F37" s="1">
+        <v>9550941</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1">
+        <v>0</v>
+      </c>
+      <c r="I37" s="1">
+        <v>20</v>
+      </c>
+      <c r="J37" s="1">
+        <v>6447410</v>
+      </c>
+      <c r="K37" s="1">
+        <v>20</v>
+      </c>
+      <c r="L37" s="1">
+        <v>6447410</v>
+      </c>
+      <c r="M37" s="1">
+        <v>0</v>
+      </c>
+      <c r="N37" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>39</v>
+      </c>
+      <c r="D39" s="1">
+        <f>SUM(D32:D37)</f>
+        <v>46438066</v>
+      </c>
+      <c r="J39" s="1">
+        <f>SUM(J32:J37)</f>
+        <v>28962716</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D40" s="3">
+        <f>100*D39/D19</f>
+        <v>31.595930010739593</v>
+      </c>
+      <c r="J40" s="3">
+        <f>100*J39/J19</f>
+        <v>28.722572032524745</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C23E754-2BB4-4F22-A1F6-E30F1A3E2522}">
-  <dimension ref="A3:D56"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="11" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
@@ -1389,7 +2788,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D12" s="1">
         <f>SUM(D4:D11)</f>
@@ -1398,7 +2797,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D13" s="1">
         <v>136810000</v>
@@ -1406,242 +2805,241 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D14" s="3">
         <f>100*D12/D13</f>
         <v>19.235737884657553</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" s="2" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2" t="s">
+      <c r="C19" s="2"/>
+      <c r="D19" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>2</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B20" s="5">
         <v>1000</v>
       </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="5">
+      <c r="C20" s="2"/>
+      <c r="D20" s="5">
         <v>11126</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="5">
-        <v>1000</v>
-      </c>
-      <c r="B20" s="5">
-        <v>2000</v>
-      </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="5">
-        <v>53807</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
+        <v>1000</v>
+      </c>
+      <c r="B21" s="5">
         <v>2000</v>
-      </c>
-      <c r="B21" s="5">
-        <v>3000</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="5">
-        <v>120250</v>
+        <v>53807</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
+        <v>2000</v>
+      </c>
+      <c r="B22" s="5">
         <v>3000</v>
-      </c>
-      <c r="B22" s="5">
-        <v>5000</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="5">
-        <v>414313</v>
+        <v>120250</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
+        <v>3000</v>
+      </c>
+      <c r="B23" s="5">
         <v>5000</v>
-      </c>
-      <c r="B23" s="5">
-        <v>7000</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="5">
-        <v>437484</v>
+        <v>414313</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
+        <v>5000</v>
+      </c>
+      <c r="B24" s="5">
         <v>7000</v>
-      </c>
-      <c r="B24" s="5">
-        <v>10000</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="5">
-        <v>611204</v>
+        <v>437484</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
+        <v>7000</v>
+      </c>
+      <c r="B25" s="5">
         <v>10000</v>
-      </c>
-      <c r="B25" s="5">
-        <v>15000</v>
       </c>
       <c r="C25" s="4"/>
       <c r="D25" s="5">
-        <v>1214439</v>
+        <v>611204</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
+        <v>10000</v>
+      </c>
+      <c r="B26" s="5">
         <v>15000</v>
-      </c>
-      <c r="B26" s="5">
-        <v>20000</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="5">
-        <v>850914</v>
+        <v>1214439</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
+        <v>15000</v>
+      </c>
+      <c r="B27" s="5">
         <v>20000</v>
-      </c>
-      <c r="B27" s="5">
-        <v>25000</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="5">
-        <v>778363</v>
+        <v>850914</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
+        <v>20000</v>
+      </c>
+      <c r="B28" s="5">
         <v>25000</v>
-      </c>
-      <c r="B28" s="5">
-        <v>30000</v>
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="5">
-        <v>563766</v>
+        <v>778363</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
+        <v>25000</v>
+      </c>
+      <c r="B29" s="5">
         <v>30000</v>
-      </c>
-      <c r="B29" s="5">
-        <v>40000</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="5">
-        <v>1243442</v>
+        <v>563766</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
+        <v>30000</v>
+      </c>
+      <c r="B30" s="5">
         <v>40000</v>
-      </c>
-      <c r="B30" s="5">
-        <v>50000</v>
       </c>
       <c r="C30" s="4"/>
       <c r="D30" s="5">
-        <v>682374</v>
+        <v>1243442</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
+        <v>40000</v>
+      </c>
+      <c r="B31" s="5">
         <v>50000</v>
-      </c>
-      <c r="B31" s="5">
-        <v>70000</v>
       </c>
       <c r="C31" s="4"/>
       <c r="D31" s="5">
-        <v>1811560</v>
+        <v>682374</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
+        <v>50000</v>
+      </c>
+      <c r="B32" s="5">
         <v>70000</v>
-      </c>
-      <c r="B32" s="5">
-        <v>100000</v>
       </c>
       <c r="C32" s="4"/>
       <c r="D32" s="5">
-        <v>2226166</v>
+        <v>1811560</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
+        <v>70000</v>
+      </c>
+      <c r="B33" s="5">
         <v>100000</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>3</v>
       </c>
       <c r="C33" s="4"/>
       <c r="D33" s="5">
-        <v>9142693</v>
+        <v>2226166</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" s="4"/>
+      <c r="A34" s="5">
+        <v>100000</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="C34" s="4"/>
       <c r="D34" s="5">
-        <f>SUM(D19:D33)</f>
-        <v>20161901</v>
+        <v>9142693</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
       <c r="D35" s="5">
-        <v>147027915</v>
+        <f>SUM(D20:D34)</f>
+        <v>20161901</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
-      <c r="D36" s="3">
-        <f>100*D34/D35</f>
-        <v>13.712974845627103</v>
+      <c r="D36" s="5">
+        <v>147027915</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="4"/>
+      <c r="A37" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
-      <c r="D37" s="5"/>
+      <c r="D37" s="3">
+        <f>100*D35/D36</f>
+        <v>13.712974845627103</v>
+      </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4"/>
@@ -1650,7 +3048,9 @@
       <c r="D38" s="5"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="4"/>
+      <c r="A39" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="5"/>
@@ -1665,7 +3065,7 @@
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
+      <c r="D41" s="5"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4"/>
@@ -1692,405 +3092,1064 @@
       <c r="D45" s="4"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>2</v>
-      </c>
-      <c r="B46">
-        <v>3</v>
-      </c>
-      <c r="D46" s="1">
-        <v>1207383</v>
-      </c>
+      <c r="A46" s="4"/>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>3</v>
-      </c>
-      <c r="B47">
-        <v>5</v>
-      </c>
-      <c r="D47" s="1">
-        <v>1255602</v>
-      </c>
+      <c r="D47" s="1"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>5</v>
-      </c>
-      <c r="B48">
-        <v>10</v>
-      </c>
-      <c r="D48" s="1">
-        <v>2688141</v>
-      </c>
+      <c r="D48" s="1"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>10</v>
-      </c>
-      <c r="B49">
-        <v>20</v>
-      </c>
-      <c r="D49" s="1">
-        <v>3522835</v>
-      </c>
+      <c r="D49" s="1"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>20</v>
-      </c>
-      <c r="B50">
-        <v>50</v>
-      </c>
-      <c r="D50" s="1">
-        <v>3982819</v>
-      </c>
+      <c r="D50" s="1"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51">
-        <v>100</v>
-      </c>
-      <c r="D51" s="1">
-        <v>4108692</v>
-      </c>
+      <c r="D51" s="1"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>100</v>
-      </c>
-      <c r="B52">
-        <v>500</v>
-      </c>
-      <c r="D52" s="1">
-        <v>5397349</v>
-      </c>
+      <c r="D52" s="1"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>500</v>
-      </c>
-      <c r="B53" t="s">
-        <v>3</v>
-      </c>
-      <c r="D53" s="1">
-        <v>4153592</v>
-      </c>
+      <c r="D53" s="1"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D54" s="1">
-        <f>SUM(D46:D53)</f>
-        <v>26316413</v>
-      </c>
+      <c r="D54" s="1"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D55" s="1">
-        <v>136810000</v>
-      </c>
+      <c r="A55" s="2"/>
+      <c r="D55" s="1"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D56" s="3">
-        <f>100*D54/D55</f>
-        <v>19.235737884657553</v>
-      </c>
+      <c r="A56" s="2"/>
+      <c r="D56" s="1"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="2"/>
+      <c r="D57" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ED326E9-8D2E-42C0-8EF9-E316006CB136}">
-  <dimension ref="A3:D14"/>
+  <dimension ref="A3:N40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="11.28515625" customWidth="1"/>
     <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I3" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="J3" s="8"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C4" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="8"/>
+      <c r="G4" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H4" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
+      <c r="I4" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="11" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="N4" s="11"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>1000</v>
+      </c>
+      <c r="H5">
+        <v>2000</v>
+      </c>
+      <c r="I5">
+        <v>14218</v>
+      </c>
+      <c r="J5" s="1">
+        <v>19337000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B6" s="1">
         <v>3000</v>
       </c>
-      <c r="D4" s="1">
+      <c r="C6">
+        <v>843</v>
+      </c>
+      <c r="D6" s="1">
         <v>1610533</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+      <c r="G6">
+        <v>2000</v>
+      </c>
+      <c r="H6">
         <v>3000</v>
       </c>
-      <c r="B5" s="1">
+      <c r="I6">
+        <v>3482</v>
+      </c>
+      <c r="J6" s="1">
+        <v>8389199</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>3000</v>
+      </c>
+      <c r="B7" s="1">
         <v>5000</v>
       </c>
-      <c r="D5" s="1">
+      <c r="C7">
+        <v>904</v>
+      </c>
+      <c r="D7" s="1">
         <v>3596828</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+      <c r="G7" s="1">
+        <v>3000</v>
+      </c>
+      <c r="H7" s="1">
         <v>5000</v>
       </c>
-      <c r="B6" s="1">
+      <c r="I7" s="1">
+        <v>1807</v>
+      </c>
+      <c r="J7" s="1">
+        <v>6732200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>5000</v>
+      </c>
+      <c r="B8" s="1">
         <v>10000</v>
       </c>
-      <c r="D6" s="1">
+      <c r="C8">
+        <v>1296</v>
+      </c>
+      <c r="D8" s="1">
         <v>9213576</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+      <c r="G8" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8">
+        <v>675</v>
+      </c>
+      <c r="J8" s="1">
+        <v>4973200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>10000</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B9" s="1">
         <v>20000</v>
       </c>
-      <c r="D7" s="1">
+      <c r="C9">
+        <v>798</v>
+      </c>
+      <c r="D9" s="1">
         <v>11150064</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>20000</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B10" s="1">
         <v>50000</v>
       </c>
-      <c r="D8" s="1">
+      <c r="C10">
+        <v>474</v>
+      </c>
+      <c r="D10" s="1">
         <v>14828309</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>50000</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B11" s="1">
         <v>100000</v>
       </c>
-      <c r="D9" s="1">
+      <c r="C11">
+        <v>156</v>
+      </c>
+      <c r="D11" s="1">
         <v>10989803</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
         <v>100000</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B12" s="1">
         <v>500000</v>
       </c>
-      <c r="D10" s="1">
+      <c r="C12">
+        <v>123</v>
+      </c>
+      <c r="D12" s="1">
         <v>24425829</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
         <v>500000</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B13" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="1">
+      <c r="C13">
+        <v>25</v>
+      </c>
+      <c r="D13" s="1">
         <v>24162753</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="G13" s="1"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="1">
+        <f>SUM(D6:D13)</f>
+        <v>99977695</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15">
+        <f>SUM(C6:C13)</f>
+        <v>4619</v>
+      </c>
+      <c r="D15" s="1">
+        <v>208826650</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="1">
-        <f>SUM(D4:D11)</f>
-        <v>99977695</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="1">
+      <c r="D16" s="3">
+        <f>100*D14/D15</f>
+        <v>47.875927234383163</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C24" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D24" s="8"/>
+      <c r="I24" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="J24" s="8"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="I25" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>2500</v>
+      </c>
+      <c r="B26" s="1">
+        <v>3000</v>
+      </c>
+      <c r="C26">
+        <v>226</v>
+      </c>
+      <c r="D26" s="1">
+        <v>621258</v>
+      </c>
+      <c r="J26" s="1"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>3000</v>
+      </c>
+      <c r="B27" s="1">
+        <v>5000</v>
+      </c>
+      <c r="C27">
+        <v>904</v>
+      </c>
+      <c r="D27" s="1">
+        <v>3596828</v>
+      </c>
+      <c r="G27">
+        <v>2500</v>
+      </c>
+      <c r="H27">
+        <v>3000</v>
+      </c>
+      <c r="I27">
+        <v>1109</v>
+      </c>
+      <c r="J27" s="1">
+        <v>3050845</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>5000</v>
+      </c>
+      <c r="B28" s="1">
+        <v>10000</v>
+      </c>
+      <c r="C28">
+        <v>1296</v>
+      </c>
+      <c r="D28" s="1">
+        <v>9213576</v>
+      </c>
+      <c r="G28" s="1">
+        <v>3000</v>
+      </c>
+      <c r="H28" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I28" s="1">
+        <v>1807</v>
+      </c>
+      <c r="J28" s="1">
+        <v>6732200</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>10000</v>
+      </c>
+      <c r="B29" s="1">
+        <v>20000</v>
+      </c>
+      <c r="C29">
+        <v>798</v>
+      </c>
+      <c r="D29" s="1">
+        <v>11150064</v>
+      </c>
+      <c r="G29" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H29" t="s">
+        <v>3</v>
+      </c>
+      <c r="I29">
+        <v>675</v>
+      </c>
+      <c r="J29" s="1">
+        <v>4973200</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>20000</v>
+      </c>
+      <c r="B30" s="1">
+        <v>50000</v>
+      </c>
+      <c r="C30">
+        <v>474</v>
+      </c>
+      <c r="D30" s="1">
+        <v>14828309</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>50000</v>
+      </c>
+      <c r="B31" s="1">
+        <v>100000</v>
+      </c>
+      <c r="C31">
+        <v>156</v>
+      </c>
+      <c r="D31" s="1">
+        <v>10989803</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>100000</v>
+      </c>
+      <c r="B32" s="1">
+        <v>500000</v>
+      </c>
+      <c r="C32">
+        <v>123</v>
+      </c>
+      <c r="D32" s="1">
+        <v>24425829</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>500000</v>
+      </c>
+      <c r="B33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33">
+        <v>25</v>
+      </c>
+      <c r="D33" s="1">
+        <v>24162753</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="1">
+        <f>SUM(D26:D33)</f>
+        <v>98988420</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D35" s="1">
         <v>208826650</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="3">
-        <f>100*D12/D13</f>
-        <v>47.875927234383163</v>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="D36" s="3"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>67</v>
+      </c>
+      <c r="D38" s="1">
+        <f>SUM(D26:D33)</f>
+        <v>98988420</v>
+      </c>
+      <c r="J38" s="1">
+        <f>SUM(J26:J33)</f>
+        <v>14756245</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D39" s="1">
+        <f>D38+J38</f>
+        <v>113744665</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D40" s="3">
+        <f>100*D39/D35</f>
+        <v>54.468462238895277</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="I24:J24"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{788ECCEF-9F8C-4056-9EBF-C43E8745BF26}">
-  <dimension ref="A3:D14"/>
+  <dimension ref="A2:J39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="13.42578125" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C3" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="8"/>
+      <c r="I3" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
+      <c r="C4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="G4" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B5" s="1">
         <v>3000</v>
       </c>
-      <c r="D4" s="1">
+      <c r="C5">
+        <v>1118</v>
+      </c>
+      <c r="D5" s="1">
         <v>2051695</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+      <c r="G5" s="4">
+        <v>1000</v>
+      </c>
+      <c r="H5" s="4">
+        <v>2000</v>
+      </c>
+      <c r="I5" s="5">
+        <v>16677</v>
+      </c>
+      <c r="J5" s="13">
+        <v>22785371</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>3000</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B6" s="1">
         <v>5000</v>
       </c>
-      <c r="D5" s="1">
+      <c r="C6">
+        <v>1028</v>
+      </c>
+      <c r="D6" s="1">
         <v>4098169</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+      <c r="G6" s="4">
+        <v>2000</v>
+      </c>
+      <c r="H6" s="4">
+        <v>3000</v>
+      </c>
+      <c r="I6" s="5">
+        <v>3911</v>
+      </c>
+      <c r="J6" s="13">
+        <v>9424188</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>5000</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B7" s="1">
         <v>10000</v>
       </c>
-      <c r="D6" s="1">
+      <c r="C7">
+        <v>1430</v>
+      </c>
+      <c r="D7" s="1">
         <v>10069839</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+      <c r="G7" s="5">
+        <v>3000</v>
+      </c>
+      <c r="H7" s="5">
+        <v>5000</v>
+      </c>
+      <c r="I7" s="5">
+        <v>2040</v>
+      </c>
+      <c r="J7" s="13">
+        <v>7656431</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>10000</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B8" s="1">
         <v>20000</v>
       </c>
-      <c r="D7" s="1">
+      <c r="C8">
+        <v>919</v>
+      </c>
+      <c r="D8" s="1">
         <v>12721674</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+      <c r="G8" s="5">
+        <v>5000</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="5">
+        <v>868</v>
+      </c>
+      <c r="J8" s="13">
+        <v>6446727</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>20000</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B9" s="1">
         <v>50000</v>
       </c>
-      <c r="D8" s="1">
+      <c r="C9">
+        <v>600</v>
+      </c>
+      <c r="D9" s="1">
         <v>18468944</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>50000</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B10" s="1">
         <v>100000</v>
       </c>
-      <c r="D9" s="1">
+      <c r="C10">
+        <v>189</v>
+      </c>
+      <c r="D10" s="1">
         <v>13054945</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+      <c r="G10" s="1"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>100000</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B11" s="1">
         <v>500000</v>
       </c>
-      <c r="D10" s="1">
+      <c r="C11">
+        <v>188</v>
+      </c>
+      <c r="D11" s="1">
         <v>38239651</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
         <v>500000</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B12" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="1">
+      <c r="C12">
+        <v>33</v>
+      </c>
+      <c r="D12" s="1">
         <v>37286597</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="1">
+        <f>SUM(D5:D12)</f>
+        <v>135991514</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14">
+        <f>SUM(C5:C12)</f>
+        <v>5505</v>
+      </c>
+      <c r="D14" s="1">
+        <v>241720134</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="1">
-        <f>SUM(D4:D11)</f>
-        <v>135991514</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="1">
+      <c r="D15" s="3">
+        <f>100*D13/D14</f>
+        <v>56.259903446851474</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C23" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="8"/>
+      <c r="I23" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="J23" s="8"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2500</v>
+      </c>
+      <c r="B25" s="1">
+        <v>3000</v>
+      </c>
+      <c r="C25">
+        <v>270</v>
+      </c>
+      <c r="D25" s="1">
+        <v>741248</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="13"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>3000</v>
+      </c>
+      <c r="B26" s="1">
+        <v>5000</v>
+      </c>
+      <c r="C26">
+        <v>1028</v>
+      </c>
+      <c r="D26" s="1">
+        <v>4098169</v>
+      </c>
+      <c r="G26" s="4">
+        <v>2500</v>
+      </c>
+      <c r="H26" s="4">
+        <v>3000</v>
+      </c>
+      <c r="I26" s="5">
+        <v>1249</v>
+      </c>
+      <c r="J26" s="13">
+        <v>3434409</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>5000</v>
+      </c>
+      <c r="B27" s="1">
+        <v>10000</v>
+      </c>
+      <c r="C27">
+        <v>1430</v>
+      </c>
+      <c r="D27" s="1">
+        <v>10069839</v>
+      </c>
+      <c r="G27" s="5">
+        <v>3000</v>
+      </c>
+      <c r="H27" s="5">
+        <v>5000</v>
+      </c>
+      <c r="I27" s="5">
+        <v>2040</v>
+      </c>
+      <c r="J27" s="13">
+        <v>7656431</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>10000</v>
+      </c>
+      <c r="B28" s="1">
+        <v>20000</v>
+      </c>
+      <c r="C28">
+        <v>919</v>
+      </c>
+      <c r="D28" s="1">
+        <v>12721674</v>
+      </c>
+      <c r="G28" s="5">
+        <v>5000</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I28" s="5">
+        <v>868</v>
+      </c>
+      <c r="J28" s="13">
+        <v>6446727</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>20000</v>
+      </c>
+      <c r="B29" s="1">
+        <v>50000</v>
+      </c>
+      <c r="C29">
+        <v>600</v>
+      </c>
+      <c r="D29" s="1">
+        <v>18468944</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>50000</v>
+      </c>
+      <c r="B30" s="1">
+        <v>100000</v>
+      </c>
+      <c r="C30">
+        <v>189</v>
+      </c>
+      <c r="D30" s="1">
+        <v>13054945</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>100000</v>
+      </c>
+      <c r="B31" s="1">
+        <v>500000</v>
+      </c>
+      <c r="C31">
+        <v>188</v>
+      </c>
+      <c r="D31" s="1">
+        <v>38239651</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>500000</v>
+      </c>
+      <c r="B32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C32">
+        <v>33</v>
+      </c>
+      <c r="D32" s="1">
+        <v>37286597</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="1">
+        <f>SUM(D25:D32)</f>
+        <v>134681067</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D34" s="1">
         <v>241720134</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="3">
-        <f>100*D12/D13</f>
-        <v>56.259903446851474</v>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>67</v>
+      </c>
+      <c r="D37" s="1">
+        <f>SUM(D25:D32)</f>
+        <v>134681067</v>
+      </c>
+      <c r="J37" s="1">
+        <f>SUM(J25:J32)</f>
+        <v>17537567</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D38" s="1">
+        <f>D37+J37</f>
+        <v>152218634</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D39" s="3">
+        <f>100*D38/D34</f>
+        <v>62.973088538830616</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C23:D23"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFDC2E70-CE4D-4995-8529-70D230642B3F}">
   <dimension ref="A3:D15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2211,7 +4270,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D13" s="1">
         <f>SUM(D4:D12)</f>
@@ -2220,7 +4279,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D14" s="1">
         <v>241720134</v>
@@ -2228,377 +4287,11 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D15" s="3">
         <f>100*D13/D14</f>
         <v>67.67576258252447</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0349413B-3CBA-4C92-A836-5049A5909C6E}">
-  <dimension ref="A3:G36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="4" max="4" width="11.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1">
-        <v>3000</v>
-      </c>
-      <c r="D4" s="1">
-        <v>727660</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>3000</v>
-      </c>
-      <c r="B5" s="1">
-        <v>5000</v>
-      </c>
-      <c r="D5" s="1">
-        <v>779186</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5000</v>
-      </c>
-      <c r="B6" s="1">
-        <v>10000</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1632180</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>10000</v>
-      </c>
-      <c r="B7" s="1">
-        <v>20000</v>
-      </c>
-      <c r="D7" s="1">
-        <v>2145140</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>20000</v>
-      </c>
-      <c r="B8" s="1">
-        <v>50000</v>
-      </c>
-      <c r="D8" s="1">
-        <v>2157322</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>50000</v>
-      </c>
-      <c r="B9" s="1">
-        <v>100000</v>
-      </c>
-      <c r="D9" s="1">
-        <v>2566621</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>100000</v>
-      </c>
-      <c r="B10" s="1">
-        <v>500000</v>
-      </c>
-      <c r="D10" s="1">
-        <v>2807455</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>500000</v>
-      </c>
-      <c r="B11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1">
-        <v>3639955</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="1">
-        <f>SUM(D4:D11)</f>
-        <v>16455519</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="1">
-        <v>92736716</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="3">
-        <f>100*D12/D13</f>
-        <v>17.744340871419254</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>2</v>
-      </c>
-      <c r="B19" s="5">
-        <v>1000</v>
-      </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="5">
-        <v>6380</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="5">
-        <v>1000</v>
-      </c>
-      <c r="B20" s="5">
-        <v>2000</v>
-      </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="5">
-        <v>47916</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="5">
-        <v>2000</v>
-      </c>
-      <c r="B21" s="5">
-        <v>3000</v>
-      </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="5">
-        <v>113308</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="5">
-        <v>3000</v>
-      </c>
-      <c r="B22" s="5">
-        <v>5000</v>
-      </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="5">
-        <v>353375</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="5">
-        <v>5000</v>
-      </c>
-      <c r="B23" s="5">
-        <v>7000</v>
-      </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="5">
-        <v>389605</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="5">
-        <v>7000</v>
-      </c>
-      <c r="B24" s="5">
-        <v>10000</v>
-      </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="5">
-        <v>517796</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="5">
-        <v>10000</v>
-      </c>
-      <c r="B25" s="5">
-        <v>15000</v>
-      </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="5">
-        <v>951932</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="5">
-        <v>15000</v>
-      </c>
-      <c r="B26" s="5">
-        <v>20000</v>
-      </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="5">
-        <v>749591</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="5">
-        <v>20000</v>
-      </c>
-      <c r="B27" s="5">
-        <v>25000</v>
-      </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="5">
-        <v>559670</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="5">
-        <v>25000</v>
-      </c>
-      <c r="B28" s="5">
-        <v>30000</v>
-      </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="5">
-        <v>432250</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="5">
-        <v>30000</v>
-      </c>
-      <c r="B29" s="5">
-        <v>40000</v>
-      </c>
-      <c r="C29" s="4"/>
-      <c r="D29" s="5">
-        <v>854763</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="5">
-        <v>40000</v>
-      </c>
-      <c r="B30" s="5">
-        <v>50000</v>
-      </c>
-      <c r="C30" s="4"/>
-      <c r="D30" s="5">
-        <v>362266</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="5">
-        <v>50000</v>
-      </c>
-      <c r="B31" s="5">
-        <v>70000</v>
-      </c>
-      <c r="C31" s="4"/>
-      <c r="D31" s="5">
-        <v>1174773</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="5">
-        <v>70000</v>
-      </c>
-      <c r="B32" s="5">
-        <v>100000</v>
-      </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="5">
-        <v>1570708</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="5">
-        <v>100000</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C33" s="4"/>
-      <c r="D33" s="5">
-        <v>6188683</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="5">
-        <f>SUM(D19:D33)</f>
-        <v>14273016</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="5">
-        <v>100891244</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="3">
-        <f>100*D34/D35</f>
-        <v>14.146932314562401</v>
       </c>
     </row>
   </sheetData>
@@ -2607,13 +4300,18 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64A02521-C453-4789-9567-9D014E4404BA}">
-  <dimension ref="A3:D14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0349413B-3CBA-4C92-A836-5049A5909C6E}">
+  <dimension ref="A1:G56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
@@ -2634,7 +4332,7 @@
         <v>3000</v>
       </c>
       <c r="D4" s="1">
-        <v>622363</v>
+        <v>727660</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2645,7 +4343,7 @@
         <v>5000</v>
       </c>
       <c r="D5" s="1">
-        <v>1763827</v>
+        <v>779186</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2656,7 +4354,7 @@
         <v>10000</v>
       </c>
       <c r="D6" s="1">
-        <v>4660310</v>
+        <v>1632180</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2667,7 +4365,7 @@
         <v>20000</v>
       </c>
       <c r="D7" s="1">
-        <v>6417782</v>
+        <v>2145140</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2678,7 +4376,7 @@
         <v>50000</v>
       </c>
       <c r="D8" s="1">
-        <v>9741418</v>
+        <v>2157322</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2689,7 +4387,7 @@
         <v>100000</v>
       </c>
       <c r="D9" s="1">
-        <v>6720976</v>
+        <v>2566621</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2700,7 +4398,7 @@
         <v>500000</v>
       </c>
       <c r="D10" s="1">
-        <v>15459194</v>
+        <v>2807455</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2711,33 +4409,400 @@
         <v>3</v>
       </c>
       <c r="D11" s="1">
-        <v>16225204</v>
+        <v>3639955</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D12" s="1">
         <f>SUM(D4:D11)</f>
-        <v>61611074</v>
+        <v>16455519</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D13" s="1">
-        <v>117534315</v>
+        <v>92736716</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D14" s="3">
         <f>100*D12/D13</f>
-        <v>52.419647827955608</v>
+        <v>17.744340871419254</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B20" s="5">
+        <v>1000</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="5">
+        <v>6380</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="5">
+        <v>1000</v>
+      </c>
+      <c r="B21" s="5">
+        <v>2000</v>
+      </c>
+      <c r="C21" s="4"/>
+      <c r="D21" s="5">
+        <v>47916</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="5">
+        <v>2000</v>
+      </c>
+      <c r="B22" s="5">
+        <v>3000</v>
+      </c>
+      <c r="C22" s="4"/>
+      <c r="D22" s="5">
+        <v>113308</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="5">
+        <v>3000</v>
+      </c>
+      <c r="B23" s="5">
+        <v>5000</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="5">
+        <v>353375</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="5">
+        <v>5000</v>
+      </c>
+      <c r="B24" s="5">
+        <v>7000</v>
+      </c>
+      <c r="C24" s="4"/>
+      <c r="D24" s="5">
+        <v>389605</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="5">
+        <v>7000</v>
+      </c>
+      <c r="B25" s="5">
+        <v>10000</v>
+      </c>
+      <c r="C25" s="4"/>
+      <c r="D25" s="5">
+        <v>517796</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="5">
+        <v>10000</v>
+      </c>
+      <c r="B26" s="5">
+        <v>15000</v>
+      </c>
+      <c r="C26" s="4"/>
+      <c r="D26" s="5">
+        <v>951932</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="5">
+        <v>15000</v>
+      </c>
+      <c r="B27" s="5">
+        <v>20000</v>
+      </c>
+      <c r="C27" s="4"/>
+      <c r="D27" s="5">
+        <v>749591</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="5">
+        <v>20000</v>
+      </c>
+      <c r="B28" s="5">
+        <v>25000</v>
+      </c>
+      <c r="C28" s="4"/>
+      <c r="D28" s="5">
+        <v>559670</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="5">
+        <v>25000</v>
+      </c>
+      <c r="B29" s="5">
+        <v>30000</v>
+      </c>
+      <c r="C29" s="4"/>
+      <c r="D29" s="5">
+        <v>432250</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="5">
+        <v>30000</v>
+      </c>
+      <c r="B30" s="5">
+        <v>40000</v>
+      </c>
+      <c r="C30" s="4"/>
+      <c r="D30" s="5">
+        <v>854763</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="5">
+        <v>40000</v>
+      </c>
+      <c r="B31" s="5">
+        <v>50000</v>
+      </c>
+      <c r="C31" s="4"/>
+      <c r="D31" s="5">
+        <v>362266</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="5">
+        <v>50000</v>
+      </c>
+      <c r="B32" s="5">
+        <v>70000</v>
+      </c>
+      <c r="C32" s="4"/>
+      <c r="D32" s="5">
+        <v>1174773</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="5">
+        <v>70000</v>
+      </c>
+      <c r="B33" s="5">
+        <v>100000</v>
+      </c>
+      <c r="C33" s="4"/>
+      <c r="D33" s="5">
+        <v>1570708</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="5">
+        <v>100000</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C34" s="4"/>
+      <c r="D34" s="5">
+        <v>6188683</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="5">
+        <f>SUM(D20:D34)</f>
+        <v>14273016</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="5">
+        <v>100891244</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="3">
+        <f>100*D35/D36</f>
+        <v>14.146932314562401</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>2</v>
+      </c>
+      <c r="B43" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>10</v>
+      </c>
+      <c r="B44" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>20</v>
+      </c>
+      <c r="B45" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>50</v>
+      </c>
+      <c r="B46" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>100</v>
+      </c>
+      <c r="B47" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>200</v>
+      </c>
+      <c r="B48" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>500</v>
+      </c>
+      <c r="B49" s="1">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B50" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>2000</v>
+      </c>
+      <c r="B51" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>5000</v>
+      </c>
+      <c r="B52" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>10000</v>
+      </c>
+      <c r="B53" s="1">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>20000</v>
+      </c>
+      <c r="B54" s="1">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>50000</v>
+      </c>
+      <c r="B55" s="1">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>100000</v>
+      </c>
+      <c r="B56" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2746,290 +4811,999 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F486153-DE52-4DDC-AC00-DEE976B14729}">
-  <dimension ref="A3:D14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64A02521-C453-4789-9567-9D014E4404BA}">
+  <dimension ref="A2:J39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I2" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="J2" s="8"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C3" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="8"/>
+      <c r="G3" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H3" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
+      <c r="I3" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="J3" s="11" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4">
+        <v>1000</v>
+      </c>
+      <c r="H4">
+        <v>2000</v>
+      </c>
+      <c r="I4">
+        <v>6057</v>
+      </c>
+      <c r="J4" s="1">
+        <v>8161371</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B5" s="1">
         <v>3000</v>
       </c>
-      <c r="D4" s="1">
-        <v>875596</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+      <c r="C5">
+        <v>316</v>
+      </c>
+      <c r="D5" s="1">
+        <v>622363</v>
+      </c>
+      <c r="G5">
+        <v>2000</v>
+      </c>
+      <c r="H5">
         <v>3000</v>
       </c>
-      <c r="B5" s="1">
+      <c r="I5">
+        <v>1450</v>
+      </c>
+      <c r="J5" s="1">
+        <v>3500966</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>3000</v>
+      </c>
+      <c r="B6" s="1">
         <v>5000</v>
       </c>
-      <c r="D5" s="1">
-        <v>2137680</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+      <c r="C6">
+        <v>443</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1763827</v>
+      </c>
+      <c r="G6" s="1">
+        <v>3000</v>
+      </c>
+      <c r="H6" s="1">
         <v>5000</v>
       </c>
-      <c r="B6" s="1">
+      <c r="I6" s="1">
+        <v>833</v>
+      </c>
+      <c r="J6" s="1">
+        <v>3125682</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>5000</v>
+      </c>
+      <c r="B7" s="1">
         <v>10000</v>
       </c>
-      <c r="D6" s="1">
-        <v>5330060</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+      <c r="C7">
+        <v>654</v>
+      </c>
+      <c r="D7" s="1">
+        <v>4660310</v>
+      </c>
+      <c r="G7" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H7" t="s">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>372</v>
+      </c>
+      <c r="J7" s="1">
+        <v>2900584</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>10000</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B8" s="1">
         <v>20000</v>
       </c>
-      <c r="D7" s="1">
-        <v>6616796</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+      <c r="C8">
+        <v>459</v>
+      </c>
+      <c r="D8" s="1">
+        <v>6417782</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>20000</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B9" s="1">
         <v>50000</v>
       </c>
-      <c r="D8" s="1">
-        <v>11565985</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+      <c r="C9">
+        <v>311</v>
+      </c>
+      <c r="D9" s="1">
+        <v>9741418</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>50000</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B10" s="1">
         <v>100000</v>
       </c>
-      <c r="D9" s="1">
-        <v>7908160</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+      <c r="C10">
+        <v>97</v>
+      </c>
+      <c r="D10" s="1">
+        <v>6720976</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>100000</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B11" s="1">
         <v>500000</v>
       </c>
-      <c r="D10" s="1">
-        <v>23315401</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+      <c r="C11">
+        <v>78</v>
+      </c>
+      <c r="D11" s="1">
+        <v>15459194</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
         <v>500000</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B12" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="1">
-        <v>23231465</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="C12">
+        <v>14</v>
+      </c>
+      <c r="D12" s="1">
+        <v>16225204</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="1">
+        <f>SUM(D5:D12)</f>
+        <v>61611074</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14">
+        <f>SUM(C5:C12)</f>
+        <v>2372</v>
+      </c>
+      <c r="D14" s="1">
+        <v>117534315</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="1">
-        <f>SUM(D4:D11)</f>
-        <v>80981143</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="1">
-        <v>130079210</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="3">
-        <f>100*D12/D13</f>
-        <v>62.255254317734554</v>
+      <c r="D15" s="3">
+        <f>100*D13/D14</f>
+        <v>52.419647827955608</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C23" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="8"/>
+      <c r="I23" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="J23" s="8"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2500</v>
+      </c>
+      <c r="B25" s="1">
+        <v>3000</v>
+      </c>
+      <c r="C25">
+        <v>97</v>
+      </c>
+      <c r="D25" s="1">
+        <v>266317</v>
+      </c>
+      <c r="J25" s="1"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>3000</v>
+      </c>
+      <c r="B26" s="1">
+        <v>5000</v>
+      </c>
+      <c r="C26">
+        <v>443</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1763827</v>
+      </c>
+      <c r="G26">
+        <v>2500</v>
+      </c>
+      <c r="H26">
+        <v>3000</v>
+      </c>
+      <c r="I26">
+        <v>477</v>
+      </c>
+      <c r="J26" s="1">
+        <v>1311563</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>5000</v>
+      </c>
+      <c r="B27" s="1">
+        <v>10000</v>
+      </c>
+      <c r="C27">
+        <v>654</v>
+      </c>
+      <c r="D27" s="1">
+        <v>4660310</v>
+      </c>
+      <c r="G27" s="1">
+        <v>3000</v>
+      </c>
+      <c r="H27" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I27" s="1">
+        <v>833</v>
+      </c>
+      <c r="J27" s="1">
+        <v>3125682</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>10000</v>
+      </c>
+      <c r="B28" s="1">
+        <v>20000</v>
+      </c>
+      <c r="C28">
+        <v>459</v>
+      </c>
+      <c r="D28" s="1">
+        <v>6417782</v>
+      </c>
+      <c r="G28" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H28" t="s">
+        <v>3</v>
+      </c>
+      <c r="I28">
+        <v>372</v>
+      </c>
+      <c r="J28" s="1">
+        <v>2900584</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>20000</v>
+      </c>
+      <c r="B29" s="1">
+        <v>50000</v>
+      </c>
+      <c r="C29">
+        <v>311</v>
+      </c>
+      <c r="D29" s="1">
+        <v>9741418</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>50000</v>
+      </c>
+      <c r="B30" s="1">
+        <v>100000</v>
+      </c>
+      <c r="C30">
+        <v>97</v>
+      </c>
+      <c r="D30" s="1">
+        <v>6720976</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>100000</v>
+      </c>
+      <c r="B31" s="1">
+        <v>500000</v>
+      </c>
+      <c r="C31">
+        <v>78</v>
+      </c>
+      <c r="D31" s="1">
+        <v>15459194</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>500000</v>
+      </c>
+      <c r="B32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C32">
+        <v>14</v>
+      </c>
+      <c r="D32" s="1">
+        <v>16225204</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="1">
+        <f>SUM(D25:D32)</f>
+        <v>61255028</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D34" s="1">
+        <v>117534315</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>67</v>
+      </c>
+      <c r="D37" s="1">
+        <f>SUM(D25:D32)</f>
+        <v>61255028</v>
+      </c>
+      <c r="J37" s="1">
+        <f>SUM(J25:J32)</f>
+        <v>7337829</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D38" s="1">
+        <f>D37+J37</f>
+        <v>68592857</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D39" s="3">
+        <f>100*D38/D34</f>
+        <v>58.359856013114126</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="I23:J23"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D70B758-2D8E-4D0F-9152-375389941F4D}">
-  <dimension ref="A3:D15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F486153-DE52-4DDC-AC00-DEE976B14729}">
+  <dimension ref="A2:J39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="22.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C3" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="8"/>
+      <c r="I3" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
+      <c r="C4" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="G4" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B5" s="1">
         <v>3000</v>
       </c>
-      <c r="D4" s="1">
-        <v>970800</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+      <c r="C5">
+        <v>460</v>
+      </c>
+      <c r="D5" s="1">
+        <v>875596</v>
+      </c>
+      <c r="G5" s="4">
+        <v>1000</v>
+      </c>
+      <c r="H5" s="4">
+        <v>2000</v>
+      </c>
+      <c r="I5" s="5">
+        <v>6333</v>
+      </c>
+      <c r="J5" s="13">
+        <v>8573108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>3000</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B6" s="1">
         <v>5000</v>
       </c>
-      <c r="D5" s="1">
-        <v>2312878</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+      <c r="C6">
+        <v>535</v>
+      </c>
+      <c r="D6" s="1">
+        <v>2137680</v>
+      </c>
+      <c r="G6" s="4">
+        <v>2000</v>
+      </c>
+      <c r="H6" s="4">
+        <v>3000</v>
+      </c>
+      <c r="I6" s="5">
+        <v>1385</v>
+      </c>
+      <c r="J6" s="13">
+        <v>3333563</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>5000</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B7" s="1">
         <v>10000</v>
       </c>
-      <c r="D6" s="1">
-        <v>5385703</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+      <c r="C7">
+        <v>761</v>
+      </c>
+      <c r="D7" s="1">
+        <v>5330060</v>
+      </c>
+      <c r="G7" s="5">
+        <v>3000</v>
+      </c>
+      <c r="H7" s="5">
+        <v>5000</v>
+      </c>
+      <c r="I7" s="5">
+        <v>846</v>
+      </c>
+      <c r="J7" s="13">
+        <v>3199082</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>10000</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B8" s="1">
         <v>20000</v>
       </c>
-      <c r="D7" s="1">
-        <v>6890054</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+      <c r="C8">
+        <v>476</v>
+      </c>
+      <c r="D8" s="1">
+        <v>6616796</v>
+      </c>
+      <c r="G8" s="5">
+        <v>5000</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="5">
+        <v>434</v>
+      </c>
+      <c r="J8" s="13">
+        <v>3401655</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>20000</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B9" s="1">
         <v>50000</v>
       </c>
-      <c r="D8" s="1">
-        <v>11978294</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+      <c r="C9">
+        <v>368</v>
+      </c>
+      <c r="D9" s="1">
+        <v>11565985</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>50000</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B10" s="1">
         <v>100000</v>
       </c>
-      <c r="D9" s="1">
-        <v>9081267</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+      <c r="C10">
+        <v>114</v>
+      </c>
+      <c r="D10" s="1">
+        <v>7908160</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>100000</v>
-      </c>
-      <c r="B10" s="1">
-        <v>250000</v>
-      </c>
-      <c r="D10" s="1">
-        <v>12881225</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>250000</v>
       </c>
       <c r="B11" s="1">
         <v>500000</v>
       </c>
+      <c r="C11">
+        <v>107</v>
+      </c>
       <c r="D11" s="1">
-        <v>14159420</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>23315401</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>500000</v>
       </c>
       <c r="B12" t="s">
         <v>3</v>
       </c>
+      <c r="C12">
+        <v>17</v>
+      </c>
       <c r="D12" s="1">
-        <v>31714226</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>23231465</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="1">
+        <f>SUM(D5:D12)</f>
+        <v>80981143</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14">
+        <f>SUM(C5:C12)</f>
+        <v>2838</v>
+      </c>
+      <c r="D14" s="1">
+        <v>130079210</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="D13" s="1">
-        <f>SUM(D4:D12)</f>
-        <v>95373867</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="1">
-        <v>241720134</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="D15" s="3">
         <f>100*D13/D14</f>
-        <v>39.456318934524504</v>
+        <v>62.255254317734554</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C23" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="8"/>
+      <c r="I23" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="J23" s="8"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2500</v>
+      </c>
+      <c r="B25" s="1">
+        <v>3000</v>
+      </c>
+      <c r="C25">
+        <v>125</v>
+      </c>
+      <c r="D25" s="1">
+        <v>342858</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="13"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>3000</v>
+      </c>
+      <c r="B26" s="1">
+        <v>5000</v>
+      </c>
+      <c r="C26">
+        <v>535</v>
+      </c>
+      <c r="D26" s="1">
+        <v>2137680</v>
+      </c>
+      <c r="G26" s="4">
+        <v>2500</v>
+      </c>
+      <c r="H26" s="4">
+        <v>3000</v>
+      </c>
+      <c r="I26" s="5">
+        <v>435</v>
+      </c>
+      <c r="J26" s="13">
+        <v>1195222</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>5000</v>
+      </c>
+      <c r="B27" s="1">
+        <v>10000</v>
+      </c>
+      <c r="C27">
+        <v>761</v>
+      </c>
+      <c r="D27" s="1">
+        <v>5330060</v>
+      </c>
+      <c r="G27" s="5">
+        <v>3000</v>
+      </c>
+      <c r="H27" s="5">
+        <v>5000</v>
+      </c>
+      <c r="I27" s="5">
+        <v>846</v>
+      </c>
+      <c r="J27" s="13">
+        <v>3199082</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>10000</v>
+      </c>
+      <c r="B28" s="1">
+        <v>20000</v>
+      </c>
+      <c r="C28">
+        <v>476</v>
+      </c>
+      <c r="D28" s="1">
+        <v>6616796</v>
+      </c>
+      <c r="G28" s="5">
+        <v>5000</v>
+      </c>
+      <c r="H28" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="I28" s="5">
+        <v>434</v>
+      </c>
+      <c r="J28" s="13">
+        <v>3401655</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>20000</v>
+      </c>
+      <c r="B29" s="1">
+        <v>50000</v>
+      </c>
+      <c r="C29">
+        <v>368</v>
+      </c>
+      <c r="D29" s="1">
+        <v>11565985</v>
+      </c>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>50000</v>
+      </c>
+      <c r="B30" s="1">
+        <v>100000</v>
+      </c>
+      <c r="C30">
+        <v>114</v>
+      </c>
+      <c r="D30" s="1">
+        <v>7908160</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>100000</v>
+      </c>
+      <c r="B31" s="1">
+        <v>500000</v>
+      </c>
+      <c r="C31">
+        <v>107</v>
+      </c>
+      <c r="D31" s="1">
+        <v>23315401</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>500000</v>
+      </c>
+      <c r="B32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C32">
+        <v>17</v>
+      </c>
+      <c r="D32" s="1">
+        <v>23231465</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="1">
+        <f>SUM(D25:D32)</f>
+        <v>80448405</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D34" s="1">
+        <v>130079210</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>67</v>
+      </c>
+      <c r="D37" s="1">
+        <f>SUM(D25:D32)</f>
+        <v>80448405</v>
+      </c>
+      <c r="J37" s="1">
+        <f>SUM(J25:J32)</f>
+        <v>7795959</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D38" s="1">
+        <f>D37+J37</f>
+        <v>88244364</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D39" s="3">
+        <f>100*D38/D34</f>
+        <v>67.838945208846212</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/workbooks/urbanization.xlsx
+++ b/workbooks/urbanization.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C6BAEA-8358-4B05-9308-53BB069095E6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC9E131-69C9-4DB3-AF72-0AD62B87B705}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="1" xr2:uid="{9806A3BC-D491-4476-99E9-37D3951075C7}"/>
+    <workbookView xWindow="945" yWindow="915" windowWidth="21045" windowHeight="20055" firstSheet="3" activeTab="3" xr2:uid="{9806A3BC-D491-4476-99E9-37D3951075C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="76">
   <si>
     <t>от</t>
   </si>
@@ -117,25 +117,13 @@
     <t>городское</t>
   </si>
   <si>
-    <t>гор. офиц.</t>
-  </si>
-  <si>
-    <t>т.е.  живущих в пунктах с более 2500</t>
-  </si>
-  <si>
     <t>MX-1960</t>
-  </si>
-  <si>
-    <t>"VIII Censo General de Población 1960. 8 de junio de 1960. Resumen general", cтр. 59, 68</t>
   </si>
   <si>
     <t>"Quinto Censo de Población. 15 de mayo de 1930. Resumen general", стр. 39-40</t>
   </si>
   <si>
     <t>MX-1970</t>
-  </si>
-  <si>
-    <t>v</t>
   </si>
   <si>
     <t>см. стр 5</t>
@@ -248,15 +236,52 @@
   <si>
     <t>всего в более 2500</t>
   </si>
+  <si>
+    <t>Население в пунктах численностью 2000 жителей и выше</t>
+  </si>
+  <si>
+    <t>Население в пунктах численностью 2500 жителей и выше</t>
+  </si>
+  <si>
+    <t>% в более 2000</t>
+  </si>
+  <si>
+    <t>всего в более 2000</t>
+  </si>
+  <si>
+    <t>сумма &gt; 2000</t>
+  </si>
+  <si>
+    <t>"VIII Censo General de Población 1960. 8 de junio de 1960. Resumen general", cтр. 59, 68, xlv-xlvi, 1</t>
+  </si>
+  <si>
+    <t>"X Censo General de Población 1970. 28 de enero de 1970. Resumen general", стр. 7, v, 4</t>
+  </si>
+  <si>
+    <t>гор. офиц. т.е.  живущих в пунктах с более 2500</t>
+  </si>
+  <si>
+    <t>сумма &gt; 5000</t>
+  </si>
+  <si>
+    <t>Население в пунктах численностью 5000 жителей и выше</t>
+  </si>
+  <si>
+    <t>всего в более 5000</t>
+  </si>
+  <si>
+    <t>% в более 5000</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -287,13 +312,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="8" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -308,7 +347,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -317,12 +356,6 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -337,6 +370,22 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -669,13 +718,13 @@
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -686,7 +735,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -697,7 +746,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -732,7 +781,7 @@
         <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -740,7 +789,7 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -756,20 +805,23 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
+      </c>
+      <c r="B26" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -929,19 +981,25 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD1CEBF5-B4BD-4DD1-AC0A-66E7B41EFED5}">
-  <dimension ref="A3:H17"/>
+  <dimension ref="A2:H30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B2" s="9" t="s">
         <v>1</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -963,6 +1021,9 @@
       <c r="B5" s="1">
         <v>1500</v>
       </c>
+      <c r="C5">
+        <v>1036</v>
+      </c>
       <c r="D5" s="1">
         <v>1251217</v>
       </c>
@@ -975,6 +1036,9 @@
       <c r="B6" s="1">
         <v>2000</v>
       </c>
+      <c r="C6">
+        <v>503</v>
+      </c>
       <c r="D6" s="1">
         <v>863103</v>
       </c>
@@ -986,6 +1050,9 @@
       <c r="B7" s="1">
         <v>2500</v>
       </c>
+      <c r="C7">
+        <v>276</v>
+      </c>
       <c r="D7" s="1">
         <v>614036</v>
       </c>
@@ -997,6 +1064,9 @@
       <c r="B8" s="1">
         <v>3000</v>
       </c>
+      <c r="C8">
+        <v>155</v>
+      </c>
       <c r="D8" s="1">
         <v>418091</v>
       </c>
@@ -1008,6 +1078,9 @@
       <c r="B9" s="1">
         <v>3500</v>
       </c>
+      <c r="C9">
+        <v>82</v>
+      </c>
       <c r="D9" s="1">
         <v>263400</v>
       </c>
@@ -1019,6 +1092,9 @@
       <c r="B10" s="1">
         <v>4000</v>
       </c>
+      <c r="C10">
+        <v>58</v>
+      </c>
       <c r="D10" s="1">
         <v>216700</v>
       </c>
@@ -1030,6 +1106,9 @@
       <c r="B11" s="1">
         <v>4500</v>
       </c>
+      <c r="C11">
+        <v>61</v>
+      </c>
       <c r="D11" s="1">
         <v>258876</v>
       </c>
@@ -1041,6 +1120,9 @@
       <c r="B12" s="1">
         <v>5000</v>
       </c>
+      <c r="C12">
+        <v>32</v>
+      </c>
       <c r="D12" s="1">
         <v>151698</v>
       </c>
@@ -1052,6 +1134,9 @@
       <c r="B13" t="s">
         <v>3</v>
       </c>
+      <c r="C13">
+        <v>218</v>
+      </c>
       <c r="D13" s="1">
         <v>4232232</v>
       </c>
@@ -1065,7 +1150,7 @@
         <v>8269353</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -1079,9 +1164,7 @@
       <c r="F15" s="1">
         <v>5540631</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>25</v>
-      </c>
+      <c r="H15" s="1"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
@@ -1102,6 +1185,127 @@
       <c r="F17" s="3">
         <f>100*F15/D16</f>
         <v>33.472627643960912</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A20" s="14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>2000</v>
+      </c>
+      <c r="B22" s="1">
+        <v>2500</v>
+      </c>
+      <c r="C22">
+        <v>276</v>
+      </c>
+      <c r="D22" s="1">
+        <v>614036</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>2500</v>
+      </c>
+      <c r="B23" s="1">
+        <v>3000</v>
+      </c>
+      <c r="C23">
+        <v>155</v>
+      </c>
+      <c r="D23" s="1">
+        <v>418091</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>3000</v>
+      </c>
+      <c r="B24" s="1">
+        <v>3500</v>
+      </c>
+      <c r="C24">
+        <v>82</v>
+      </c>
+      <c r="D24" s="1">
+        <v>263400</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>3500</v>
+      </c>
+      <c r="B25" s="1">
+        <v>4000</v>
+      </c>
+      <c r="C25">
+        <v>58</v>
+      </c>
+      <c r="D25" s="1">
+        <v>216700</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>4000</v>
+      </c>
+      <c r="B26" s="1">
+        <v>4500</v>
+      </c>
+      <c r="C26">
+        <v>61</v>
+      </c>
+      <c r="D26" s="1">
+        <v>258876</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>4500</v>
+      </c>
+      <c r="B27" s="1">
+        <v>5000</v>
+      </c>
+      <c r="C27">
+        <v>32</v>
+      </c>
+      <c r="D27" s="1">
+        <v>151698</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>5000</v>
+      </c>
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28">
+        <v>218</v>
+      </c>
+      <c r="D28" s="1">
+        <v>4232232</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" s="1">
+        <f>SUM(D22:D28)</f>
+        <v>6155033</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="15">
+        <f>100*D29/D16</f>
+        <v>37.184415952856575</v>
       </c>
     </row>
   </sheetData>
@@ -1111,463 +1315,1013 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E93D3E-D80F-423E-BDEC-5E3B3CDBD631}">
-  <dimension ref="A3:G23"/>
+  <dimension ref="A2:H40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B2" s="9" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="C2" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4">
+        <v>100</v>
+      </c>
+      <c r="C4" s="4">
+        <v>51555</v>
+      </c>
+      <c r="D4" s="5">
+        <f>D21-SUM(D5:D18)</f>
+        <v>1558268</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>100</v>
+      </c>
+      <c r="B5" s="4">
+        <v>500</v>
+      </c>
+      <c r="C5">
+        <v>27098</v>
+      </c>
+      <c r="D5" s="1">
+        <v>6410224</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>500</v>
+      </c>
+      <c r="B6" s="1">
         <v>1000</v>
       </c>
-      <c r="C4" s="1">
-        <f>C19-C17</f>
-        <v>12222347</v>
-      </c>
-      <c r="D4" s="1"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+      <c r="C6" s="1">
+        <v>6156</v>
+      </c>
+      <c r="D6" s="1">
+        <v>4253855</v>
+      </c>
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>1000</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B7" s="1">
         <v>2500</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C7" s="1">
+        <v>3342</v>
+      </c>
+      <c r="D7" s="1">
         <v>4995664</v>
       </c>
-      <c r="D5" s="1"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>2500</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B8" s="1">
         <v>5000</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C8" s="1">
+        <v>865</v>
+      </c>
+      <c r="D8" s="1">
         <v>2959460</v>
       </c>
-      <c r="D6" s="1"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>5000</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B9" s="1">
         <v>10000</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C9" s="1">
+        <v>340</v>
+      </c>
+      <c r="D9" s="1">
         <v>2366431</v>
       </c>
-      <c r="D7" s="1"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>10000</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B10" s="1">
         <v>20000</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C10" s="1">
+        <v>146</v>
+      </c>
+      <c r="D10" s="1">
         <v>2027511</v>
       </c>
-      <c r="D8" s="1"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>20000</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B11" s="1">
         <v>30000</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C11" s="1">
+        <v>38</v>
+      </c>
+      <c r="D11" s="1">
         <v>939938</v>
       </c>
-      <c r="D9" s="1"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
         <v>30000</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B12" s="1">
         <v>40000</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C12" s="1">
+        <v>20</v>
+      </c>
+      <c r="D12" s="1">
         <v>683971</v>
       </c>
-      <c r="D10" s="1"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
         <v>40000</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B13" s="1">
         <v>50000</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C13" s="1">
+        <v>11</v>
+      </c>
+      <c r="D13" s="1">
         <v>484642</v>
       </c>
-      <c r="D11" s="1"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+      <c r="E13" s="1"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
         <v>50000</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B14" s="1">
         <v>75000</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C14" s="1">
+        <v>15</v>
+      </c>
+      <c r="D14" s="1">
         <v>932190</v>
       </c>
-      <c r="D12" s="1"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
+      <c r="E14" s="1"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
         <v>75000</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B15" s="1">
         <v>100000</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C15" s="1">
+        <v>9</v>
+      </c>
+      <c r="D15" s="1">
         <v>798743</v>
       </c>
-      <c r="D13" s="1"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
+      <c r="E15" s="1"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
         <v>100000</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B16" s="1">
         <v>250000</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C16" s="1">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1">
         <v>1795192</v>
       </c>
-      <c r="D14" s="1"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
+      <c r="E16" s="1"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
         <v>250000</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B17" s="1">
         <v>500000</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C17" s="1">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1">
         <v>551168</v>
       </c>
-      <c r="D15" s="1"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
+      <c r="E17" s="1"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
         <v>500000</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B18" t="s">
         <v>3</v>
       </c>
-      <c r="C16" s="1">
+      <c r="D18" s="1">
         <v>4165872</v>
       </c>
-      <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="E18" s="1"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="1">
-        <f>SUM(C5:C16)</f>
+      <c r="D19" s="1">
+        <f>SUM(D7:D18)</f>
         <v>22700782</v>
       </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+      <c r="E19" s="3"/>
+      <c r="F19" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="1">
-        <f>C17</f>
+      <c r="D20" s="1">
+        <f>D19</f>
         <v>22700782</v>
       </c>
-      <c r="E18" s="1">
+      <c r="F20" s="1">
         <v>17218011</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="1">
+      <c r="D21" s="1">
         <v>34923129</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C20">
-        <f>100*C18/C19</f>
+      <c r="D22">
+        <f>100*D20/D21</f>
         <v>65.002142276541136</v>
       </c>
-      <c r="E20" s="3">
-        <f>100*E18/C19</f>
+      <c r="F22" s="3">
+        <f>100*F20/D21</f>
         <v>49.302601150085948</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>59</v>
-      </c>
-      <c r="B23">
+    <row r="25" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A25" s="14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>2000</v>
+      </c>
+      <c r="B27" s="1">
+        <v>2500</v>
+      </c>
+      <c r="C27" s="1">
+        <v>491</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1092427</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>2500</v>
+      </c>
+      <c r="B28" s="1">
+        <v>5000</v>
+      </c>
+      <c r="C28" s="1">
+        <v>865</v>
+      </c>
+      <c r="D28" s="1">
+        <v>2959460</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>5000</v>
+      </c>
+      <c r="B29" s="1">
+        <v>10000</v>
+      </c>
+      <c r="C29" s="1">
+        <v>340</v>
+      </c>
+      <c r="D29" s="1">
+        <v>2366431</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>10000</v>
+      </c>
+      <c r="B30" s="1">
+        <v>20000</v>
+      </c>
+      <c r="C30" s="1">
+        <v>146</v>
+      </c>
+      <c r="D30" s="1">
+        <v>2027511</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>20000</v>
+      </c>
+      <c r="B31" s="1">
+        <v>30000</v>
+      </c>
+      <c r="C31" s="1">
+        <v>38</v>
+      </c>
+      <c r="D31" s="1">
+        <v>939938</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>30000</v>
+      </c>
+      <c r="B32" s="1">
+        <v>40000</v>
+      </c>
+      <c r="C32" s="1">
+        <v>20</v>
+      </c>
+      <c r="D32" s="1">
+        <v>683971</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>40000</v>
+      </c>
+      <c r="B33" s="1">
+        <v>50000</v>
+      </c>
+      <c r="C33" s="1">
+        <v>11</v>
+      </c>
+      <c r="D33" s="1">
+        <v>484642</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>50000</v>
+      </c>
+      <c r="B34" s="1">
+        <v>75000</v>
+      </c>
+      <c r="C34" s="1">
+        <v>15</v>
+      </c>
+      <c r="D34" s="1">
+        <v>932190</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>75000</v>
+      </c>
+      <c r="B35" s="1">
+        <v>100000</v>
+      </c>
+      <c r="C35" s="1">
+        <v>9</v>
+      </c>
+      <c r="D35" s="1">
+        <v>798743</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>100000</v>
+      </c>
+      <c r="B36" s="1">
+        <v>250000</v>
+      </c>
+      <c r="C36" s="1">
+        <v>1</v>
+      </c>
+      <c r="D36" s="1">
+        <v>1795192</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>250000</v>
+      </c>
+      <c r="B37" s="1">
+        <v>500000</v>
+      </c>
+      <c r="C37" s="1">
+        <v>3</v>
+      </c>
+      <c r="D37" s="1">
+        <v>551168</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>500000</v>
+      </c>
+      <c r="B38" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="1">
+        <v>4165872</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
         <v>68</v>
+      </c>
+      <c r="D39" s="1">
+        <f>SUM(D27:D38)</f>
+        <v>18797545</v>
+      </c>
+      <c r="F39" s="16">
+        <f>100*D39/D21</f>
+        <v>53.825489119259615</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D40" s="1">
+        <f>SUM(D29:D38)</f>
+        <v>14745658</v>
+      </c>
+      <c r="F40" s="16">
+        <f>100*D40/D21</f>
+        <v>42.223186816965914</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A2F5240-BC93-4757-9D88-C679B5B701EC}">
-  <dimension ref="A3:E26"/>
+  <dimension ref="A3:M42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="15.140625" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" style="18" customWidth="1"/>
+    <col min="13" max="13" width="10.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="9" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1">
+      <c r="C3" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4">
+        <v>100</v>
+      </c>
+      <c r="C5">
+        <v>55650</v>
+      </c>
+      <c r="D5" s="10">
+        <v>1471154</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>100</v>
+      </c>
+      <c r="B6" s="4">
+        <v>500</v>
+      </c>
+      <c r="C6">
+        <v>28055</v>
+      </c>
+      <c r="D6" s="10">
+        <v>6889077</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>500</v>
+      </c>
+      <c r="B7" s="1">
         <v>1000</v>
       </c>
-      <c r="C4" s="1">
-        <f>C19-C17</f>
-        <v>13550397</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+      <c r="C7">
+        <v>7473</v>
+      </c>
+      <c r="D7" s="10">
+        <v>5190166</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>1000</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B8" s="1">
         <v>2500</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C8">
+        <v>4232</v>
+      </c>
+      <c r="D8" s="10">
         <v>6366285</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>2500</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B9" s="1">
         <v>5000</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C9">
+        <v>1201</v>
+      </c>
+      <c r="D9" s="10">
         <v>4129872</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>5000</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B10" s="1">
         <v>10000</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C10">
+        <v>539</v>
+      </c>
+      <c r="D10" s="10">
         <v>3764208</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>10000</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B11" s="1">
         <v>20000</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C11">
+        <v>248</v>
+      </c>
+      <c r="D11" s="10">
         <v>3409846</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
         <v>20000</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B12" s="1">
         <v>30000</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C12">
+        <v>65</v>
+      </c>
+      <c r="D12" s="10">
         <v>1531569</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
         <v>30000</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B13" s="1">
         <v>40000</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C13">
+        <v>30</v>
+      </c>
+      <c r="D13" s="10">
         <v>1015827</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
         <v>40000</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B14" s="1">
         <v>50000</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C14">
+        <v>19</v>
+      </c>
+      <c r="D14" s="10">
         <v>858422</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+      <c r="M14" s="10"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
         <v>50000</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B15" s="1">
         <v>75000</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C15">
+        <v>21</v>
+      </c>
+      <c r="D15" s="10">
         <v>1242173</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
+      <c r="M15" s="10"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
         <v>75000</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B16" s="1">
         <v>100000</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C16">
+        <v>13</v>
+      </c>
+      <c r="D16" s="10">
         <v>1114396</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
+      <c r="M16" s="10"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
         <v>100000</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B17" s="1">
         <v>250000</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C17">
+        <v>24</v>
+      </c>
+      <c r="D17" s="10">
         <v>3735336</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
+      <c r="M17" s="10"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
         <v>250000</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B18" s="1">
         <v>500000</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C18">
+        <v>6</v>
+      </c>
+      <c r="D18" s="10">
         <v>1971794</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
+      <c r="M18" s="10"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
         <v>500000</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B19" t="s">
         <v>3</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C19">
+        <v>4</v>
+      </c>
+      <c r="D19" s="10">
         <v>5535113</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="M19" s="10"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="1">
-        <f>SUM(C5:C16)</f>
+      <c r="D20" s="1">
+        <f>SUM(D8:D19)</f>
         <v>34674841</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M20" s="10"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="1">
+        <f>D20</f>
+        <v>34674841</v>
+      </c>
+      <c r="F21" s="1">
+        <f>D22-D8-D7</f>
+        <v>36668787</v>
+      </c>
+      <c r="M21" s="10"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="1">
+        <v>48225238</v>
+      </c>
+      <c r="M22" s="10"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="3">
+        <f>100*D21/D22</f>
+        <v>71.901855621738974</v>
+      </c>
+      <c r="F23" s="3">
+        <f>100*F21/D22</f>
+        <v>76.036508103910236</v>
+      </c>
+      <c r="M23" s="10"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J24" s="10"/>
+      <c r="M24" s="10"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M25" s="10"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M26" s="10"/>
+    </row>
+    <row r="27" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A27" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="M27" s="10"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M28" s="10"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>2000</v>
+      </c>
+      <c r="B29" s="1">
+        <v>2500</v>
+      </c>
+      <c r="C29">
+        <v>651</v>
+      </c>
+      <c r="D29" s="10">
+        <v>1449152</v>
+      </c>
+      <c r="M29" s="10"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>2500</v>
+      </c>
+      <c r="B30" s="1">
+        <v>5000</v>
+      </c>
+      <c r="C30">
+        <v>1201</v>
+      </c>
+      <c r="D30" s="10">
+        <v>4129872</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>5000</v>
+      </c>
+      <c r="B31" s="1">
+        <v>10000</v>
+      </c>
+      <c r="C31">
+        <v>539</v>
+      </c>
+      <c r="D31" s="10">
+        <v>3764208</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>10000</v>
+      </c>
+      <c r="B32" s="1">
+        <v>20000</v>
+      </c>
+      <c r="C32">
+        <v>248</v>
+      </c>
+      <c r="D32" s="10">
+        <v>3409846</v>
+      </c>
+      <c r="M32" s="1"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>20000</v>
+      </c>
+      <c r="B33" s="1">
+        <v>30000</v>
+      </c>
+      <c r="C33">
+        <v>65</v>
+      </c>
+      <c r="D33" s="10">
+        <v>1531569</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>30000</v>
+      </c>
+      <c r="B34" s="1">
+        <v>40000</v>
+      </c>
+      <c r="C34">
+        <v>30</v>
+      </c>
+      <c r="D34" s="10">
+        <v>1015827</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>40000</v>
+      </c>
+      <c r="B35" s="1">
+        <v>50000</v>
+      </c>
+      <c r="C35">
+        <v>19</v>
+      </c>
+      <c r="D35" s="10">
+        <v>858422</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>50000</v>
+      </c>
+      <c r="B36" s="1">
+        <v>75000</v>
+      </c>
+      <c r="C36">
+        <v>21</v>
+      </c>
+      <c r="D36" s="10">
+        <v>1242173</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>75000</v>
+      </c>
+      <c r="B37" s="1">
+        <v>100000</v>
+      </c>
+      <c r="C37">
+        <v>13</v>
+      </c>
+      <c r="D37" s="10">
+        <v>1114396</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>100000</v>
+      </c>
+      <c r="B38" s="1">
+        <v>250000</v>
+      </c>
+      <c r="C38">
         <v>24</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="1">
-        <f>C17</f>
-        <v>34674841</v>
-      </c>
-      <c r="E18" s="1">
-        <f>C19-C5-C4</f>
-        <v>28308556</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="1">
-        <v>48225238</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="3">
-        <f>100*C18/C19</f>
-        <v>71.901855621738974</v>
-      </c>
-      <c r="E20" s="3">
-        <f>100*E18/C19</f>
-        <v>58.700707708275075</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>7</v>
-      </c>
-      <c r="B24">
+      <c r="D38" s="10">
+        <v>3735336</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>250000</v>
+      </c>
+      <c r="B39" s="1">
+        <v>500000</v>
+      </c>
+      <c r="C39">
+        <v>6</v>
+      </c>
+      <c r="D39" s="10">
+        <v>1971794</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>500000</v>
+      </c>
+      <c r="B40" t="s">
+        <v>3</v>
+      </c>
+      <c r="C40">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>30</v>
+      <c r="D40" s="10">
+        <v>5535113</v>
+      </c>
+      <c r="F40" s="13" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D41" s="1">
+        <f>SUM(D29:D40)</f>
+        <v>29757708</v>
+      </c>
+      <c r="F41" s="16">
+        <f>100*D41/D22</f>
+        <v>61.705673697245416</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D42" s="1">
+        <f>SUM(D31:D40)</f>
+        <v>24178684</v>
+      </c>
+      <c r="F42" s="16">
+        <f>100*D42/D22</f>
+        <v>50.13699258467112</v>
       </c>
     </row>
   </sheetData>
@@ -1577,7 +2331,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4D8DB8B-3990-447D-A504-5F100C779FB0}">
-  <dimension ref="A3:N40"/>
+  <dimension ref="A3:N55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -1594,76 +2348,76 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9" t="s">
+      <c r="A3" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9" t="s">
+      <c r="B3" s="20"/>
+      <c r="C3" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="N3" s="19"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="N3" s="9"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="F4" s="10" t="s">
+      <c r="E4" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="H4" s="10" t="s">
+      <c r="G4" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="J4" s="10" t="s">
+      <c r="I4" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="K4" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="L4" s="10" t="s">
+      <c r="K4" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L4" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="M4" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="N4" s="10" t="s">
+      <c r="M4" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="N4" s="8" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2241,7 +2995,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B18" s="1">
         <v>100000</v>
@@ -2285,7 +3039,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C19" s="1">
         <v>615513</v>
@@ -2324,352 +3078,693 @@
         <v>83392561</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>47</v>
+    <row r="21" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A21" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>49</v>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B28" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>53</v>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
-        <v>2500</v>
-      </c>
-      <c r="B32" s="1">
-        <v>5000</v>
-      </c>
-      <c r="C32" s="1">
-        <v>4300</v>
-      </c>
-      <c r="D32" s="1">
-        <v>14506569</v>
-      </c>
-      <c r="E32" s="1">
-        <v>428</v>
-      </c>
-      <c r="F32" s="1">
-        <v>1551432</v>
-      </c>
-      <c r="G32" s="1">
-        <v>3871</v>
-      </c>
-      <c r="H32" s="1">
-        <v>12955137</v>
-      </c>
-      <c r="I32" s="1">
-        <v>2466</v>
-      </c>
-      <c r="J32" s="1">
-        <v>8289401</v>
-      </c>
-      <c r="K32" s="1">
-        <v>279</v>
-      </c>
-      <c r="L32" s="1">
-        <v>1011440</v>
-      </c>
-      <c r="M32" s="1">
-        <v>2187</v>
-      </c>
-      <c r="N32" s="1">
-        <v>7277961</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
-        <v>5000</v>
-      </c>
-      <c r="B33" s="1">
-        <v>10000</v>
-      </c>
-      <c r="C33" s="1">
-        <v>1280</v>
-      </c>
-      <c r="D33" s="1">
-        <v>8557326</v>
-      </c>
-      <c r="E33" s="1">
-        <v>378</v>
-      </c>
-      <c r="F33" s="1">
-        <v>2688102</v>
-      </c>
-      <c r="G33" s="1">
-        <v>902</v>
-      </c>
-      <c r="H33" s="1">
-        <v>5869224</v>
-      </c>
-      <c r="I33" s="1">
-        <v>721</v>
-      </c>
-      <c r="J33" s="1">
-        <v>4861267</v>
-      </c>
-      <c r="K33" s="1">
-        <v>243</v>
-      </c>
-      <c r="L33" s="1">
-        <v>1727240</v>
-      </c>
-      <c r="M33" s="1">
-        <v>478</v>
-      </c>
-      <c r="N33" s="1">
-        <v>3134027</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
-        <v>10000</v>
-      </c>
-      <c r="B34" s="1">
-        <v>20000</v>
-      </c>
-      <c r="C34" s="1">
-        <v>421</v>
-      </c>
-      <c r="D34" s="1">
-        <v>5620665</v>
-      </c>
-      <c r="E34" s="1">
-        <v>253</v>
-      </c>
-      <c r="F34" s="1">
-        <v>3522846</v>
-      </c>
-      <c r="G34" s="1">
-        <v>168</v>
-      </c>
-      <c r="H34" s="1">
-        <v>2097819</v>
-      </c>
-      <c r="I34" s="1">
-        <v>292</v>
-      </c>
-      <c r="J34" s="1">
-        <v>3907710</v>
-      </c>
-      <c r="K34" s="1">
-        <v>161</v>
-      </c>
-      <c r="L34" s="1">
-        <v>2276487</v>
-      </c>
-      <c r="M34" s="1">
-        <v>131</v>
-      </c>
-      <c r="N34" s="1">
-        <v>1631223</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
-        <v>20000</v>
-      </c>
-      <c r="B35" s="1">
-        <v>50000</v>
-      </c>
-      <c r="C35" s="1">
-        <v>140</v>
-      </c>
-      <c r="D35" s="1">
-        <v>4093873</v>
-      </c>
-      <c r="E35" s="1">
-        <v>135</v>
-      </c>
-      <c r="F35" s="1">
-        <v>3982819</v>
-      </c>
-      <c r="G35" s="1">
-        <v>5</v>
-      </c>
-      <c r="H35" s="1">
-        <v>111054</v>
-      </c>
-      <c r="I35" s="1">
-        <v>93</v>
-      </c>
-      <c r="J35" s="1">
-        <v>2670393</v>
-      </c>
-      <c r="K35" s="1">
-        <v>90</v>
-      </c>
-      <c r="L35" s="1">
-        <v>2605731</v>
-      </c>
-      <c r="M35" s="1">
-        <v>3</v>
-      </c>
-      <c r="N35" s="1">
-        <v>64662</v>
+      <c r="B32" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
+        <v>2500</v>
+      </c>
+      <c r="B36" s="1">
+        <v>5000</v>
+      </c>
+      <c r="C36" s="1">
+        <v>4300</v>
+      </c>
+      <c r="D36" s="1">
+        <v>14506569</v>
+      </c>
+      <c r="E36" s="1">
+        <v>428</v>
+      </c>
+      <c r="F36" s="1">
+        <v>1551432</v>
+      </c>
+      <c r="G36" s="1">
+        <v>3871</v>
+      </c>
+      <c r="H36" s="1">
+        <v>12955137</v>
+      </c>
+      <c r="I36" s="1">
+        <v>2466</v>
+      </c>
+      <c r="J36" s="1">
+        <v>8289401</v>
+      </c>
+      <c r="K36" s="1">
+        <v>279</v>
+      </c>
+      <c r="L36" s="1">
+        <v>1011440</v>
+      </c>
+      <c r="M36" s="1">
+        <v>2187</v>
+      </c>
+      <c r="N36" s="1">
+        <v>7277961</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>5000</v>
+      </c>
+      <c r="B37" s="1">
+        <v>10000</v>
+      </c>
+      <c r="C37" s="1">
+        <v>1280</v>
+      </c>
+      <c r="D37" s="1">
+        <v>8557326</v>
+      </c>
+      <c r="E37" s="1">
+        <v>378</v>
+      </c>
+      <c r="F37" s="1">
+        <v>2688102</v>
+      </c>
+      <c r="G37" s="1">
+        <v>902</v>
+      </c>
+      <c r="H37" s="1">
+        <v>5869224</v>
+      </c>
+      <c r="I37" s="1">
+        <v>721</v>
+      </c>
+      <c r="J37" s="1">
+        <v>4861267</v>
+      </c>
+      <c r="K37" s="1">
+        <v>243</v>
+      </c>
+      <c r="L37" s="1">
+        <v>1727240</v>
+      </c>
+      <c r="M37" s="1">
+        <v>478</v>
+      </c>
+      <c r="N37" s="1">
+        <v>3134027</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>10000</v>
+      </c>
+      <c r="B38" s="1">
+        <v>20000</v>
+      </c>
+      <c r="C38" s="1">
+        <v>421</v>
+      </c>
+      <c r="D38" s="1">
+        <v>5620665</v>
+      </c>
+      <c r="E38" s="1">
+        <v>253</v>
+      </c>
+      <c r="F38" s="1">
+        <v>3522846</v>
+      </c>
+      <c r="G38" s="1">
+        <v>168</v>
+      </c>
+      <c r="H38" s="1">
+        <v>2097819</v>
+      </c>
+      <c r="I38" s="1">
+        <v>292</v>
+      </c>
+      <c r="J38" s="1">
+        <v>3907710</v>
+      </c>
+      <c r="K38" s="1">
+        <v>161</v>
+      </c>
+      <c r="L38" s="1">
+        <v>2276487</v>
+      </c>
+      <c r="M38" s="1">
+        <v>131</v>
+      </c>
+      <c r="N38" s="1">
+        <v>1631223</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>20000</v>
+      </c>
+      <c r="B39" s="1">
         <v>50000</v>
       </c>
-      <c r="B36" s="1">
+      <c r="C39" s="1">
+        <v>140</v>
+      </c>
+      <c r="D39" s="1">
+        <v>4093873</v>
+      </c>
+      <c r="E39" s="1">
+        <v>135</v>
+      </c>
+      <c r="F39" s="1">
+        <v>3982819</v>
+      </c>
+      <c r="G39" s="1">
+        <v>5</v>
+      </c>
+      <c r="H39" s="1">
+        <v>111054</v>
+      </c>
+      <c r="I39" s="1">
+        <v>93</v>
+      </c>
+      <c r="J39" s="1">
+        <v>2670393</v>
+      </c>
+      <c r="K39" s="1">
+        <v>90</v>
+      </c>
+      <c r="L39" s="1">
+        <v>2605731</v>
+      </c>
+      <c r="M39" s="1">
+        <v>3</v>
+      </c>
+      <c r="N39" s="1">
+        <v>64662</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>50000</v>
+      </c>
+      <c r="B40" s="1">
         <v>100000</v>
       </c>
-      <c r="C36" s="1">
+      <c r="C40" s="1">
         <v>60</v>
       </c>
-      <c r="D36" s="1">
+      <c r="D40" s="1">
         <v>4108692</v>
       </c>
-      <c r="E36" s="1">
+      <c r="E40" s="1">
         <v>60</v>
       </c>
-      <c r="F36" s="1">
+      <c r="F40" s="1">
         <v>4108692</v>
       </c>
-      <c r="G36" s="1">
+      <c r="G40" s="1">
         <v>0</v>
       </c>
-      <c r="H36" s="1">
+      <c r="H40" s="1">
         <v>0</v>
       </c>
-      <c r="I36" s="1">
+      <c r="I40" s="1">
         <v>40</v>
       </c>
-      <c r="J36" s="1">
+      <c r="J40" s="1">
         <v>2786535</v>
       </c>
-      <c r="K36" s="1">
+      <c r="K40" s="1">
         <v>40</v>
       </c>
-      <c r="L36" s="1">
+      <c r="L40" s="1">
         <v>2786535</v>
       </c>
-      <c r="M36" s="1">
+      <c r="M40" s="1">
         <v>0</v>
       </c>
-      <c r="N36" s="1">
+      <c r="N40" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>44</v>
-      </c>
-      <c r="B37" s="1">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="1">
         <v>100000</v>
       </c>
-      <c r="C37" s="1">
+      <c r="C41" s="1">
         <v>32</v>
       </c>
-      <c r="D37" s="1">
+      <c r="D41" s="1">
         <v>9550941</v>
       </c>
-      <c r="E37" s="1">
+      <c r="E41" s="1">
         <v>32</v>
       </c>
-      <c r="F37" s="1">
+      <c r="F41" s="1">
         <v>9550941</v>
       </c>
-      <c r="G37" s="1">
+      <c r="G41" s="1">
         <v>0</v>
       </c>
-      <c r="H37" s="1">
+      <c r="H41" s="1">
         <v>0</v>
       </c>
-      <c r="I37" s="1">
+      <c r="I41" s="1">
         <v>20</v>
       </c>
-      <c r="J37" s="1">
+      <c r="J41" s="1">
         <v>6447410</v>
       </c>
-      <c r="K37" s="1">
+      <c r="K41" s="1">
         <v>20</v>
       </c>
-      <c r="L37" s="1">
+      <c r="L41" s="1">
         <v>6447410</v>
       </c>
-      <c r="M37" s="1">
+      <c r="M41" s="1">
         <v>0</v>
       </c>
-      <c r="N37" s="1">
+      <c r="N41" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>39</v>
-      </c>
-      <c r="D39" s="1">
-        <f>SUM(D32:D37)</f>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>35</v>
+      </c>
+      <c r="D43" s="1">
+        <f>SUM(D36:D41)</f>
         <v>46438066</v>
       </c>
-      <c r="J39" s="1">
-        <f>SUM(J32:J37)</f>
+      <c r="J43" s="1">
+        <f>SUM(J36:J41)</f>
         <v>28962716</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>56</v>
-      </c>
-      <c r="D40" s="3">
-        <f>100*D39/D19</f>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>52</v>
+      </c>
+      <c r="D44" s="3">
+        <f>100*D43/D19</f>
         <v>31.595930010739593</v>
       </c>
-      <c r="J40" s="3">
-        <f>100*J39/J19</f>
+      <c r="J44" s="3">
+        <f>100*J43/J19</f>
         <v>28.722572032524745</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A46" s="14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>2000</v>
+      </c>
+      <c r="B48" s="1">
+        <v>5000</v>
+      </c>
+      <c r="C48" s="1">
+        <v>7219</v>
+      </c>
+      <c r="D48" s="1">
+        <v>20999532</v>
+      </c>
+      <c r="E48" s="1">
+        <v>559</v>
+      </c>
+      <c r="F48" s="1">
+        <v>1844645</v>
+      </c>
+      <c r="G48" s="1">
+        <v>6660</v>
+      </c>
+      <c r="H48" s="1">
+        <v>19154887</v>
+      </c>
+      <c r="I48" s="1">
+        <v>4218</v>
+      </c>
+      <c r="J48" s="1">
+        <v>12184306</v>
+      </c>
+      <c r="K48" s="1">
+        <v>362</v>
+      </c>
+      <c r="L48" s="1">
+        <v>1198303</v>
+      </c>
+      <c r="M48" s="1">
+        <v>3856</v>
+      </c>
+      <c r="N48" s="1">
+        <v>10986003</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>5000</v>
+      </c>
+      <c r="B49" s="1">
+        <v>10000</v>
+      </c>
+      <c r="C49" s="1">
+        <v>1280</v>
+      </c>
+      <c r="D49" s="1">
+        <v>8557326</v>
+      </c>
+      <c r="E49" s="1">
+        <v>378</v>
+      </c>
+      <c r="F49" s="1">
+        <v>2688102</v>
+      </c>
+      <c r="G49" s="1">
+        <v>902</v>
+      </c>
+      <c r="H49" s="1">
+        <v>5869224</v>
+      </c>
+      <c r="I49" s="1">
+        <v>721</v>
+      </c>
+      <c r="J49" s="1">
+        <v>4861267</v>
+      </c>
+      <c r="K49" s="1">
+        <v>243</v>
+      </c>
+      <c r="L49" s="1">
+        <v>1727240</v>
+      </c>
+      <c r="M49" s="1">
+        <v>478</v>
+      </c>
+      <c r="N49" s="1">
+        <v>3134027</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>10000</v>
+      </c>
+      <c r="B50" s="1">
+        <v>20000</v>
+      </c>
+      <c r="C50" s="1">
+        <v>421</v>
+      </c>
+      <c r="D50" s="1">
+        <v>5620665</v>
+      </c>
+      <c r="E50" s="1">
+        <v>253</v>
+      </c>
+      <c r="F50" s="1">
+        <v>3522846</v>
+      </c>
+      <c r="G50" s="1">
+        <v>168</v>
+      </c>
+      <c r="H50" s="1">
+        <v>2097819</v>
+      </c>
+      <c r="I50" s="1">
+        <v>292</v>
+      </c>
+      <c r="J50" s="1">
+        <v>3907710</v>
+      </c>
+      <c r="K50" s="1">
+        <v>161</v>
+      </c>
+      <c r="L50" s="1">
+        <v>2276487</v>
+      </c>
+      <c r="M50" s="1">
+        <v>131</v>
+      </c>
+      <c r="N50" s="1">
+        <v>1631223</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>20000</v>
+      </c>
+      <c r="B51" s="1">
+        <v>50000</v>
+      </c>
+      <c r="C51" s="1">
+        <v>140</v>
+      </c>
+      <c r="D51" s="1">
+        <v>4093873</v>
+      </c>
+      <c r="E51" s="1">
+        <v>135</v>
+      </c>
+      <c r="F51" s="1">
+        <v>3982819</v>
+      </c>
+      <c r="G51" s="1">
+        <v>5</v>
+      </c>
+      <c r="H51" s="1">
+        <v>111054</v>
+      </c>
+      <c r="I51" s="1">
+        <v>93</v>
+      </c>
+      <c r="J51" s="1">
+        <v>2670393</v>
+      </c>
+      <c r="K51" s="1">
+        <v>90</v>
+      </c>
+      <c r="L51" s="1">
+        <v>2605731</v>
+      </c>
+      <c r="M51" s="1">
+        <v>3</v>
+      </c>
+      <c r="N51" s="1">
+        <v>64662</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>50000</v>
+      </c>
+      <c r="B52" s="1">
+        <v>100000</v>
+      </c>
+      <c r="C52" s="1">
+        <v>60</v>
+      </c>
+      <c r="D52" s="1">
+        <v>4108692</v>
+      </c>
+      <c r="E52" s="1">
+        <v>60</v>
+      </c>
+      <c r="F52" s="1">
+        <v>4108692</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0</v>
+      </c>
+      <c r="H52" s="1">
+        <v>0</v>
+      </c>
+      <c r="I52" s="1">
+        <v>40</v>
+      </c>
+      <c r="J52" s="1">
+        <v>2786535</v>
+      </c>
+      <c r="K52" s="1">
+        <v>40</v>
+      </c>
+      <c r="L52" s="1">
+        <v>2786535</v>
+      </c>
+      <c r="M52" s="1">
+        <v>0</v>
+      </c>
+      <c r="N52" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>40</v>
+      </c>
+      <c r="B53" s="1">
+        <v>100000</v>
+      </c>
+      <c r="C53" s="1">
+        <v>32</v>
+      </c>
+      <c r="D53" s="1">
+        <v>9550941</v>
+      </c>
+      <c r="E53" s="1">
+        <v>32</v>
+      </c>
+      <c r="F53" s="1">
+        <v>9550941</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0</v>
+      </c>
+      <c r="H53" s="1">
+        <v>0</v>
+      </c>
+      <c r="I53" s="1">
+        <v>20</v>
+      </c>
+      <c r="J53" s="1">
+        <v>6447410</v>
+      </c>
+      <c r="K53" s="1">
+        <v>20</v>
+      </c>
+      <c r="L53" s="1">
+        <v>6447410</v>
+      </c>
+      <c r="M53" s="1">
+        <v>0</v>
+      </c>
+      <c r="N53" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>35</v>
+      </c>
+      <c r="C54" s="1">
+        <f>SUM(C48:C53)</f>
+        <v>9152</v>
+      </c>
+      <c r="D54" s="1">
+        <f t="shared" ref="D54:N54" si="0">SUM(D48:D53)</f>
+        <v>52931029</v>
+      </c>
+      <c r="E54" s="1">
+        <f t="shared" si="0"/>
+        <v>1417</v>
+      </c>
+      <c r="F54" s="1">
+        <f t="shared" si="0"/>
+        <v>25698045</v>
+      </c>
+      <c r="G54" s="1">
+        <f t="shared" si="0"/>
+        <v>7735</v>
+      </c>
+      <c r="H54" s="1">
+        <f t="shared" si="0"/>
+        <v>27232984</v>
+      </c>
+      <c r="I54" s="1">
+        <f t="shared" si="0"/>
+        <v>5384</v>
+      </c>
+      <c r="J54" s="1">
+        <f t="shared" si="0"/>
+        <v>32857621</v>
+      </c>
+      <c r="K54" s="1">
+        <f t="shared" si="0"/>
+        <v>916</v>
+      </c>
+      <c r="L54" s="1">
+        <f t="shared" si="0"/>
+        <v>17041706</v>
+      </c>
+      <c r="M54" s="1">
+        <f t="shared" si="0"/>
+        <v>4468</v>
+      </c>
+      <c r="N54" s="1">
+        <f t="shared" si="0"/>
+        <v>15815915</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>52</v>
+      </c>
+      <c r="D55" s="16">
+        <f>100*D54/D19</f>
+        <v>36.013667918048689</v>
+      </c>
+      <c r="J55" s="16">
+        <f>100*J54/J19</f>
+        <v>32.585182480465498</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3049,7 +4144,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -3140,52 +4235,53 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ED326E9-8D2E-42C0-8EF9-E316006CB136}">
-  <dimension ref="A3:N40"/>
+  <dimension ref="A3:N62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="11.28515625" customWidth="1"/>
     <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="I3" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="J3" s="8"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
+      <c r="I3" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J3" s="20"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C4" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" s="8"/>
-      <c r="G4" s="11" t="s">
+      <c r="C4" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="20"/>
+      <c r="G4" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="I4" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="J4" s="11" t="s">
+      <c r="I4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="N4" s="11"/>
+      <c r="N4" s="9"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="11" t="s">
+      <c r="C5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>4</v>
       </c>
       <c r="G5">
@@ -3388,49 +4484,54 @@
         <v>47.875927234383163</v>
       </c>
     </row>
+    <row r="18" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A18" s="14" t="s">
+        <v>65</v>
+      </c>
+    </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C24" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="D24" s="8"/>
-      <c r="I24" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="J24" s="8"/>
+      <c r="C24" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="20"/>
+      <c r="I24" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J24" s="20"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C25" s="11" t="s">
-        <v>40</v>
+      <c r="C25" s="9" t="s">
+        <v>36</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G25" s="11" t="s">
+      <c r="G25" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="H25" s="11" t="s">
+      <c r="H25" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="I25" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="J25" s="11" t="s">
+      <c r="I25" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="J25" s="9" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3606,7 +4707,7 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D38" s="1">
         <f>SUM(D26:D33)</f>
@@ -3619,7 +4720,7 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D39" s="1">
         <f>D38+J38</f>
@@ -3628,19 +4729,277 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D40" s="3">
         <f>100*D39/D35</f>
         <v>54.468462238895277</v>
       </c>
     </row>
+    <row r="42" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A42" s="14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C44" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D44" s="20"/>
+      <c r="I44" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J44" s="20"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="J45" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>2000</v>
+      </c>
+      <c r="B46" s="1">
+        <v>3000</v>
+      </c>
+      <c r="C46">
+        <v>433</v>
+      </c>
+      <c r="D46" s="1">
+        <v>1089026</v>
+      </c>
+      <c r="J46" s="1"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>3000</v>
+      </c>
+      <c r="B47" s="1">
+        <v>5000</v>
+      </c>
+      <c r="C47">
+        <v>904</v>
+      </c>
+      <c r="D47" s="1">
+        <v>3596828</v>
+      </c>
+      <c r="G47">
+        <v>2000</v>
+      </c>
+      <c r="H47">
+        <v>3000</v>
+      </c>
+      <c r="I47">
+        <v>3482</v>
+      </c>
+      <c r="J47" s="1">
+        <v>8389199</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>5000</v>
+      </c>
+      <c r="B48" s="1">
+        <v>10000</v>
+      </c>
+      <c r="C48">
+        <v>1296</v>
+      </c>
+      <c r="D48" s="1">
+        <v>9213576</v>
+      </c>
+      <c r="G48" s="1">
+        <v>3000</v>
+      </c>
+      <c r="H48" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I48" s="1">
+        <v>1807</v>
+      </c>
+      <c r="J48" s="1">
+        <v>6732200</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>10000</v>
+      </c>
+      <c r="B49" s="1">
+        <v>20000</v>
+      </c>
+      <c r="C49">
+        <v>798</v>
+      </c>
+      <c r="D49" s="1">
+        <v>11150064</v>
+      </c>
+      <c r="G49" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H49" t="s">
+        <v>3</v>
+      </c>
+      <c r="I49">
+        <v>675</v>
+      </c>
+      <c r="J49" s="1">
+        <v>4973200</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>20000</v>
+      </c>
+      <c r="B50" s="1">
+        <v>50000</v>
+      </c>
+      <c r="C50">
+        <v>474</v>
+      </c>
+      <c r="D50" s="1">
+        <v>14828309</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>50000</v>
+      </c>
+      <c r="B51" s="1">
+        <v>100000</v>
+      </c>
+      <c r="C51">
+        <v>156</v>
+      </c>
+      <c r="D51" s="1">
+        <v>10989803</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>100000</v>
+      </c>
+      <c r="B52" s="1">
+        <v>500000</v>
+      </c>
+      <c r="C52">
+        <v>123</v>
+      </c>
+      <c r="D52" s="1">
+        <v>24425829</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>500000</v>
+      </c>
+      <c r="B53" t="s">
+        <v>3</v>
+      </c>
+      <c r="C53">
+        <v>25</v>
+      </c>
+      <c r="D53" s="1">
+        <v>24162753</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D54" s="1">
+        <v>208826650</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D56" s="1">
+        <f>SUM(D46:D53)</f>
+        <v>99456188</v>
+      </c>
+      <c r="J56" s="1">
+        <f>SUM(J46:J52)</f>
+        <v>20094599</v>
+      </c>
+      <c r="L56" s="1">
+        <f>D56+J56</f>
+        <v>119550787</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D57" s="3"/>
+      <c r="L57" s="16">
+        <f>100*L56/D54</f>
+        <v>57.248817140915683</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A59" s="14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>74</v>
+      </c>
+      <c r="D61" s="1">
+        <f>SUM(D48:D53)</f>
+        <v>94770334</v>
+      </c>
+      <c r="J61" s="1">
+        <f>J49</f>
+        <v>4973200</v>
+      </c>
+      <c r="L61" s="1">
+        <f>J61+D61</f>
+        <v>99743534</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>75</v>
+      </c>
+      <c r="L62" s="16">
+        <f>100*L61/D54</f>
+        <v>47.763795473422576</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="C44:D44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3649,26 +5008,27 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{788ECCEF-9F8C-4056-9EBF-C43E8745BF26}">
-  <dimension ref="A2:J39"/>
+  <dimension ref="A2:L62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="13.42578125" customWidth="1"/>
     <col min="10" max="10" width="10.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C3" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="D3" s="8"/>
-      <c r="I3" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="J3" s="8"/>
+      <c r="C3" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="20"/>
+      <c r="I3" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J3" s="20"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -3678,21 +5038,21 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="I4" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="J4" s="11" t="s">
+      <c r="I4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="9" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3718,7 +5078,7 @@
       <c r="I5" s="5">
         <v>16677</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="11">
         <v>22785371</v>
       </c>
     </row>
@@ -3744,7 +5104,7 @@
       <c r="I6" s="5">
         <v>3911</v>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="11">
         <v>9424188</v>
       </c>
     </row>
@@ -3770,7 +5130,7 @@
       <c r="I7" s="5">
         <v>2040</v>
       </c>
-      <c r="J7" s="13">
+      <c r="J7" s="11">
         <v>7656431</v>
       </c>
     </row>
@@ -3796,7 +5156,7 @@
       <c r="I8" s="5">
         <v>868</v>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="11">
         <v>6446727</v>
       </c>
     </row>
@@ -3830,7 +5190,7 @@
         <v>13054945</v>
       </c>
       <c r="G10" s="1"/>
-      <c r="H10" s="12"/>
+      <c r="H10" s="10"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
     </row>
@@ -3892,25 +5252,30 @@
         <v>56.259903446851474</v>
       </c>
     </row>
+    <row r="17" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A17" s="14" t="s">
+        <v>65</v>
+      </c>
+    </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C23" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="D23" s="8"/>
-      <c r="I23" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="J23" s="8"/>
+      <c r="C23" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="20"/>
+      <c r="I23" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J23" s="20"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
@@ -3919,22 +5284,22 @@
       <c r="B24" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D24" s="11" t="s">
+      <c r="C24" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D24" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G24" s="11" t="s">
+      <c r="G24" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="H24" s="11" t="s">
+      <c r="H24" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="I24" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="J24" s="11" t="s">
+      <c r="I24" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="J24" s="9" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3954,7 +5319,7 @@
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="5"/>
-      <c r="J25" s="13"/>
+      <c r="J25" s="11"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
@@ -3978,7 +5343,7 @@
       <c r="I26" s="5">
         <v>1249</v>
       </c>
-      <c r="J26" s="13">
+      <c r="J26" s="11">
         <v>3434409</v>
       </c>
     </row>
@@ -4004,7 +5369,7 @@
       <c r="I27" s="5">
         <v>2040</v>
       </c>
-      <c r="J27" s="13">
+      <c r="J27" s="11">
         <v>7656431</v>
       </c>
     </row>
@@ -4030,7 +5395,7 @@
       <c r="I28" s="5">
         <v>868</v>
       </c>
-      <c r="J28" s="13">
+      <c r="J28" s="11">
         <v>6446727</v>
       </c>
     </row>
@@ -4109,7 +5474,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D37" s="1">
         <f>SUM(D25:D32)</f>
@@ -4122,7 +5487,7 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D38" s="1">
         <f>D37+J37</f>
@@ -4131,19 +5496,282 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D39" s="3">
         <f>100*D38/D34</f>
         <v>62.973088538830616</v>
       </c>
     </row>
+    <row r="41" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A41" s="14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C44" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D44" s="20"/>
+      <c r="I44" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J44" s="20"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="J45" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>2000</v>
+      </c>
+      <c r="B46" s="1">
+        <v>3000</v>
+      </c>
+      <c r="C46">
+        <v>536</v>
+      </c>
+      <c r="D46" s="1">
+        <v>1341238</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="11"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>3000</v>
+      </c>
+      <c r="B47" s="1">
+        <v>5000</v>
+      </c>
+      <c r="C47">
+        <v>1028</v>
+      </c>
+      <c r="D47" s="1">
+        <v>4098169</v>
+      </c>
+      <c r="G47" s="4">
+        <v>2000</v>
+      </c>
+      <c r="H47" s="4">
+        <v>3000</v>
+      </c>
+      <c r="I47" s="5">
+        <v>3911</v>
+      </c>
+      <c r="J47" s="11">
+        <v>9424188</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>5000</v>
+      </c>
+      <c r="B48" s="1">
+        <v>10000</v>
+      </c>
+      <c r="C48">
+        <v>1430</v>
+      </c>
+      <c r="D48" s="1">
+        <v>10069839</v>
+      </c>
+      <c r="G48" s="5">
+        <v>3000</v>
+      </c>
+      <c r="H48" s="5">
+        <v>5000</v>
+      </c>
+      <c r="I48" s="5">
+        <v>2040</v>
+      </c>
+      <c r="J48" s="11">
+        <v>7656431</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>10000</v>
+      </c>
+      <c r="B49" s="1">
+        <v>20000</v>
+      </c>
+      <c r="C49">
+        <v>919</v>
+      </c>
+      <c r="D49" s="1">
+        <v>12721674</v>
+      </c>
+      <c r="G49" s="5">
+        <v>5000</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I49" s="5">
+        <v>868</v>
+      </c>
+      <c r="J49" s="11">
+        <v>6446727</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>20000</v>
+      </c>
+      <c r="B50" s="1">
+        <v>50000</v>
+      </c>
+      <c r="C50">
+        <v>600</v>
+      </c>
+      <c r="D50" s="1">
+        <v>18468944</v>
+      </c>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>50000</v>
+      </c>
+      <c r="B51" s="1">
+        <v>100000</v>
+      </c>
+      <c r="C51">
+        <v>189</v>
+      </c>
+      <c r="D51" s="1">
+        <v>13054945</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>100000</v>
+      </c>
+      <c r="B52" s="1">
+        <v>500000</v>
+      </c>
+      <c r="C52">
+        <v>188</v>
+      </c>
+      <c r="D52" s="1">
+        <v>38239651</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>500000</v>
+      </c>
+      <c r="B53" t="s">
+        <v>3</v>
+      </c>
+      <c r="C53">
+        <v>33</v>
+      </c>
+      <c r="D53" s="1">
+        <v>37286597</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D54" s="1">
+        <v>241720134</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D56" s="1">
+        <f>SUM(D46:D53)</f>
+        <v>135281057</v>
+      </c>
+      <c r="J56" s="1">
+        <f>SUM(J46:J53)</f>
+        <v>23527346</v>
+      </c>
+      <c r="L56" s="1">
+        <f>D56+J56</f>
+        <v>158808403</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D57" s="3"/>
+      <c r="L57" s="17">
+        <f>100*L56/D54</f>
+        <v>65.699286349063499</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A59" s="14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>74</v>
+      </c>
+      <c r="D61" s="1">
+        <f>SUM(D48:D53)</f>
+        <v>129841650</v>
+      </c>
+      <c r="J61" s="1">
+        <f>J49</f>
+        <v>6446727</v>
+      </c>
+      <c r="L61" s="1">
+        <f>J61+D61</f>
+        <v>136288377</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>75</v>
+      </c>
+      <c r="L62" s="16">
+        <f>100*L61/D54</f>
+        <v>56.382716137332608</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="C23:D23"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="C44:D44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4515,7 +6143,7 @@
         <v>389605</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -4672,7 +6300,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -4687,10 +6315,10 @@
         <v>4</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -4812,47 +6440,48 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64A02521-C453-4789-9567-9D014E4404BA}">
-  <dimension ref="A2:J39"/>
+  <dimension ref="A2:L62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="I2" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="J2" s="8"/>
+      <c r="I2" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J2" s="20"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C3" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="D3" s="8"/>
-      <c r="G3" s="11" t="s">
+      <c r="C3" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="20"/>
+      <c r="G3" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="J3" s="11" t="s">
+      <c r="I3" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" s="9" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="11" t="s">
+      <c r="C4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>4</v>
       </c>
       <c r="G4">
@@ -5046,49 +6675,54 @@
         <v>52.419647827955608</v>
       </c>
     </row>
+    <row r="17" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A17" s="14" t="s">
+        <v>65</v>
+      </c>
+    </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C23" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="D23" s="8"/>
-      <c r="I23" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="J23" s="8"/>
+      <c r="C23" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="20"/>
+      <c r="I23" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J23" s="20"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D24" s="11" t="s">
+      <c r="C24" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D24" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G24" s="11" t="s">
+      <c r="G24" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="H24" s="11" t="s">
+      <c r="H24" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="I24" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="J24" s="11" t="s">
+      <c r="I24" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="J24" s="9" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5260,7 +6894,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D37" s="1">
         <f>SUM(D25:D32)</f>
@@ -5273,7 +6907,7 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D38" s="1">
         <f>D37+J37</f>
@@ -5282,19 +6916,277 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D39" s="3">
         <f>100*D38/D34</f>
         <v>58.359856013114126</v>
       </c>
     </row>
+    <row r="41" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A41" s="14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C44" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D44" s="20"/>
+      <c r="I44" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J44" s="20"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="J45" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>2000</v>
+      </c>
+      <c r="B46" s="1">
+        <v>3000</v>
+      </c>
+      <c r="C46">
+        <v>172</v>
+      </c>
+      <c r="D46" s="1">
+        <v>436629</v>
+      </c>
+      <c r="J46" s="1"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>3000</v>
+      </c>
+      <c r="B47" s="1">
+        <v>5000</v>
+      </c>
+      <c r="C47">
+        <v>443</v>
+      </c>
+      <c r="D47" s="1">
+        <v>1763827</v>
+      </c>
+      <c r="G47">
+        <v>2000</v>
+      </c>
+      <c r="H47">
+        <v>3000</v>
+      </c>
+      <c r="I47">
+        <v>1450</v>
+      </c>
+      <c r="J47" s="1">
+        <v>3500966</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>5000</v>
+      </c>
+      <c r="B48" s="1">
+        <v>10000</v>
+      </c>
+      <c r="C48">
+        <v>654</v>
+      </c>
+      <c r="D48" s="1">
+        <v>4660310</v>
+      </c>
+      <c r="G48" s="1">
+        <v>3000</v>
+      </c>
+      <c r="H48" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I48" s="1">
+        <v>833</v>
+      </c>
+      <c r="J48" s="1">
+        <v>3125682</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>10000</v>
+      </c>
+      <c r="B49" s="1">
+        <v>20000</v>
+      </c>
+      <c r="C49">
+        <v>459</v>
+      </c>
+      <c r="D49" s="1">
+        <v>6417782</v>
+      </c>
+      <c r="G49" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H49" t="s">
+        <v>3</v>
+      </c>
+      <c r="I49">
+        <v>372</v>
+      </c>
+      <c r="J49" s="1">
+        <v>2900584</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>20000</v>
+      </c>
+      <c r="B50" s="1">
+        <v>50000</v>
+      </c>
+      <c r="C50">
+        <v>311</v>
+      </c>
+      <c r="D50" s="1">
+        <v>9741418</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>50000</v>
+      </c>
+      <c r="B51" s="1">
+        <v>100000</v>
+      </c>
+      <c r="C51">
+        <v>97</v>
+      </c>
+      <c r="D51" s="1">
+        <v>6720976</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>100000</v>
+      </c>
+      <c r="B52" s="1">
+        <v>500000</v>
+      </c>
+      <c r="C52">
+        <v>78</v>
+      </c>
+      <c r="D52" s="1">
+        <v>15459194</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>500000</v>
+      </c>
+      <c r="B53" t="s">
+        <v>3</v>
+      </c>
+      <c r="C53">
+        <v>14</v>
+      </c>
+      <c r="D53" s="1">
+        <v>16225204</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D54" s="1">
+        <v>117534315</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>67</v>
+      </c>
+      <c r="D56" s="1">
+        <f>SUM(D46:D53)</f>
+        <v>61425340</v>
+      </c>
+      <c r="J56" s="1">
+        <f>SUM(J46:J53)</f>
+        <v>9527232</v>
+      </c>
+      <c r="L56" s="1">
+        <f>D56+J56</f>
+        <v>70952572</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D57" s="3"/>
+      <c r="L57" s="16">
+        <f>100*L56/D54</f>
+        <v>60.367537769714318</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A59" s="14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>74</v>
+      </c>
+      <c r="D61" s="1">
+        <f>SUM(D48:D53)</f>
+        <v>59224884</v>
+      </c>
+      <c r="J61" s="1">
+        <f>J49</f>
+        <v>2900584</v>
+      </c>
+      <c r="L61" s="1">
+        <f>D61+J61</f>
+        <v>62125468</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>75</v>
+      </c>
+      <c r="L62" s="16">
+        <f>100*L61/D54</f>
+        <v>52.85730214193191</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="I23:J23"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="C44:D44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5302,26 +7194,27 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F486153-DE52-4DDC-AC00-DEE976B14729}">
-  <dimension ref="A2:J39"/>
+  <dimension ref="A2:L62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="12.85546875" customWidth="1"/>
     <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C3" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="D3" s="8"/>
-      <c r="I3" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="J3" s="8"/>
+      <c r="C3" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="20"/>
+      <c r="I3" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J3" s="20"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -5330,22 +7223,22 @@
       <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>40</v>
+      <c r="C4" s="9" t="s">
+        <v>36</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="I4" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="J4" s="11" t="s">
+      <c r="I4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="9" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5371,7 +7264,7 @@
       <c r="I5" s="5">
         <v>6333</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="11">
         <v>8573108</v>
       </c>
     </row>
@@ -5397,7 +7290,7 @@
       <c r="I6" s="5">
         <v>1385</v>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="11">
         <v>3333563</v>
       </c>
     </row>
@@ -5423,7 +7316,7 @@
       <c r="I7" s="5">
         <v>846</v>
       </c>
-      <c r="J7" s="13">
+      <c r="J7" s="11">
         <v>3199082</v>
       </c>
     </row>
@@ -5443,13 +7336,13 @@
       <c r="G8" s="5">
         <v>5000</v>
       </c>
-      <c r="H8" s="14" t="s">
+      <c r="H8" s="12" t="s">
         <v>3</v>
       </c>
       <c r="I8" s="5">
         <v>434</v>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="11">
         <v>3401655</v>
       </c>
     </row>
@@ -5485,7 +7378,7 @@
         <v>7908160</v>
       </c>
       <c r="G10" s="1"/>
-      <c r="H10" s="12"/>
+      <c r="H10" s="10"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
     </row>
@@ -5547,25 +7440,30 @@
         <v>62.255254317734554</v>
       </c>
     </row>
+    <row r="17" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A17" s="14" t="s">
+        <v>65</v>
+      </c>
+    </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C23" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="D23" s="8"/>
-      <c r="I23" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="J23" s="8"/>
+      <c r="C23" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="20"/>
+      <c r="I23" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J23" s="20"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
@@ -5574,22 +7472,22 @@
       <c r="B24" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="11" t="s">
-        <v>40</v>
+      <c r="C24" s="9" t="s">
+        <v>36</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G24" s="11" t="s">
+      <c r="G24" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="H24" s="11" t="s">
+      <c r="H24" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="I24" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="J24" s="11" t="s">
+      <c r="I24" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="J24" s="9" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5609,7 +7507,7 @@
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="5"/>
-      <c r="J25" s="13"/>
+      <c r="J25" s="11"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
@@ -5633,7 +7531,7 @@
       <c r="I26" s="5">
         <v>435</v>
       </c>
-      <c r="J26" s="13">
+      <c r="J26" s="11">
         <v>1195222</v>
       </c>
     </row>
@@ -5659,7 +7557,7 @@
       <c r="I27" s="5">
         <v>846</v>
       </c>
-      <c r="J27" s="13">
+      <c r="J27" s="11">
         <v>3199082</v>
       </c>
     </row>
@@ -5679,13 +7577,13 @@
       <c r="G28" s="5">
         <v>5000</v>
       </c>
-      <c r="H28" s="14" t="s">
+      <c r="H28" s="12" t="s">
         <v>3</v>
       </c>
       <c r="I28" s="5">
         <v>434</v>
       </c>
-      <c r="J28" s="13">
+      <c r="J28" s="11">
         <v>3401655</v>
       </c>
     </row>
@@ -5768,7 +7666,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D37" s="1">
         <f>SUM(D25:D32)</f>
@@ -5781,7 +7679,7 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D38" s="1">
         <f>D37+J37</f>
@@ -5790,19 +7688,280 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D39" s="3">
         <f>100*D38/D34</f>
         <v>67.838945208846212</v>
       </c>
     </row>
+    <row r="41" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A41" s="14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C44" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D44" s="20"/>
+      <c r="I44" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J44" s="20"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="J45" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>2000</v>
+      </c>
+      <c r="B46" s="1">
+        <v>3000</v>
+      </c>
+      <c r="C46">
+        <v>236</v>
+      </c>
+      <c r="D46" s="1">
+        <v>593006</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="11"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>3000</v>
+      </c>
+      <c r="B47" s="1">
+        <v>5000</v>
+      </c>
+      <c r="C47">
+        <v>535</v>
+      </c>
+      <c r="D47" s="1">
+        <v>2137680</v>
+      </c>
+      <c r="G47" s="4">
+        <v>2000</v>
+      </c>
+      <c r="H47" s="4">
+        <v>3000</v>
+      </c>
+      <c r="I47" s="5">
+        <v>1385</v>
+      </c>
+      <c r="J47" s="11">
+        <v>3333563</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>5000</v>
+      </c>
+      <c r="B48" s="1">
+        <v>10000</v>
+      </c>
+      <c r="C48">
+        <v>761</v>
+      </c>
+      <c r="D48" s="1">
+        <v>5330060</v>
+      </c>
+      <c r="G48" s="5">
+        <v>3000</v>
+      </c>
+      <c r="H48" s="5">
+        <v>5000</v>
+      </c>
+      <c r="I48" s="5">
+        <v>846</v>
+      </c>
+      <c r="J48" s="11">
+        <v>3199082</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>10000</v>
+      </c>
+      <c r="B49" s="1">
+        <v>20000</v>
+      </c>
+      <c r="C49">
+        <v>476</v>
+      </c>
+      <c r="D49" s="1">
+        <v>6616796</v>
+      </c>
+      <c r="G49" s="5">
+        <v>5000</v>
+      </c>
+      <c r="H49" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="I49" s="5">
+        <v>434</v>
+      </c>
+      <c r="J49" s="11">
+        <v>3401655</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>20000</v>
+      </c>
+      <c r="B50" s="1">
+        <v>50000</v>
+      </c>
+      <c r="C50">
+        <v>368</v>
+      </c>
+      <c r="D50" s="1">
+        <v>11565985</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>50000</v>
+      </c>
+      <c r="B51" s="1">
+        <v>100000</v>
+      </c>
+      <c r="C51">
+        <v>114</v>
+      </c>
+      <c r="D51" s="1">
+        <v>7908160</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>100000</v>
+      </c>
+      <c r="B52" s="1">
+        <v>500000</v>
+      </c>
+      <c r="C52">
+        <v>107</v>
+      </c>
+      <c r="D52" s="1">
+        <v>23315401</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>500000</v>
+      </c>
+      <c r="B53" t="s">
+        <v>3</v>
+      </c>
+      <c r="C53">
+        <v>17</v>
+      </c>
+      <c r="D53" s="1">
+        <v>23231465</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D54" s="1">
+        <v>130079210</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>67</v>
+      </c>
+      <c r="D56" s="1">
+        <f>SUM(D46:D53)</f>
+        <v>80698553</v>
+      </c>
+      <c r="J56" s="1">
+        <f>SUM(J46:J52)</f>
+        <v>9934300</v>
+      </c>
+      <c r="L56" s="1">
+        <f>D56+J56</f>
+        <v>90632853</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D57" s="3"/>
+      <c r="L57" s="16">
+        <f>100*L56/D54</f>
+        <v>69.675125640753819</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A59" s="14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>74</v>
+      </c>
+      <c r="D61" s="1">
+        <f>SUM(D48:D53)</f>
+        <v>77967867</v>
+      </c>
+      <c r="J61" s="1">
+        <f>J49</f>
+        <v>3401655</v>
+      </c>
+      <c r="L61" s="1">
+        <f>D61+J61</f>
+        <v>81369522</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L62" s="16">
+        <f>100*L61/D54</f>
+        <v>62.553825472956056</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="C3:D3"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="C44:D44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/workbooks/urbanization.xlsx
+++ b/workbooks/urbanization.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68803F96-C190-40AA-AD0C-C42AF119A1F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87E9A5E8-B0CA-4784-89AA-38743A1131AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58035" yWindow="1140" windowWidth="27720" windowHeight="19005" firstSheet="5" xr2:uid="{9806A3BC-D491-4476-99E9-37D3951075C7}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" firstSheet="5" activeTab="9" xr2:uid="{9806A3BC-D491-4476-99E9-37D3951075C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -22,14 +22,14 @@
     <sheet name="RSFSR-1926" sheetId="4" r:id="rId7"/>
     <sheet name="RSFSR-1959" sheetId="6" r:id="rId8"/>
     <sheet name="RSFSR-1970" sheetId="8" r:id="rId9"/>
-    <sheet name="RSFSR-1979" sheetId="10" r:id="rId10"/>
-    <sheet name="RSFSR-1989" sheetId="20" r:id="rId11"/>
-    <sheet name="MX-1930" sheetId="13" r:id="rId12"/>
-    <sheet name="MX-1960" sheetId="14" r:id="rId13"/>
-    <sheet name="MX-1970" sheetId="15" r:id="rId14"/>
-    <sheet name="MX-1980" sheetId="22" r:id="rId15"/>
-    <sheet name="MX-1990" sheetId="21" r:id="rId16"/>
-    <sheet name="Итоги" sheetId="19" r:id="rId17"/>
+    <sheet name="Итоги" sheetId="19" r:id="rId10"/>
+    <sheet name="RSFSR-1979" sheetId="10" r:id="rId11"/>
+    <sheet name="RSFSR-1989" sheetId="20" r:id="rId12"/>
+    <sheet name="MX-1930" sheetId="13" r:id="rId13"/>
+    <sheet name="MX-1960" sheetId="14" r:id="rId14"/>
+    <sheet name="MX-1970" sheetId="15" r:id="rId15"/>
+    <sheet name="MX-1980" sheetId="22" r:id="rId16"/>
+    <sheet name="MX-1990" sheetId="21" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="119">
   <si>
     <t>от</t>
   </si>
@@ -421,7 +421,7 @@
     <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="_-[$€-2]* #,##0.00_-;\-[$€-2]* #,##0.00_-;_-[$€-2]* &quot;-&quot;??_-"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -456,14 +456,6 @@
       <b/>
       <sz val="14"/>
       <color theme="8" tint="-0.249977111117893"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -571,16 +563,16 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -608,34 +600,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma 2" xfId="5" xr:uid="{2A5730CF-2000-4C9F-A914-E035B50DA721}"/>
@@ -1151,6 +1141,942 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2920F376-2D53-4EC0-B932-712BB7C94480}">
+  <dimension ref="A1:M66"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="12.15625" customWidth="1"/>
+    <col min="3" max="3" width="11.15625" customWidth="1"/>
+    <col min="4" max="4" width="11.41796875" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="6" width="10.15625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="9.83984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="M1" s="16"/>
+    </row>
+    <row r="2" spans="1:13" ht="18.3" x14ac:dyDescent="0.7">
+      <c r="A2" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="M3" s="16"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="C4" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" s="16"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="14">
+        <v>1930</v>
+      </c>
+      <c r="C5" s="3">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="D5" s="3">
+        <v>36</v>
+      </c>
+      <c r="E5" s="3">
+        <v>32.6</v>
+      </c>
+      <c r="K5" s="3">
+        <f>E5-C5</f>
+        <v>-4.6000000000000014</v>
+      </c>
+      <c r="M5" s="16">
+        <f>E5/C5</f>
+        <v>0.87634408602150538</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="14">
+        <v>1960</v>
+      </c>
+      <c r="C6" s="3">
+        <v>53.8</v>
+      </c>
+      <c r="D6" s="3">
+        <v>57.2</v>
+      </c>
+      <c r="E6" s="3">
+        <v>60.4</v>
+      </c>
+      <c r="K6" s="3">
+        <f>E6-C6</f>
+        <v>6.6000000000000014</v>
+      </c>
+      <c r="M6" s="16">
+        <f>E6/C6</f>
+        <v>1.1226765799256506</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="14">
+        <v>1970</v>
+      </c>
+      <c r="C7" s="3">
+        <v>61.7</v>
+      </c>
+      <c r="D7" s="3">
+        <v>65.7</v>
+      </c>
+      <c r="E7" s="3">
+        <v>69.7</v>
+      </c>
+      <c r="K7" s="3">
+        <f>E7-C7</f>
+        <v>8</v>
+      </c>
+      <c r="M7" s="16">
+        <f>E7/C7</f>
+        <v>1.1296596434359805</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="14">
+        <v>1980</v>
+      </c>
+      <c r="C8" s="3">
+        <v>68.8</v>
+      </c>
+      <c r="D8" s="3">
+        <v>67.400000000000006</v>
+      </c>
+      <c r="E8" s="3">
+        <v>67.400000000000006</v>
+      </c>
+      <c r="K8" s="3">
+        <f>E8-C8</f>
+        <v>-1.3999999999999915</v>
+      </c>
+      <c r="M8" s="16">
+        <f>E8/C8</f>
+        <v>0.97965116279069775</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="14">
+        <v>1990</v>
+      </c>
+      <c r="C9" s="3">
+        <v>73.400000000000006</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3">
+        <v>73</v>
+      </c>
+      <c r="K9" s="3">
+        <f>E9-C9</f>
+        <v>-0.40000000000000568</v>
+      </c>
+      <c r="M9" s="16">
+        <f>E9/C9</f>
+        <v>0.99455040871934597</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="M10" s="16"/>
+    </row>
+    <row r="11" spans="1:13" ht="18.3" x14ac:dyDescent="0.7">
+      <c r="A11" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M11" s="16"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="M12" s="16"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="C13" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="M13" s="16"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="14">
+        <v>1930</v>
+      </c>
+      <c r="C14" s="3">
+        <v>25.6</v>
+      </c>
+      <c r="D14" s="3">
+        <v>21.7</v>
+      </c>
+      <c r="E14" s="3">
+        <v>20.5</v>
+      </c>
+      <c r="K14" s="3">
+        <f>E14-C14</f>
+        <v>-5.1000000000000014</v>
+      </c>
+      <c r="M14" s="16">
+        <f t="shared" ref="M14:M16" si="0">E14/C14</f>
+        <v>0.80078125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" s="14">
+        <v>1960</v>
+      </c>
+      <c r="C15" s="3">
+        <v>42.2</v>
+      </c>
+      <c r="D15" s="3">
+        <v>47.8</v>
+      </c>
+      <c r="E15" s="3">
+        <v>52.9</v>
+      </c>
+      <c r="K15" s="3">
+        <f>E15-C15</f>
+        <v>10.699999999999996</v>
+      </c>
+      <c r="M15" s="16">
+        <f t="shared" si="0"/>
+        <v>1.2535545023696681</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" s="14">
+        <v>1970</v>
+      </c>
+      <c r="C16" s="3">
+        <v>50.1</v>
+      </c>
+      <c r="D16" s="3">
+        <v>56.4</v>
+      </c>
+      <c r="E16" s="3">
+        <v>62.6</v>
+      </c>
+      <c r="K16" s="3">
+        <f>E16-C16</f>
+        <v>12.5</v>
+      </c>
+      <c r="M16" s="16">
+        <f t="shared" si="0"/>
+        <v>1.2495009980039919</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" s="14">
+        <v>1980</v>
+      </c>
+      <c r="C17" s="3">
+        <v>60.3</v>
+      </c>
+      <c r="D17" s="3">
+        <v>65</v>
+      </c>
+      <c r="E17" s="3">
+        <v>66.900000000000006</v>
+      </c>
+      <c r="K17" s="3">
+        <f>E17-C17</f>
+        <v>6.6000000000000085</v>
+      </c>
+      <c r="M17" s="16">
+        <f t="shared" ref="M17:M18" si="1">E17/C17</f>
+        <v>1.1094527363184081</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" s="14">
+        <v>1990</v>
+      </c>
+      <c r="C18" s="3">
+        <v>65.599999999999994</v>
+      </c>
+      <c r="E18" s="3">
+        <v>71.099999999999994</v>
+      </c>
+      <c r="K18" s="3">
+        <f>E18-C18</f>
+        <v>5.5</v>
+      </c>
+      <c r="M18" s="16">
+        <f t="shared" si="1"/>
+        <v>1.0838414634146341</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="18.3" x14ac:dyDescent="0.7">
+      <c r="A20" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="C21" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" s="14">
+        <v>1930</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3">
+        <v>12.1</v>
+      </c>
+      <c r="E22" s="3">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" s="14">
+        <v>1960</v>
+      </c>
+      <c r="C23" s="3">
+        <v>29.6</v>
+      </c>
+      <c r="D23" s="3">
+        <v>35.6</v>
+      </c>
+      <c r="E23" s="3">
+        <v>41</v>
+      </c>
+      <c r="K23" s="3">
+        <f>E23-C23</f>
+        <v>11.399999999999999</v>
+      </c>
+      <c r="M23" s="16">
+        <f t="shared" ref="M23:M24" si="2">E23/C23</f>
+        <v>1.3851351351351351</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="B24" s="14">
+        <v>1970</v>
+      </c>
+      <c r="C24" s="3">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="D24" s="3">
+        <v>44.3</v>
+      </c>
+      <c r="E24" s="3">
+        <v>50.8</v>
+      </c>
+      <c r="K24" s="3">
+        <f>E24-C24</f>
+        <v>15.5</v>
+      </c>
+      <c r="M24" s="16">
+        <f t="shared" si="2"/>
+        <v>1.4390934844192635</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B25" s="14">
+        <v>1980</v>
+      </c>
+      <c r="C25" s="3">
+        <v>49.9</v>
+      </c>
+      <c r="D25" s="3">
+        <v>54.9</v>
+      </c>
+      <c r="E25" s="15">
+        <v>58</v>
+      </c>
+      <c r="K25" s="3">
+        <f>E25-C25</f>
+        <v>8.1000000000000014</v>
+      </c>
+      <c r="M25" s="16">
+        <f t="shared" ref="M25:M26" si="3">E25/C25</f>
+        <v>1.1623246492985972</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B26" s="14">
+        <v>1990</v>
+      </c>
+      <c r="C26" s="3">
+        <v>55.4</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="15">
+        <v>61.9</v>
+      </c>
+      <c r="K26" s="3">
+        <f>E26-C26</f>
+        <v>6.5</v>
+      </c>
+      <c r="M26" s="16">
+        <f t="shared" si="3"/>
+        <v>1.1173285198555958</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="B27" s="14"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="15"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+    </row>
+    <row r="29" spans="1:13" ht="18.3" x14ac:dyDescent="0.7">
+      <c r="A29" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="C30" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B31" s="14">
+        <v>1930</v>
+      </c>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="E31" s="3">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B32" s="14">
+        <v>1960</v>
+      </c>
+      <c r="C32" s="3">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="D32" s="3">
+        <v>23.3</v>
+      </c>
+      <c r="E32" s="3">
+        <v>27</v>
+      </c>
+      <c r="K32" s="3">
+        <f>E32-C32</f>
+        <v>8.3999999999999986</v>
+      </c>
+      <c r="M32" s="16">
+        <f t="shared" ref="M32:M33" si="4">E32/C32</f>
+        <v>1.4516129032258063</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="B33" s="14">
+        <v>1970</v>
+      </c>
+      <c r="C33" s="3">
+        <v>23.3</v>
+      </c>
+      <c r="D33" s="3">
+        <v>31.2</v>
+      </c>
+      <c r="E33" s="3">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="K33" s="3">
+        <f>E33-C33</f>
+        <v>12.499999999999996</v>
+      </c>
+      <c r="M33" s="16">
+        <f t="shared" si="4"/>
+        <v>1.5364806866952787</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B34" s="14">
+        <v>1980</v>
+      </c>
+      <c r="C34" s="3">
+        <v>40.9</v>
+      </c>
+      <c r="D34" s="3">
+        <v>40.4</v>
+      </c>
+      <c r="E34" s="15">
+        <v>42.7</v>
+      </c>
+      <c r="K34" s="3">
+        <f>E34-C34</f>
+        <v>1.8000000000000043</v>
+      </c>
+      <c r="M34" s="16">
+        <f t="shared" ref="M34:M35" si="5">E34/C34</f>
+        <v>1.0440097799511003</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B35" s="14">
+        <v>1990</v>
+      </c>
+      <c r="C35" s="3">
+        <v>44.4</v>
+      </c>
+      <c r="D35" s="3"/>
+      <c r="E35" s="15">
+        <v>45.7</v>
+      </c>
+      <c r="K35" s="3">
+        <f>E35-C35</f>
+        <v>1.3000000000000043</v>
+      </c>
+      <c r="M35" s="16">
+        <f t="shared" si="5"/>
+        <v>1.0292792792792793</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="18.3" x14ac:dyDescent="0.7">
+      <c r="A38" s="11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="C40" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="H40" s="27"/>
+      <c r="I40" s="27"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" t="s">
+        <v>77</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F41" s="2"/>
+      <c r="G41" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="14">
+        <v>1897</v>
+      </c>
+      <c r="E42">
+        <v>15</v>
+      </c>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="14">
+        <v>1913</v>
+      </c>
+      <c r="E43">
+        <v>18</v>
+      </c>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="14">
+        <v>1920</v>
+      </c>
+      <c r="E44">
+        <v>15</v>
+      </c>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="14">
+        <v>1926</v>
+      </c>
+      <c r="E45">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="14">
+        <v>1937</v>
+      </c>
+      <c r="C46" s="1">
+        <v>162039470</v>
+      </c>
+      <c r="D46" s="1">
+        <v>51949458</v>
+      </c>
+      <c r="E46">
+        <v>31.2</v>
+      </c>
+      <c r="G46" s="1">
+        <v>103967924</v>
+      </c>
+      <c r="H46" s="1">
+        <v>34373245</v>
+      </c>
+      <c r="I46" s="18">
+        <f>H46/G46*100</f>
+        <v>33.061394012253245</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C47" s="3">
+        <f>C46/1000000</f>
+        <v>162.03946999999999</v>
+      </c>
+      <c r="D47" s="3">
+        <v>43.7</v>
+      </c>
+      <c r="E47" s="3">
+        <f>D47/C47*100</f>
+        <v>26.968737925395587</v>
+      </c>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3">
+        <f>G46/1000000</f>
+        <v>103.967924</v>
+      </c>
+      <c r="H47" s="3">
+        <v>30</v>
+      </c>
+      <c r="I47" s="3">
+        <f>H47/G47*100</f>
+        <v>28.855053410511495</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="14">
+        <v>1939</v>
+      </c>
+      <c r="C48" s="1">
+        <v>190677890</v>
+      </c>
+      <c r="D48" s="1">
+        <v>60409216</v>
+      </c>
+      <c r="E48" s="3">
+        <f>D48/C48*100</f>
+        <v>31.681290368799448</v>
+      </c>
+      <c r="G48" s="1">
+        <v>108377210</v>
+      </c>
+      <c r="H48" s="1">
+        <v>36295552</v>
+      </c>
+      <c r="I48" s="18">
+        <f>H48/G48*100</f>
+        <v>33.490022487200036</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C49">
+        <v>167.65</v>
+      </c>
+      <c r="D49">
+        <v>47.5</v>
+      </c>
+      <c r="E49" s="3">
+        <f>D49/C49*100</f>
+        <v>28.332836266030419</v>
+      </c>
+      <c r="G49" s="18">
+        <v>106.9</v>
+      </c>
+      <c r="H49" s="18">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="I49" s="18">
+        <f>H49/G49*100</f>
+        <v>31.524789522918617</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="14">
+        <v>1959</v>
+      </c>
+      <c r="C50" s="1">
+        <v>208826650</v>
+      </c>
+      <c r="D50" s="1">
+        <v>99977695</v>
+      </c>
+      <c r="E50" s="3">
+        <f t="shared" ref="E50:E53" si="6">D50/C50*100</f>
+        <v>47.875927234383155</v>
+      </c>
+      <c r="G50" s="1">
+        <v>117534306</v>
+      </c>
+      <c r="H50" s="1">
+        <v>61611074</v>
+      </c>
+      <c r="I50" s="18">
+        <f t="shared" ref="I50:I53" si="7">H50/G50*100</f>
+        <v>52.419651841905633</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="14">
+        <v>1970</v>
+      </c>
+      <c r="C51" s="1">
+        <v>241720134</v>
+      </c>
+      <c r="D51" s="1">
+        <v>135991514</v>
+      </c>
+      <c r="E51" s="3">
+        <f t="shared" si="6"/>
+        <v>56.259903446851482</v>
+      </c>
+      <c r="G51" s="1">
+        <v>130079210</v>
+      </c>
+      <c r="H51" s="1">
+        <v>80981143</v>
+      </c>
+      <c r="I51" s="18">
+        <f t="shared" si="7"/>
+        <v>62.255254317734554</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="14">
+        <v>1979</v>
+      </c>
+      <c r="C52" s="1">
+        <v>262436227</v>
+      </c>
+      <c r="D52" s="1">
+        <v>163585914</v>
+      </c>
+      <c r="E52" s="3">
+        <f t="shared" si="6"/>
+        <v>62.333587047035245</v>
+      </c>
+      <c r="G52" s="1">
+        <v>137550949</v>
+      </c>
+      <c r="H52" s="1">
+        <v>95373867</v>
+      </c>
+      <c r="I52" s="18">
+        <f t="shared" si="7"/>
+        <v>69.337120313143018</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="14">
+        <v>1989</v>
+      </c>
+      <c r="C53" s="1">
+        <v>286731</v>
+      </c>
+      <c r="D53" s="1">
+        <v>188814</v>
+      </c>
+      <c r="E53" s="3">
+        <f t="shared" si="6"/>
+        <v>65.850570744007456</v>
+      </c>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1">
+        <v>147400</v>
+      </c>
+      <c r="H53" s="1">
+        <v>108425</v>
+      </c>
+      <c r="I53" s="18">
+        <f t="shared" si="7"/>
+        <v>73.558344640434186</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B56" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B57" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B60" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B62" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B64" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B65" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B66" t="s">
+        <v>102</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="G40:I40"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D70B758-2D8E-4D0F-9152-375389941F4D}">
   <dimension ref="A1:M37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
@@ -1163,7 +2089,7 @@
       <c r="A1" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="J1" s="20" t="s">
+      <c r="J1" s="19" t="s">
         <v>98</v>
       </c>
     </row>
@@ -1581,7 +2507,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBE7E47A-F406-4131-8275-CA858AD6FB0F}">
   <dimension ref="A1:AA40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
@@ -1596,7 +2522,7 @@
       <c r="A1" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="J1" s="20" t="s">
+      <c r="J1" s="19" t="s">
         <v>98</v>
       </c>
     </row>
@@ -2149,7 +3075,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD1CEBF5-B4BD-4DD1-AC0A-66E7B41EFED5}">
   <dimension ref="A2:H38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
@@ -2457,7 +3383,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E93D3E-D80F-423E-BDEC-5E3B3CDBD631}">
   <dimension ref="A1:O54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
@@ -2471,7 +3397,7 @@
       <c r="A1" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="L1" s="20" t="s">
+      <c r="L1" s="19" t="s">
         <v>98</v>
       </c>
     </row>
@@ -2977,7 +3903,7 @@
         <f>SUM(O8:O19)</f>
         <v>18795417</v>
       </c>
-      <c r="F27" s="30"/>
+      <c r="F27" s="3"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="2" t="s">
@@ -2987,7 +3913,7 @@
         <f>D27/D21*100</f>
         <v>53.819395736275524</v>
       </c>
-      <c r="F28" s="30"/>
+      <c r="F28" s="3"/>
     </row>
     <row r="30" spans="1:15" ht="18.3" x14ac:dyDescent="0.7">
       <c r="A30" s="11" t="s">
@@ -3113,7 +4039,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A2F5240-BC93-4757-9D88-C679B5B701EC}">
   <dimension ref="A1:O56"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
@@ -3129,7 +4055,7 @@
       <c r="A1" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="L1" s="20" t="s">
+      <c r="L1" s="19" t="s">
         <v>98</v>
       </c>
     </row>
@@ -3642,7 +4568,7 @@
         <f>SUM(O9:O20)</f>
         <v>29745847</v>
       </c>
-      <c r="F29" s="30"/>
+      <c r="F29" s="3"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="2" t="s">
@@ -3652,7 +4578,7 @@
         <f>D29/D22*100</f>
         <v>61.681078691617863</v>
       </c>
-      <c r="F30" s="30"/>
+      <c r="F30" s="3"/>
     </row>
     <row r="33" spans="1:4" ht="18.3" x14ac:dyDescent="0.7">
       <c r="A33" s="11" t="s">
@@ -3777,7 +4703,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{281F1983-1E2D-4296-BC15-C6FA9A40CC5F}">
   <dimension ref="A1:Q51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
@@ -3791,12 +4717,12 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="21" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="21" t="s">
         <v>110</v>
       </c>
     </row>
@@ -3829,7 +4755,7 @@
       <c r="C7" s="1">
         <v>78806</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="25">
         <v>1888882</v>
       </c>
     </row>
@@ -3843,7 +4769,7 @@
       <c r="C8" s="1">
         <v>31054</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="26">
         <v>7544871</v>
       </c>
     </row>
@@ -3857,7 +4783,7 @@
       <c r="C9" s="1">
         <v>8473</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="26">
         <v>5886009</v>
       </c>
     </row>
@@ -3871,7 +4797,7 @@
       <c r="C10" s="1">
         <v>4100</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="26">
         <v>5585494</v>
       </c>
     </row>
@@ -3885,7 +4811,7 @@
       <c r="C11" s="1">
         <v>736</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="26">
         <v>1641848</v>
       </c>
     </row>
@@ -3899,7 +4825,7 @@
       <c r="C12" s="1">
         <v>1147</v>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="26">
         <v>4092168</v>
       </c>
     </row>
@@ -3913,7 +4839,7 @@
       <c r="C13" s="1">
         <v>513</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="26">
         <v>3527104</v>
       </c>
     </row>
@@ -3927,7 +4853,7 @@
       <c r="C14" s="1">
         <v>171</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="26">
         <v>2075770</v>
       </c>
     </row>
@@ -3941,7 +4867,7 @@
       <c r="C15" s="1">
         <v>77</v>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="26">
         <v>1331710</v>
       </c>
     </row>
@@ -3955,7 +4881,7 @@
       <c r="C16" s="1">
         <v>119</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="26">
         <v>3596371</v>
       </c>
     </row>
@@ -3969,7 +4895,7 @@
       <c r="C17" s="1">
         <v>33</v>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="25">
         <v>2408180</v>
       </c>
     </row>
@@ -3983,7 +4909,7 @@
       <c r="C18" s="1">
         <v>52</v>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="26">
         <v>11352926</v>
       </c>
     </row>
@@ -3997,7 +4923,7 @@
       <c r="C19" s="1">
         <v>14</v>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="26">
         <v>9158189</v>
       </c>
     </row>
@@ -4011,7 +4937,7 @@
       <c r="C20" s="1">
         <v>5</v>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="26">
         <v>6827792</v>
       </c>
     </row>
@@ -4023,7 +4949,7 @@
       <c r="C21" s="1">
         <v>125300</v>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="26">
         <v>66846833</v>
       </c>
       <c r="F21" t="s">
@@ -4101,49 +5027,49 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="2"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="23"/>
-      <c r="H37" s="23"/>
-      <c r="I37" s="23"/>
-      <c r="J37" s="23"/>
-      <c r="K37" s="23"/>
-      <c r="L37" s="23"/>
-      <c r="M37" s="23"/>
-      <c r="N37" s="23"/>
-      <c r="O37" s="23"/>
-      <c r="P37" s="23"/>
-      <c r="Q37" s="23"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="22"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="22"/>
+      <c r="M37" s="22"/>
+      <c r="N37" s="22"/>
+      <c r="O37" s="22"/>
+      <c r="P37" s="22"/>
+      <c r="Q37" s="22"/>
     </row>
     <row r="38" spans="1:17" ht="18.3" x14ac:dyDescent="0.7">
       <c r="A38" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="F38" s="23"/>
-      <c r="G38" s="23"/>
-      <c r="H38" s="23"/>
-      <c r="I38" s="23"/>
-      <c r="J38" s="23"/>
-      <c r="K38" s="23"/>
-      <c r="L38" s="23"/>
-      <c r="M38" s="23"/>
-      <c r="N38" s="23"/>
-      <c r="O38" s="23"/>
-      <c r="P38" s="23"/>
-      <c r="Q38" s="23"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="22"/>
+      <c r="J38" s="22"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="22"/>
+      <c r="M38" s="22"/>
+      <c r="N38" s="22"/>
+      <c r="O38" s="22"/>
+      <c r="P38" s="22"/>
+      <c r="Q38" s="22"/>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="F39" s="23"/>
-      <c r="G39" s="23"/>
-      <c r="H39" s="23"/>
-      <c r="I39" s="23"/>
-      <c r="J39" s="23"/>
-      <c r="K39" s="23"/>
-      <c r="L39" s="23"/>
-      <c r="M39" s="23"/>
-      <c r="N39" s="23"/>
-      <c r="O39" s="23"/>
-      <c r="P39" s="23"/>
-      <c r="Q39" s="23"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="22"/>
+      <c r="H39" s="22"/>
+      <c r="I39" s="22"/>
+      <c r="J39" s="22"/>
+      <c r="K39" s="22"/>
+      <c r="L39" s="22"/>
+      <c r="M39" s="22"/>
+      <c r="N39" s="22"/>
+      <c r="O39" s="22"/>
+      <c r="P39" s="22"/>
+      <c r="Q39" s="22"/>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="4" t="s">
@@ -4153,18 +5079,18 @@
         <f>SUM(D13:D20)</f>
         <v>40278042</v>
       </c>
-      <c r="F40" s="24"/>
-      <c r="G40" s="24"/>
-      <c r="H40" s="24"/>
-      <c r="I40" s="24"/>
-      <c r="J40" s="24"/>
-      <c r="K40" s="24"/>
-      <c r="L40" s="24"/>
-      <c r="M40" s="24"/>
-      <c r="N40" s="24"/>
-      <c r="O40" s="24"/>
-      <c r="P40" s="24"/>
-      <c r="Q40" s="24"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
+      <c r="H40" s="23"/>
+      <c r="I40" s="23"/>
+      <c r="J40" s="23"/>
+      <c r="K40" s="23"/>
+      <c r="L40" s="23"/>
+      <c r="M40" s="23"/>
+      <c r="N40" s="23"/>
+      <c r="O40" s="23"/>
+      <c r="P40" s="23"/>
+      <c r="Q40" s="23"/>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="2" t="s">
@@ -4174,18 +5100,18 @@
         <f>D40/D21*100</f>
         <v>60.254226254817489</v>
       </c>
-      <c r="F41" s="25"/>
-      <c r="G41" s="25"/>
-      <c r="H41" s="25"/>
-      <c r="I41" s="25"/>
-      <c r="J41" s="25"/>
-      <c r="K41" s="25"/>
-      <c r="L41" s="25"/>
-      <c r="M41" s="25"/>
-      <c r="N41" s="25"/>
-      <c r="O41" s="25"/>
-      <c r="P41" s="25"/>
-      <c r="Q41" s="25"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="24"/>
+      <c r="H41" s="24"/>
+      <c r="I41" s="24"/>
+      <c r="J41" s="24"/>
+      <c r="K41" s="24"/>
+      <c r="L41" s="24"/>
+      <c r="M41" s="24"/>
+      <c r="N41" s="24"/>
+      <c r="O41" s="24"/>
+      <c r="P41" s="24"/>
+      <c r="Q41" s="24"/>
     </row>
     <row r="43" spans="1:17" ht="18.3" x14ac:dyDescent="0.7">
       <c r="A43" s="11" t="s">
@@ -4245,7 +5171,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC5F3DFD-C1E0-4182-B8B9-0550FFE0B4EA}">
   <dimension ref="A1:D51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
@@ -4298,7 +5224,7 @@
       <c r="C7" s="1">
         <v>108307</v>
       </c>
-      <c r="D7" s="21">
+      <c r="D7" s="20">
         <v>2190339</v>
       </c>
     </row>
@@ -4312,7 +5238,7 @@
       <c r="C8" s="1">
         <v>32244</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="20">
         <v>7760320</v>
       </c>
     </row>
@@ -4326,7 +5252,7 @@
       <c r="C9" s="1">
         <v>8515</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D9" s="20">
         <v>5922495</v>
       </c>
     </row>
@@ -4340,7 +5266,7 @@
       <c r="C10" s="1">
         <v>4216</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="20">
         <v>5779036</v>
       </c>
     </row>
@@ -4354,7 +5280,7 @@
       <c r="C11">
         <v>734</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="20">
         <v>1637734</v>
       </c>
     </row>
@@ -4368,7 +5294,7 @@
       <c r="C12" s="1">
         <v>1364</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="20">
         <v>4647566</v>
       </c>
     </row>
@@ -4382,7 +5308,7 @@
       <c r="C13">
         <v>609</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="20">
         <v>4226294</v>
       </c>
     </row>
@@ -4396,7 +5322,7 @@
       <c r="C14">
         <v>197</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="20">
         <v>2410451</v>
       </c>
     </row>
@@ -4410,7 +5336,7 @@
       <c r="C15">
         <v>96</v>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="20">
         <v>1675566</v>
       </c>
     </row>
@@ -4424,7 +5350,7 @@
       <c r="C16">
         <v>167</v>
       </c>
-      <c r="D16" s="21">
+      <c r="D16" s="20">
         <v>5075188</v>
       </c>
     </row>
@@ -4438,7 +5364,7 @@
       <c r="C17">
         <v>55</v>
       </c>
-      <c r="D17" s="21">
+      <c r="D17" s="20">
         <v>3854850</v>
       </c>
     </row>
@@ -4452,7 +5378,7 @@
       <c r="C18">
         <v>77</v>
       </c>
-      <c r="D18" s="21">
+      <c r="D18" s="20">
         <v>18233313</v>
       </c>
     </row>
@@ -4466,7 +5392,7 @@
       <c r="C19">
         <v>14</v>
       </c>
-      <c r="D19" s="21">
+      <c r="D19" s="20">
         <v>8878127</v>
       </c>
     </row>
@@ -4480,7 +5406,7 @@
       <c r="C20">
         <v>7</v>
       </c>
-      <c r="D20" s="21">
+      <c r="D20" s="20">
         <v>8958366</v>
       </c>
     </row>
@@ -4645,1088 +5571,6 @@
   <ignoredErrors>
     <ignoredError sqref="D25 D30 D35 D40 D45 D50" formulaRange="1"/>
   </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2920F376-2D53-4EC0-B932-712BB7C94480}">
-  <dimension ref="A1:M82"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
-  <cols>
-    <col min="1" max="1" width="12.15625" customWidth="1"/>
-    <col min="3" max="3" width="11.15625" customWidth="1"/>
-    <col min="4" max="4" width="11.41796875" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="10.15625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="9.83984375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="18.3" x14ac:dyDescent="0.7">
-      <c r="A1" s="11" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="C3" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="B4" s="14">
-        <v>1930</v>
-      </c>
-      <c r="C4" s="3">
-        <v>50</v>
-      </c>
-      <c r="D4" s="3">
-        <v>50.6</v>
-      </c>
-      <c r="E4" s="3">
-        <v>46.2</v>
-      </c>
-      <c r="K4" s="3">
-        <f>E4-C4</f>
-        <v>-3.7999999999999972</v>
-      </c>
-      <c r="M4" s="17">
-        <f>E4/C4</f>
-        <v>0.92400000000000004</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B5" s="14">
-        <v>1960</v>
-      </c>
-      <c r="C5" s="3">
-        <v>65</v>
-      </c>
-      <c r="D5" s="3">
-        <v>66.7</v>
-      </c>
-      <c r="E5" s="3">
-        <v>67.400000000000006</v>
-      </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3">
-        <f>E5-C5</f>
-        <v>2.4000000000000057</v>
-      </c>
-      <c r="L5" s="15"/>
-      <c r="M5" s="17">
-        <f>E5/C5</f>
-        <v>1.0369230769230771</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="14">
-        <v>1970</v>
-      </c>
-      <c r="C6" s="3">
-        <v>71.900000000000006</v>
-      </c>
-      <c r="D6" s="3">
-        <v>75.400000000000006</v>
-      </c>
-      <c r="E6" s="3">
-        <v>76.5</v>
-      </c>
-      <c r="K6" s="3">
-        <f>E6-C6</f>
-        <v>4.5999999999999943</v>
-      </c>
-      <c r="M6" s="17">
-        <f>E6/C6</f>
-        <v>1.0639777468706535</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="14">
-        <v>1990</v>
-      </c>
-      <c r="C7" s="3">
-        <v>80.5</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="M7" s="17"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="M8" s="17"/>
-    </row>
-    <row r="9" spans="1:13" ht="18.3" x14ac:dyDescent="0.7">
-      <c r="A9" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M9" s="17"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="M10" s="17"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="M11" s="17"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="B12" s="14">
-        <v>1930</v>
-      </c>
-      <c r="C12" s="3">
-        <v>37.200000000000003</v>
-      </c>
-      <c r="D12" s="3">
-        <v>36</v>
-      </c>
-      <c r="E12" s="3">
-        <v>32.6</v>
-      </c>
-      <c r="K12" s="3">
-        <f>E12-C12</f>
-        <v>-4.6000000000000014</v>
-      </c>
-      <c r="M12" s="17">
-        <f>E12/C12</f>
-        <v>0.87634408602150538</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B13" s="14">
-        <v>1960</v>
-      </c>
-      <c r="C13" s="3">
-        <v>53.6</v>
-      </c>
-      <c r="D13" s="3">
-        <v>57.2</v>
-      </c>
-      <c r="E13" s="3">
-        <v>60.4</v>
-      </c>
-      <c r="K13" s="3">
-        <f>E13-C13</f>
-        <v>6.7999999999999972</v>
-      </c>
-      <c r="M13" s="17">
-        <f>E13/C13</f>
-        <v>1.1268656716417911</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="14">
-        <v>1970</v>
-      </c>
-      <c r="C14" s="3">
-        <v>61.4</v>
-      </c>
-      <c r="D14" s="3">
-        <v>65.7</v>
-      </c>
-      <c r="E14" s="3">
-        <v>69.7</v>
-      </c>
-      <c r="K14" s="3">
-        <f>E14-C14</f>
-        <v>8.3000000000000043</v>
-      </c>
-      <c r="M14" s="17">
-        <f>E14/C14</f>
-        <v>1.1351791530944626</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="M15" s="17"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="B16" s="14">
-        <v>1990</v>
-      </c>
-      <c r="C16" s="3">
-        <v>73.400000000000006</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="M16" s="17"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="M17" s="17"/>
-    </row>
-    <row r="18" spans="1:13" ht="18.3" x14ac:dyDescent="0.7">
-      <c r="A18" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="M18" s="17"/>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="M19" s="17"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="C20" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="M20" s="17"/>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="B21" s="14">
-        <v>1930</v>
-      </c>
-      <c r="C21" s="3">
-        <v>33.5</v>
-      </c>
-      <c r="D21" s="3">
-        <v>31.6</v>
-      </c>
-      <c r="E21" s="3">
-        <v>28.7</v>
-      </c>
-      <c r="K21" s="3">
-        <f>E21-C21</f>
-        <v>-4.8000000000000007</v>
-      </c>
-      <c r="M21" s="17">
-        <f t="shared" ref="M21:M23" si="0">E21/C21</f>
-        <v>0.85671641791044773</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B22" s="14">
-        <v>1960</v>
-      </c>
-      <c r="C22" s="3">
-        <v>50.7</v>
-      </c>
-      <c r="D22" s="16">
-        <v>54.6</v>
-      </c>
-      <c r="E22" s="16">
-        <v>58.5</v>
-      </c>
-      <c r="K22" s="3">
-        <f>E22-C22</f>
-        <v>7.7999999999999972</v>
-      </c>
-      <c r="M22" s="17">
-        <f t="shared" si="0"/>
-        <v>1.1538461538461537</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="B23" s="14">
-        <v>1970</v>
-      </c>
-      <c r="C23" s="3">
-        <v>58.7</v>
-      </c>
-      <c r="D23" s="16">
-        <v>63.1</v>
-      </c>
-      <c r="E23" s="16">
-        <v>67.900000000000006</v>
-      </c>
-      <c r="K23" s="3">
-        <f>E23-C23</f>
-        <v>9.2000000000000028</v>
-      </c>
-      <c r="M23" s="17">
-        <f t="shared" si="0"/>
-        <v>1.1567291311754686</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="K24" s="3"/>
-      <c r="M24" s="17"/>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="B25" s="14">
-        <v>1990</v>
-      </c>
-      <c r="C25" s="3">
-        <v>71.3</v>
-      </c>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="K25" s="3"/>
-      <c r="M25" s="17"/>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="M26" s="17"/>
-    </row>
-    <row r="27" spans="1:13" ht="18.3" x14ac:dyDescent="0.7">
-      <c r="A27" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="M27" s="17"/>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="M28" s="17"/>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="C29" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="M29" s="17"/>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="B30" s="14">
-        <v>1930</v>
-      </c>
-      <c r="C30" s="3">
-        <v>25.6</v>
-      </c>
-      <c r="D30" s="3">
-        <v>21.7</v>
-      </c>
-      <c r="E30" s="3">
-        <v>20.5</v>
-      </c>
-      <c r="K30" s="3">
-        <f>E30-C30</f>
-        <v>-5.1000000000000014</v>
-      </c>
-      <c r="M30" s="17">
-        <f t="shared" ref="M30:M32" si="1">E30/C30</f>
-        <v>0.80078125</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B31" s="14">
-        <v>1960</v>
-      </c>
-      <c r="C31" s="3">
-        <v>42.2</v>
-      </c>
-      <c r="D31" s="3">
-        <v>47.8</v>
-      </c>
-      <c r="E31" s="3">
-        <v>52.9</v>
-      </c>
-      <c r="K31" s="3">
-        <f>E31-C31</f>
-        <v>10.699999999999996</v>
-      </c>
-      <c r="M31" s="17">
-        <f t="shared" si="1"/>
-        <v>1.2535545023696681</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="14">
-        <v>1970</v>
-      </c>
-      <c r="C32" s="3">
-        <v>50.1</v>
-      </c>
-      <c r="D32" s="3">
-        <v>56.4</v>
-      </c>
-      <c r="E32" s="3">
-        <v>62.6</v>
-      </c>
-      <c r="K32" s="3">
-        <f>E32-C32</f>
-        <v>12.5</v>
-      </c>
-      <c r="M32" s="17">
-        <f t="shared" si="1"/>
-        <v>1.2495009980039919</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="B33" s="14"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3">
-        <v>65</v>
-      </c>
-      <c r="E33" s="3">
-        <v>66.900000000000006</v>
-      </c>
-      <c r="K33" s="3"/>
-      <c r="M33" s="17"/>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="B34" s="14">
-        <v>1990</v>
-      </c>
-      <c r="C34" s="3">
-        <v>65.599999999999994</v>
-      </c>
-      <c r="E34" s="3">
-        <v>71.099999999999994</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="18.3" x14ac:dyDescent="0.7">
-      <c r="A36" s="11" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="C37" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="B38" s="14">
-        <v>1930</v>
-      </c>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3">
-        <v>12.1</v>
-      </c>
-      <c r="E38" s="3">
-        <v>11.8</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B39" s="14">
-        <v>1960</v>
-      </c>
-      <c r="C39" s="3">
-        <v>29.6</v>
-      </c>
-      <c r="D39" s="3">
-        <v>35.6</v>
-      </c>
-      <c r="E39" s="3">
-        <v>41</v>
-      </c>
-      <c r="K39" s="3">
-        <f>E39-C39</f>
-        <v>11.399999999999999</v>
-      </c>
-      <c r="M39" s="17">
-        <f t="shared" ref="M39:M40" si="2">E39/C39</f>
-        <v>1.3851351351351351</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="B40" s="14">
-        <v>1970</v>
-      </c>
-      <c r="C40" s="3">
-        <v>35.299999999999997</v>
-      </c>
-      <c r="D40" s="3">
-        <v>44.3</v>
-      </c>
-      <c r="E40" s="3">
-        <v>50.8</v>
-      </c>
-      <c r="K40" s="3">
-        <f>E40-C40</f>
-        <v>15.5</v>
-      </c>
-      <c r="M40" s="17">
-        <f t="shared" si="2"/>
-        <v>1.4390934844192635</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="B41" s="14">
-        <v>1979</v>
-      </c>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3">
-        <v>54.9</v>
-      </c>
-      <c r="E41" s="16">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="B42" s="14"/>
-      <c r="C42" s="3">
-        <v>55.4</v>
-      </c>
-      <c r="D42" s="3"/>
-      <c r="E42" s="16">
-        <v>61.9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="B43" s="14"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="16"/>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-    </row>
-    <row r="45" spans="1:13" ht="18.3" x14ac:dyDescent="0.7">
-      <c r="A45" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="C46" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="D46" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E46" s="18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="B47" s="14">
-        <v>1930</v>
-      </c>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3">
-        <v>6.5</v>
-      </c>
-      <c r="E47" s="3">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B48" s="14">
-        <v>1960</v>
-      </c>
-      <c r="C48" s="3">
-        <v>18.600000000000001</v>
-      </c>
-      <c r="D48" s="3">
-        <v>23.3</v>
-      </c>
-      <c r="E48" s="3">
-        <v>27</v>
-      </c>
-      <c r="K48" s="3">
-        <f>E48-C48</f>
-        <v>8.3999999999999986</v>
-      </c>
-      <c r="M48" s="17">
-        <f t="shared" ref="M48:M49" si="3">E48/C48</f>
-        <v>1.4516129032258063</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="B49" s="14">
-        <v>1970</v>
-      </c>
-      <c r="C49" s="3">
-        <v>23.3</v>
-      </c>
-      <c r="D49" s="3">
-        <v>31.2</v>
-      </c>
-      <c r="E49" s="3">
-        <v>35.799999999999997</v>
-      </c>
-      <c r="K49" s="3">
-        <f>E49-C49</f>
-        <v>12.499999999999996</v>
-      </c>
-      <c r="M49" s="17">
-        <f t="shared" si="3"/>
-        <v>1.5364806866952787</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="B50" s="14">
-        <v>1979</v>
-      </c>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3">
-        <v>40.4</v>
-      </c>
-      <c r="E50" s="16">
-        <v>42.7</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="B51" s="14"/>
-      <c r="C51" s="3">
-        <v>44.4</v>
-      </c>
-      <c r="D51" s="3"/>
-      <c r="E51" s="16">
-        <v>45.7</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="18.3" x14ac:dyDescent="0.7">
-      <c r="A54" s="11" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="C56" s="29" t="s">
-        <v>37</v>
-      </c>
-      <c r="D56" s="29"/>
-      <c r="E56" s="29"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="H56" s="29"/>
-      <c r="I56" s="29"/>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" t="s">
-        <v>77</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="F57" s="2"/>
-      <c r="G57" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="H57" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I57" s="7" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="14">
-        <v>1897</v>
-      </c>
-      <c r="E58">
-        <v>15</v>
-      </c>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
-      <c r="I58">
-        <v>14.7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="14">
-        <v>1913</v>
-      </c>
-      <c r="E59">
-        <v>18</v>
-      </c>
-      <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="14">
-        <v>1920</v>
-      </c>
-      <c r="E60">
-        <v>15</v>
-      </c>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
-      <c r="I60">
-        <v>14.2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="14">
-        <v>1926</v>
-      </c>
-      <c r="E61">
-        <v>17.899999999999999</v>
-      </c>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
-      <c r="I61">
-        <v>17.3</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="14">
-        <v>1937</v>
-      </c>
-      <c r="C62" s="1">
-        <v>162039470</v>
-      </c>
-      <c r="D62" s="1">
-        <v>51949458</v>
-      </c>
-      <c r="E62">
-        <v>31.2</v>
-      </c>
-      <c r="G62" s="1">
-        <v>103967924</v>
-      </c>
-      <c r="H62" s="1">
-        <v>34373245</v>
-      </c>
-      <c r="I62" s="19">
-        <f>H62/G62*100</f>
-        <v>33.061394012253245</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="C63" s="3">
-        <f>C62/1000000</f>
-        <v>162.03946999999999</v>
-      </c>
-      <c r="D63" s="3">
-        <v>43.7</v>
-      </c>
-      <c r="E63" s="3">
-        <f>D63/C63*100</f>
-        <v>26.968737925395587</v>
-      </c>
-      <c r="F63" s="3"/>
-      <c r="G63" s="3">
-        <f>G62/1000000</f>
-        <v>103.967924</v>
-      </c>
-      <c r="H63" s="3">
-        <v>30</v>
-      </c>
-      <c r="I63" s="3">
-        <f>H63/G63*100</f>
-        <v>28.855053410511495</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" s="14">
-        <v>1939</v>
-      </c>
-      <c r="C64" s="1">
-        <v>190677890</v>
-      </c>
-      <c r="D64" s="1">
-        <v>60409216</v>
-      </c>
-      <c r="E64" s="3">
-        <f>D64/C64*100</f>
-        <v>31.681290368799448</v>
-      </c>
-      <c r="G64" s="1">
-        <v>108377210</v>
-      </c>
-      <c r="H64" s="1">
-        <v>36295552</v>
-      </c>
-      <c r="I64" s="19">
-        <f>H64/G64*100</f>
-        <v>33.490022487200036</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A65" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="C65">
-        <v>167.65</v>
-      </c>
-      <c r="D65">
-        <v>47.5</v>
-      </c>
-      <c r="E65" s="3">
-        <f>D65/C65*100</f>
-        <v>28.332836266030419</v>
-      </c>
-      <c r="G65" s="19">
-        <v>106.9</v>
-      </c>
-      <c r="H65" s="19">
-        <v>33.700000000000003</v>
-      </c>
-      <c r="I65" s="19">
-        <f>H65/G65*100</f>
-        <v>31.524789522918617</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66" s="14">
-        <v>1959</v>
-      </c>
-      <c r="C66" s="1">
-        <v>208826650</v>
-      </c>
-      <c r="D66" s="1">
-        <v>99977695</v>
-      </c>
-      <c r="E66" s="3">
-        <f t="shared" ref="E66:E69" si="4">D66/C66*100</f>
-        <v>47.875927234383155</v>
-      </c>
-      <c r="G66" s="1">
-        <v>117534306</v>
-      </c>
-      <c r="H66" s="1">
-        <v>61611074</v>
-      </c>
-      <c r="I66" s="19">
-        <f t="shared" ref="I66:I69" si="5">H66/G66*100</f>
-        <v>52.419651841905633</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67" s="14">
-        <v>1970</v>
-      </c>
-      <c r="C67" s="1">
-        <v>241720134</v>
-      </c>
-      <c r="D67" s="1">
-        <v>135991514</v>
-      </c>
-      <c r="E67" s="3">
-        <f t="shared" si="4"/>
-        <v>56.259903446851482</v>
-      </c>
-      <c r="G67" s="1">
-        <v>130079210</v>
-      </c>
-      <c r="H67" s="1">
-        <v>80981143</v>
-      </c>
-      <c r="I67" s="19">
-        <f t="shared" si="5"/>
-        <v>62.255254317734554</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A68" s="14">
-        <v>1979</v>
-      </c>
-      <c r="C68" s="1">
-        <v>262436227</v>
-      </c>
-      <c r="D68" s="1">
-        <v>163585914</v>
-      </c>
-      <c r="E68" s="3">
-        <f t="shared" si="4"/>
-        <v>62.333587047035245</v>
-      </c>
-      <c r="G68" s="1">
-        <v>137550949</v>
-      </c>
-      <c r="H68" s="1">
-        <v>95373867</v>
-      </c>
-      <c r="I68" s="19">
-        <f t="shared" si="5"/>
-        <v>69.337120313143018</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A69" s="14">
-        <v>1989</v>
-      </c>
-      <c r="C69" s="1">
-        <v>286731</v>
-      </c>
-      <c r="D69" s="1">
-        <v>188814</v>
-      </c>
-      <c r="E69" s="3">
-        <f t="shared" si="4"/>
-        <v>65.850570744007456</v>
-      </c>
-      <c r="F69" s="1"/>
-      <c r="G69" s="1">
-        <v>147400</v>
-      </c>
-      <c r="H69" s="1">
-        <v>108425</v>
-      </c>
-      <c r="I69" s="19">
-        <f t="shared" si="5"/>
-        <v>73.558344640434186</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A71" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="B73" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A74" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A75" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="B76" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A77" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="B78" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A79" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="B80" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B81" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B82" t="s">
-        <v>102</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="G56:I56"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5757,13 +5601,13 @@
       <c r="A1" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="Q1" s="20"/>
+      <c r="Q1" s="19"/>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="29"/>
+      <c r="B3" s="27"/>
       <c r="C3" s="28" t="s">
         <v>37</v>
       </c>
@@ -5788,8 +5632,8 @@
         <v>34</v>
       </c>
       <c r="N3" s="28"/>
-      <c r="Q3" s="29"/>
-      <c r="R3" s="29"/>
+      <c r="Q3" s="27"/>
+      <c r="R3" s="27"/>
       <c r="S3" s="28"/>
       <c r="T3" s="28"/>
       <c r="U3" s="28"/>
@@ -6846,7 +6690,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="18.3" x14ac:dyDescent="0.7">
-      <c r="A47" s="20" t="s">
+      <c r="A47" s="19" t="s">
         <v>81</v>
       </c>
     </row>
@@ -6862,16 +6706,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="I3:J3"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="U3:V3"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -7304,23 +7148,23 @@
       <c r="A2" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="N2" s="20" t="s">
+      <c r="N2" s="19" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="I3" s="29" t="s">
+      <c r="I3" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="J3" s="29"/>
+      <c r="J3" s="27"/>
       <c r="M3" s="7"/>
       <c r="N3" s="7"/>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="29"/>
+      <c r="D4" s="27"/>
       <c r="G4" s="7" t="s">
         <v>0</v>
       </c>
@@ -7333,14 +7177,14 @@
       <c r="J4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="P4" s="29" t="s">
+      <c r="P4" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="Q4" s="29"/>
-      <c r="U4" s="29" t="s">
+      <c r="Q4" s="27"/>
+      <c r="U4" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="V4" s="29"/>
+      <c r="V4" s="27"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="7" t="s">
@@ -7945,7 +7789,7 @@
       <c r="A1" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="N1" s="20" t="s">
+      <c r="N1" s="19" t="s">
         <v>98</v>
       </c>
     </row>
@@ -7954,22 +7798,22 @@
       <c r="J2" s="7"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.55000000000000004">
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="29"/>
-      <c r="I3" s="29" t="s">
+      <c r="D3" s="27"/>
+      <c r="I3" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="J3" s="29"/>
-      <c r="P3" s="29" t="s">
+      <c r="J3" s="27"/>
+      <c r="P3" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="Q3" s="29"/>
-      <c r="U3" s="29" t="s">
+      <c r="Q3" s="27"/>
+      <c r="U3" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="V3" s="29"/>
+      <c r="V3" s="27"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2" t="s">
@@ -8595,7 +8439,7 @@
       <c r="A1" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="K1" s="20" t="s">
+      <c r="K1" s="19" t="s">
         <v>98</v>
       </c>
     </row>
@@ -9518,21 +9362,21 @@
       <c r="A1" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="M1" s="20" t="s">
+      <c r="M1" s="19" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="I2" s="29" t="s">
+      <c r="I2" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="J2" s="29"/>
+      <c r="J2" s="27"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="29"/>
+      <c r="D3" s="27"/>
       <c r="G3" s="7" t="s">
         <v>0</v>
       </c>
@@ -9545,14 +9389,14 @@
       <c r="J3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="O3" s="29" t="s">
+      <c r="O3" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="P3" s="29"/>
-      <c r="T3" s="29" t="s">
+      <c r="P3" s="27"/>
+      <c r="T3" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="U3" s="29"/>
+      <c r="U3" s="27"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="7" t="s">
@@ -10143,7 +9987,7 @@
       <c r="A1" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="M1" s="20" t="s">
+      <c r="M1" s="19" t="s">
         <v>98</v>
       </c>
     </row>
@@ -10152,22 +9996,22 @@
       <c r="J2" s="7"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="29"/>
-      <c r="I3" s="29" t="s">
+      <c r="D3" s="27"/>
+      <c r="I3" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="J3" s="29"/>
-      <c r="O3" s="29" t="s">
+      <c r="J3" s="27"/>
+      <c r="O3" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="P3" s="29"/>
-      <c r="U3" s="29" t="s">
+      <c r="P3" s="27"/>
+      <c r="U3" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="V3" s="29"/>
+      <c r="V3" s="27"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2" t="s">

--- a/workbooks/urbanization.xlsx
+++ b/workbooks/urbanization.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87E9A5E8-B0CA-4784-89AA-38743A1131AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3981196F-74B5-4C71-9BE8-CC5F13EF0D9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" firstSheet="5" activeTab="9" xr2:uid="{9806A3BC-D491-4476-99E9-37D3951075C7}"/>
+    <workbookView xWindow="63585" yWindow="1500" windowWidth="30300" windowHeight="18000" firstSheet="7" activeTab="17" xr2:uid="{9806A3BC-D491-4476-99E9-37D3951075C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -22,14 +22,15 @@
     <sheet name="RSFSR-1926" sheetId="4" r:id="rId7"/>
     <sheet name="RSFSR-1959" sheetId="6" r:id="rId8"/>
     <sheet name="RSFSR-1970" sheetId="8" r:id="rId9"/>
-    <sheet name="Итоги" sheetId="19" r:id="rId10"/>
-    <sheet name="RSFSR-1979" sheetId="10" r:id="rId11"/>
-    <sheet name="RSFSR-1989" sheetId="20" r:id="rId12"/>
-    <sheet name="MX-1930" sheetId="13" r:id="rId13"/>
+    <sheet name="RSFSR-1979" sheetId="10" r:id="rId10"/>
+    <sheet name="RSFSR-1989" sheetId="20" r:id="rId11"/>
+    <sheet name="MX-1930" sheetId="13" r:id="rId12"/>
+    <sheet name="MX-1950" sheetId="23" r:id="rId13"/>
     <sheet name="MX-1960" sheetId="14" r:id="rId14"/>
     <sheet name="MX-1970" sheetId="15" r:id="rId15"/>
     <sheet name="MX-1980" sheetId="22" r:id="rId16"/>
     <sheet name="MX-1990" sheetId="21" r:id="rId17"/>
+    <sheet name="Итоги" sheetId="19" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="137">
   <si>
     <t>от</t>
   </si>
@@ -409,6 +410,60 @@
   </si>
   <si>
     <t>Переписи Мексики 1940 и 1950 не собирали сведений о распределении населения по численности городов и посёлков.</t>
+  </si>
+  <si>
+    <t>MX-1950</t>
+  </si>
+  <si>
+    <t>INEGI, "Estadísticas históricas de México 2014", табл. 2.15</t>
+  </si>
+  <si>
+    <t>ниже 2,500</t>
+  </si>
+  <si>
+    <t>2500-5000</t>
+  </si>
+  <si>
+    <t>5000-15000</t>
+  </si>
+  <si>
+    <t>15000-20000</t>
+  </si>
+  <si>
+    <t>20-50 тыс</t>
+  </si>
+  <si>
+    <t>50-100 тыс</t>
+  </si>
+  <si>
+    <t>100-500 тыс</t>
+  </si>
+  <si>
+    <t>500 тыс и выше</t>
+  </si>
+  <si>
+    <t>По переписи</t>
+  </si>
+  <si>
+    <t>Предполагая то же распределение внутри 1-2500 в 1950, что и в 1960</t>
+  </si>
+  <si>
+    <t>% в 1960</t>
+  </si>
+  <si>
+    <t>в 1960</t>
+  </si>
+  <si>
+    <t>сумма</t>
+  </si>
+  <si>
+    <t>Оценка для 1950</t>
+  </si>
+  <si>
+    <t>Население в пунктах численностью 20000 жителей и выше</t>
+  </si>
+  <si>
+    <t>Население в пунктах численностью 100000 жителей и выше</t>
   </si>
 </sst>
 </file>
@@ -561,7 +616,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
+  <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
@@ -571,6 +626,7 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -627,13 +683,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="7">
     <cellStyle name="Comma 2" xfId="5" xr:uid="{2A5730CF-2000-4C9F-A914-E035B50DA721}"/>
     <cellStyle name="Euro" xfId="3" xr:uid="{13FA6C99-1DA1-4BDE-A330-70CA7E69198D}"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Hyperlink 2" xfId="4" xr:uid="{3B50002E-2B40-4A53-9A5A-330329E22FD3}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{7DDB2CAA-4EE4-4CED-9BCF-19D89D6652BE}"/>
+    <cellStyle name="Normal 2 2" xfId="6" xr:uid="{932A0CD9-754C-4CE4-8215-E4DF05526CBB}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -945,7 +1002,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BA24E3F-1F27-45F2-85D8-EE2D60E7DC98}">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="13.15625" customWidth="1"/>
@@ -1073,29 +1130,26 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="2" t="s">
-        <v>24</v>
+        <v>119</v>
       </c>
       <c r="B26" t="s">
-        <v>55</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="2"/>
+        <v>55</v>
+      </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="2" t="s">
-        <v>113</v>
+        <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>108</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -1103,34 +1157,45 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B32" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="2"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B34" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" t="s">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" t="s">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" t="s">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" t="s">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" t="s">
         <v>116</v>
       </c>
     </row>
@@ -1141,942 +1206,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2920F376-2D53-4EC0-B932-712BB7C94480}">
-  <dimension ref="A1:M66"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
-  <cols>
-    <col min="1" max="1" width="12.15625" customWidth="1"/>
-    <col min="3" max="3" width="11.15625" customWidth="1"/>
-    <col min="4" max="4" width="11.41796875" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="10.15625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="9.83984375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="M1" s="16"/>
-    </row>
-    <row r="2" spans="1:13" ht="18.3" x14ac:dyDescent="0.7">
-      <c r="A2" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="M3" s="16"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="C4" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="M4" s="16"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="B5" s="14">
-        <v>1930</v>
-      </c>
-      <c r="C5" s="3">
-        <v>37.200000000000003</v>
-      </c>
-      <c r="D5" s="3">
-        <v>36</v>
-      </c>
-      <c r="E5" s="3">
-        <v>32.6</v>
-      </c>
-      <c r="K5" s="3">
-        <f>E5-C5</f>
-        <v>-4.6000000000000014</v>
-      </c>
-      <c r="M5" s="16">
-        <f>E5/C5</f>
-        <v>0.87634408602150538</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="14">
-        <v>1960</v>
-      </c>
-      <c r="C6" s="3">
-        <v>53.8</v>
-      </c>
-      <c r="D6" s="3">
-        <v>57.2</v>
-      </c>
-      <c r="E6" s="3">
-        <v>60.4</v>
-      </c>
-      <c r="K6" s="3">
-        <f>E6-C6</f>
-        <v>6.6000000000000014</v>
-      </c>
-      <c r="M6" s="16">
-        <f>E6/C6</f>
-        <v>1.1226765799256506</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="14">
-        <v>1970</v>
-      </c>
-      <c r="C7" s="3">
-        <v>61.7</v>
-      </c>
-      <c r="D7" s="3">
-        <v>65.7</v>
-      </c>
-      <c r="E7" s="3">
-        <v>69.7</v>
-      </c>
-      <c r="K7" s="3">
-        <f>E7-C7</f>
-        <v>8</v>
-      </c>
-      <c r="M7" s="16">
-        <f>E7/C7</f>
-        <v>1.1296596434359805</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="B8" s="14">
-        <v>1980</v>
-      </c>
-      <c r="C8" s="3">
-        <v>68.8</v>
-      </c>
-      <c r="D8" s="3">
-        <v>67.400000000000006</v>
-      </c>
-      <c r="E8" s="3">
-        <v>67.400000000000006</v>
-      </c>
-      <c r="K8" s="3">
-        <f>E8-C8</f>
-        <v>-1.3999999999999915</v>
-      </c>
-      <c r="M8" s="16">
-        <f>E8/C8</f>
-        <v>0.97965116279069775</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="B9" s="14">
-        <v>1990</v>
-      </c>
-      <c r="C9" s="3">
-        <v>73.400000000000006</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3">
-        <v>73</v>
-      </c>
-      <c r="K9" s="3">
-        <f>E9-C9</f>
-        <v>-0.40000000000000568</v>
-      </c>
-      <c r="M9" s="16">
-        <f>E9/C9</f>
-        <v>0.99455040871934597</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="M10" s="16"/>
-    </row>
-    <row r="11" spans="1:13" ht="18.3" x14ac:dyDescent="0.7">
-      <c r="A11" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="M11" s="16"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="M12" s="16"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="C13" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="M13" s="16"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="B14" s="14">
-        <v>1930</v>
-      </c>
-      <c r="C14" s="3">
-        <v>25.6</v>
-      </c>
-      <c r="D14" s="3">
-        <v>21.7</v>
-      </c>
-      <c r="E14" s="3">
-        <v>20.5</v>
-      </c>
-      <c r="K14" s="3">
-        <f>E14-C14</f>
-        <v>-5.1000000000000014</v>
-      </c>
-      <c r="M14" s="16">
-        <f t="shared" ref="M14:M16" si="0">E14/C14</f>
-        <v>0.80078125</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B15" s="14">
-        <v>1960</v>
-      </c>
-      <c r="C15" s="3">
-        <v>42.2</v>
-      </c>
-      <c r="D15" s="3">
-        <v>47.8</v>
-      </c>
-      <c r="E15" s="3">
-        <v>52.9</v>
-      </c>
-      <c r="K15" s="3">
-        <f>E15-C15</f>
-        <v>10.699999999999996</v>
-      </c>
-      <c r="M15" s="16">
-        <f t="shared" si="0"/>
-        <v>1.2535545023696681</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="14">
-        <v>1970</v>
-      </c>
-      <c r="C16" s="3">
-        <v>50.1</v>
-      </c>
-      <c r="D16" s="3">
-        <v>56.4</v>
-      </c>
-      <c r="E16" s="3">
-        <v>62.6</v>
-      </c>
-      <c r="K16" s="3">
-        <f>E16-C16</f>
-        <v>12.5</v>
-      </c>
-      <c r="M16" s="16">
-        <f t="shared" si="0"/>
-        <v>1.2495009980039919</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="B17" s="14">
-        <v>1980</v>
-      </c>
-      <c r="C17" s="3">
-        <v>60.3</v>
-      </c>
-      <c r="D17" s="3">
-        <v>65</v>
-      </c>
-      <c r="E17" s="3">
-        <v>66.900000000000006</v>
-      </c>
-      <c r="K17" s="3">
-        <f>E17-C17</f>
-        <v>6.6000000000000085</v>
-      </c>
-      <c r="M17" s="16">
-        <f t="shared" ref="M17:M18" si="1">E17/C17</f>
-        <v>1.1094527363184081</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="B18" s="14">
-        <v>1990</v>
-      </c>
-      <c r="C18" s="3">
-        <v>65.599999999999994</v>
-      </c>
-      <c r="E18" s="3">
-        <v>71.099999999999994</v>
-      </c>
-      <c r="K18" s="3">
-        <f>E18-C18</f>
-        <v>5.5</v>
-      </c>
-      <c r="M18" s="16">
-        <f t="shared" si="1"/>
-        <v>1.0838414634146341</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="18.3" x14ac:dyDescent="0.7">
-      <c r="A20" s="11" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="C21" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="B22" s="14">
-        <v>1930</v>
-      </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3">
-        <v>12.1</v>
-      </c>
-      <c r="E22" s="3">
-        <v>11.8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B23" s="14">
-        <v>1960</v>
-      </c>
-      <c r="C23" s="3">
-        <v>29.6</v>
-      </c>
-      <c r="D23" s="3">
-        <v>35.6</v>
-      </c>
-      <c r="E23" s="3">
-        <v>41</v>
-      </c>
-      <c r="K23" s="3">
-        <f>E23-C23</f>
-        <v>11.399999999999999</v>
-      </c>
-      <c r="M23" s="16">
-        <f t="shared" ref="M23:M24" si="2">E23/C23</f>
-        <v>1.3851351351351351</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="B24" s="14">
-        <v>1970</v>
-      </c>
-      <c r="C24" s="3">
-        <v>35.299999999999997</v>
-      </c>
-      <c r="D24" s="3">
-        <v>44.3</v>
-      </c>
-      <c r="E24" s="3">
-        <v>50.8</v>
-      </c>
-      <c r="K24" s="3">
-        <f>E24-C24</f>
-        <v>15.5</v>
-      </c>
-      <c r="M24" s="16">
-        <f t="shared" si="2"/>
-        <v>1.4390934844192635</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="B25" s="14">
-        <v>1980</v>
-      </c>
-      <c r="C25" s="3">
-        <v>49.9</v>
-      </c>
-      <c r="D25" s="3">
-        <v>54.9</v>
-      </c>
-      <c r="E25" s="15">
-        <v>58</v>
-      </c>
-      <c r="K25" s="3">
-        <f>E25-C25</f>
-        <v>8.1000000000000014</v>
-      </c>
-      <c r="M25" s="16">
-        <f t="shared" ref="M25:M26" si="3">E25/C25</f>
-        <v>1.1623246492985972</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="B26" s="14">
-        <v>1990</v>
-      </c>
-      <c r="C26" s="3">
-        <v>55.4</v>
-      </c>
-      <c r="D26" s="3"/>
-      <c r="E26" s="15">
-        <v>61.9</v>
-      </c>
-      <c r="K26" s="3">
-        <f>E26-C26</f>
-        <v>6.5</v>
-      </c>
-      <c r="M26" s="16">
-        <f t="shared" si="3"/>
-        <v>1.1173285198555958</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="B27" s="14"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="15"/>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-    </row>
-    <row r="29" spans="1:13" ht="18.3" x14ac:dyDescent="0.7">
-      <c r="A29" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="C30" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="D30" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="E30" s="17" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="B31" s="14">
-        <v>1930</v>
-      </c>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3">
-        <v>6.5</v>
-      </c>
-      <c r="E31" s="3">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B32" s="14">
-        <v>1960</v>
-      </c>
-      <c r="C32" s="3">
-        <v>18.600000000000001</v>
-      </c>
-      <c r="D32" s="3">
-        <v>23.3</v>
-      </c>
-      <c r="E32" s="3">
-        <v>27</v>
-      </c>
-      <c r="K32" s="3">
-        <f>E32-C32</f>
-        <v>8.3999999999999986</v>
-      </c>
-      <c r="M32" s="16">
-        <f t="shared" ref="M32:M33" si="4">E32/C32</f>
-        <v>1.4516129032258063</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="B33" s="14">
-        <v>1970</v>
-      </c>
-      <c r="C33" s="3">
-        <v>23.3</v>
-      </c>
-      <c r="D33" s="3">
-        <v>31.2</v>
-      </c>
-      <c r="E33" s="3">
-        <v>35.799999999999997</v>
-      </c>
-      <c r="K33" s="3">
-        <f>E33-C33</f>
-        <v>12.499999999999996</v>
-      </c>
-      <c r="M33" s="16">
-        <f t="shared" si="4"/>
-        <v>1.5364806866952787</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="B34" s="14">
-        <v>1980</v>
-      </c>
-      <c r="C34" s="3">
-        <v>40.9</v>
-      </c>
-      <c r="D34" s="3">
-        <v>40.4</v>
-      </c>
-      <c r="E34" s="15">
-        <v>42.7</v>
-      </c>
-      <c r="K34" s="3">
-        <f>E34-C34</f>
-        <v>1.8000000000000043</v>
-      </c>
-      <c r="M34" s="16">
-        <f t="shared" ref="M34:M35" si="5">E34/C34</f>
-        <v>1.0440097799511003</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="B35" s="14">
-        <v>1990</v>
-      </c>
-      <c r="C35" s="3">
-        <v>44.4</v>
-      </c>
-      <c r="D35" s="3"/>
-      <c r="E35" s="15">
-        <v>45.7</v>
-      </c>
-      <c r="K35" s="3">
-        <f>E35-C35</f>
-        <v>1.3000000000000043</v>
-      </c>
-      <c r="M35" s="16">
-        <f t="shared" si="5"/>
-        <v>1.0292792792792793</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="18.3" x14ac:dyDescent="0.7">
-      <c r="A38" s="11" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="C40" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="H40" s="27"/>
-      <c r="I40" s="27"/>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" t="s">
-        <v>77</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="F41" s="2"/>
-      <c r="G41" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="H41" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I41" s="7" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="14">
-        <v>1897</v>
-      </c>
-      <c r="E42">
-        <v>15</v>
-      </c>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42">
-        <v>14.7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="14">
-        <v>1913</v>
-      </c>
-      <c r="E43">
-        <v>18</v>
-      </c>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="14">
-        <v>1920</v>
-      </c>
-      <c r="E44">
-        <v>15</v>
-      </c>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44">
-        <v>14.2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="14">
-        <v>1926</v>
-      </c>
-      <c r="E45">
-        <v>17.899999999999999</v>
-      </c>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45">
-        <v>17.3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="14">
-        <v>1937</v>
-      </c>
-      <c r="C46" s="1">
-        <v>162039470</v>
-      </c>
-      <c r="D46" s="1">
-        <v>51949458</v>
-      </c>
-      <c r="E46">
-        <v>31.2</v>
-      </c>
-      <c r="G46" s="1">
-        <v>103967924</v>
-      </c>
-      <c r="H46" s="1">
-        <v>34373245</v>
-      </c>
-      <c r="I46" s="18">
-        <f>H46/G46*100</f>
-        <v>33.061394012253245</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="C47" s="3">
-        <f>C46/1000000</f>
-        <v>162.03946999999999</v>
-      </c>
-      <c r="D47" s="3">
-        <v>43.7</v>
-      </c>
-      <c r="E47" s="3">
-        <f>D47/C47*100</f>
-        <v>26.968737925395587</v>
-      </c>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3">
-        <f>G46/1000000</f>
-        <v>103.967924</v>
-      </c>
-      <c r="H47" s="3">
-        <v>30</v>
-      </c>
-      <c r="I47" s="3">
-        <f>H47/G47*100</f>
-        <v>28.855053410511495</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="14">
-        <v>1939</v>
-      </c>
-      <c r="C48" s="1">
-        <v>190677890</v>
-      </c>
-      <c r="D48" s="1">
-        <v>60409216</v>
-      </c>
-      <c r="E48" s="3">
-        <f>D48/C48*100</f>
-        <v>31.681290368799448</v>
-      </c>
-      <c r="G48" s="1">
-        <v>108377210</v>
-      </c>
-      <c r="H48" s="1">
-        <v>36295552</v>
-      </c>
-      <c r="I48" s="18">
-        <f>H48/G48*100</f>
-        <v>33.490022487200036</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="C49">
-        <v>167.65</v>
-      </c>
-      <c r="D49">
-        <v>47.5</v>
-      </c>
-      <c r="E49" s="3">
-        <f>D49/C49*100</f>
-        <v>28.332836266030419</v>
-      </c>
-      <c r="G49" s="18">
-        <v>106.9</v>
-      </c>
-      <c r="H49" s="18">
-        <v>33.700000000000003</v>
-      </c>
-      <c r="I49" s="18">
-        <f>H49/G49*100</f>
-        <v>31.524789522918617</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="14">
-        <v>1959</v>
-      </c>
-      <c r="C50" s="1">
-        <v>208826650</v>
-      </c>
-      <c r="D50" s="1">
-        <v>99977695</v>
-      </c>
-      <c r="E50" s="3">
-        <f t="shared" ref="E50:E53" si="6">D50/C50*100</f>
-        <v>47.875927234383155</v>
-      </c>
-      <c r="G50" s="1">
-        <v>117534306</v>
-      </c>
-      <c r="H50" s="1">
-        <v>61611074</v>
-      </c>
-      <c r="I50" s="18">
-        <f t="shared" ref="I50:I53" si="7">H50/G50*100</f>
-        <v>52.419651841905633</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="14">
-        <v>1970</v>
-      </c>
-      <c r="C51" s="1">
-        <v>241720134</v>
-      </c>
-      <c r="D51" s="1">
-        <v>135991514</v>
-      </c>
-      <c r="E51" s="3">
-        <f t="shared" si="6"/>
-        <v>56.259903446851482</v>
-      </c>
-      <c r="G51" s="1">
-        <v>130079210</v>
-      </c>
-      <c r="H51" s="1">
-        <v>80981143</v>
-      </c>
-      <c r="I51" s="18">
-        <f t="shared" si="7"/>
-        <v>62.255254317734554</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="14">
-        <v>1979</v>
-      </c>
-      <c r="C52" s="1">
-        <v>262436227</v>
-      </c>
-      <c r="D52" s="1">
-        <v>163585914</v>
-      </c>
-      <c r="E52" s="3">
-        <f t="shared" si="6"/>
-        <v>62.333587047035245</v>
-      </c>
-      <c r="G52" s="1">
-        <v>137550949</v>
-      </c>
-      <c r="H52" s="1">
-        <v>95373867</v>
-      </c>
-      <c r="I52" s="18">
-        <f t="shared" si="7"/>
-        <v>69.337120313143018</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="14">
-        <v>1989</v>
-      </c>
-      <c r="C53" s="1">
-        <v>286731</v>
-      </c>
-      <c r="D53" s="1">
-        <v>188814</v>
-      </c>
-      <c r="E53" s="3">
-        <f t="shared" si="6"/>
-        <v>65.850570744007456</v>
-      </c>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1">
-        <v>147400</v>
-      </c>
-      <c r="H53" s="1">
-        <v>108425</v>
-      </c>
-      <c r="I53" s="18">
-        <f t="shared" si="7"/>
-        <v>73.558344640434186</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="B56" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="B57" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="B60" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="B62" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="B64" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B65" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B66" t="s">
-        <v>102</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="G40:I40"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D70B758-2D8E-4D0F-9152-375389941F4D}">
   <dimension ref="A1:M37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
@@ -2507,7 +1636,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBE7E47A-F406-4131-8275-CA858AD6FB0F}">
   <dimension ref="A1:AA40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
@@ -3075,7 +2204,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD1CEBF5-B4BD-4DD1-AC0A-66E7B41EFED5}">
   <dimension ref="A2:H38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
@@ -3376,6 +2505,517 @@
       <c r="D38" s="12">
         <f>D37/D16 * 100</f>
         <v>49.957662552418867</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26B1A78D-D0DF-4D29-8FEE-3CBA1F2AAB01}">
+  <dimension ref="A1:M55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="13.734375" customWidth="1"/>
+    <col min="2" max="2" width="10.578125" customWidth="1"/>
+    <col min="12" max="12" width="9.62890625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.26171875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="18.3" x14ac:dyDescent="0.7">
+      <c r="A1" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="I1" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="18.3" x14ac:dyDescent="0.7">
+      <c r="I2" s="19"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B3" s="1">
+        <v>14790299</v>
+      </c>
+      <c r="I3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" s="1"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B5" s="1">
+        <v>2063467</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="M5" s="14" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1472397</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>100</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1558268</v>
+      </c>
+      <c r="M6" s="3">
+        <f>L6/L$12*100</f>
+        <v>9.0502207252626334</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1281299</v>
+      </c>
+      <c r="I7">
+        <v>100</v>
+      </c>
+      <c r="J7">
+        <v>500</v>
+      </c>
+      <c r="L7" s="1">
+        <v>6410224</v>
+      </c>
+      <c r="M7" s="3">
+        <f t="shared" ref="M7:M10" si="0">L7/L$12*100</f>
+        <v>37.229759000618593</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" s="1">
+        <v>1258428</v>
+      </c>
+      <c r="I8">
+        <v>500</v>
+      </c>
+      <c r="J8" s="1">
+        <v>1000</v>
+      </c>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1">
+        <v>4253855</v>
+      </c>
+      <c r="M8" s="3">
+        <f t="shared" si="0"/>
+        <v>24.705844362627019</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B9" s="1">
+        <v>725296</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J9" s="1">
+        <v>2000</v>
+      </c>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1">
+        <v>3905365</v>
+      </c>
+      <c r="M9" s="3">
+        <f t="shared" si="0"/>
+        <v>22.681859129954095</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B10" s="1">
+        <v>1406204</v>
+      </c>
+      <c r="I10" s="1">
+        <v>2000</v>
+      </c>
+      <c r="J10" s="1">
+        <v>2500</v>
+      </c>
+      <c r="L10" s="1">
+        <v>1090299</v>
+      </c>
+      <c r="M10" s="3">
+        <f t="shared" si="0"/>
+        <v>6.3323167815376582</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>128</v>
+      </c>
+      <c r="B11" s="1">
+        <v>2234795</v>
+      </c>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="1">
+        <v>25791017</v>
+      </c>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="L12" s="1">
+        <f>SUM(L6:L10)</f>
+        <v>17218011</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="I15" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="I16" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="9:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="I17" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="J17" s="1">
+        <v>100</v>
+      </c>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1">
+        <f>M6*$B$3/100</f>
+        <v>1338554.7054263121</v>
+      </c>
+    </row>
+    <row r="18" spans="9:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="I18" s="1">
+        <v>100</v>
+      </c>
+      <c r="J18" s="1">
+        <v>500</v>
+      </c>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1">
+        <f t="shared" ref="L18:L21" si="1">M7*$B$3/100</f>
+        <v>5506392.6731709018</v>
+      </c>
+    </row>
+    <row r="19" spans="9:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="I19" s="1">
+        <v>500</v>
+      </c>
+      <c r="J19" s="1">
+        <v>1000</v>
+      </c>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1">
+        <f t="shared" si="1"/>
+        <v>3654068.2517071799</v>
+      </c>
+    </row>
+    <row r="20" spans="9:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="I20" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J20" s="1">
+        <v>2000</v>
+      </c>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1">
+        <f t="shared" si="1"/>
+        <v>3354714.7840790092</v>
+      </c>
+    </row>
+    <row r="21" spans="9:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="I21" s="1">
+        <v>2000</v>
+      </c>
+      <c r="J21" s="1">
+        <v>2500</v>
+      </c>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1">
+        <f t="shared" si="1"/>
+        <v>936568.58561659651</v>
+      </c>
+    </row>
+    <row r="22" spans="9:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="I22" s="1">
+        <v>2500</v>
+      </c>
+      <c r="J22" s="1">
+        <v>5000</v>
+      </c>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1">
+        <f>B5</f>
+        <v>2063467</v>
+      </c>
+    </row>
+    <row r="23" spans="9:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="I23" s="1">
+        <v>5000</v>
+      </c>
+      <c r="J23" s="1">
+        <v>15000</v>
+      </c>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1">
+        <f t="shared" ref="L23:L28" si="2">B6</f>
+        <v>1472397</v>
+      </c>
+    </row>
+    <row r="24" spans="9:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="I24" s="1">
+        <v>15000</v>
+      </c>
+      <c r="J24" s="1">
+        <v>20000</v>
+      </c>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1">
+        <f t="shared" si="2"/>
+        <v>1281299</v>
+      </c>
+    </row>
+    <row r="25" spans="9:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="I25" s="1">
+        <v>20000</v>
+      </c>
+      <c r="J25" s="1">
+        <v>50000</v>
+      </c>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1">
+        <f t="shared" si="2"/>
+        <v>1258428</v>
+      </c>
+    </row>
+    <row r="26" spans="9:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="I26" s="1">
+        <v>50000</v>
+      </c>
+      <c r="J26" s="1">
+        <v>100000</v>
+      </c>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1">
+        <f t="shared" si="2"/>
+        <v>725296</v>
+      </c>
+    </row>
+    <row r="27" spans="9:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="I27" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J27" s="1">
+        <v>500000</v>
+      </c>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1">
+        <f t="shared" si="2"/>
+        <v>1406204</v>
+      </c>
+    </row>
+    <row r="28" spans="9:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="I28" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1">
+        <f t="shared" si="2"/>
+        <v>2234795</v>
+      </c>
+    </row>
+    <row r="30" spans="9:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="J30" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L30" s="1">
+        <f>B12</f>
+        <v>25791017</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="18.3" x14ac:dyDescent="0.7">
+      <c r="A33" s="11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="J34" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="L34" s="1">
+        <f>SUM(L20:L28)</f>
+        <v>14733169.369695606</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="J35" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L35" s="12">
+        <f>L34/L30*100</f>
+        <v>57.12519738828292</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="18.3" x14ac:dyDescent="0.7">
+      <c r="A37" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="J38" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="L38" s="1">
+        <f>SUM(L21:L28)</f>
+        <v>11378454.585616596</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="J39" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L39" s="12">
+        <f>L38/L30*100</f>
+        <v>44.117898048055245</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="18.3" x14ac:dyDescent="0.7">
+      <c r="A41" s="11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="J42" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="L42" s="1">
+        <f>SUM(L22:L28)</f>
+        <v>10441886</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="J43" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L43" s="12">
+        <f>L42/L30*100</f>
+        <v>40.48652288508049</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="18.3" x14ac:dyDescent="0.7">
+      <c r="A45" s="11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="J46" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="L46" s="1">
+        <f>SUM(L23:L28)</f>
+        <v>8378419</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="J47" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L47" s="12">
+        <f>L46/L30*100</f>
+        <v>32.48580309958308</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="18.3" x14ac:dyDescent="0.7">
+      <c r="A49" s="11" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="J50" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="L50" s="1">
+        <f>SUM(L25:L28)</f>
+        <v>5624723</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="J51" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L51" s="12">
+        <f>L50/L30*100</f>
+        <v>21.808845304549255</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="18.3" x14ac:dyDescent="0.7">
+      <c r="A53" s="11" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="J54" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="L54" s="1">
+        <f>SUM(L27:L28)</f>
+        <v>3640999</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="J55" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L55" s="12">
+        <f>L54/L30*100</f>
+        <v>14.117314567316209</v>
       </c>
     </row>
   </sheetData>
@@ -5571,6 +5211,942 @@
   <ignoredErrors>
     <ignoredError sqref="D25 D30 D35 D40 D45 D50" formulaRange="1"/>
   </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2920F376-2D53-4EC0-B932-712BB7C94480}">
+  <dimension ref="A1:M66"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="12.15625" customWidth="1"/>
+    <col min="3" max="3" width="11.15625" customWidth="1"/>
+    <col min="4" max="4" width="11.41796875" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="6" width="10.15625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="9.83984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="M1" s="16"/>
+    </row>
+    <row r="2" spans="1:13" ht="18.3" x14ac:dyDescent="0.7">
+      <c r="A2" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="M3" s="16"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="C4" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" s="16"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="14">
+        <v>1930</v>
+      </c>
+      <c r="C5" s="3">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="D5" s="3">
+        <v>36</v>
+      </c>
+      <c r="E5" s="3">
+        <v>32.6</v>
+      </c>
+      <c r="K5" s="3">
+        <f>E5-C5</f>
+        <v>-4.6000000000000014</v>
+      </c>
+      <c r="M5" s="16">
+        <f>E5/C5</f>
+        <v>0.87634408602150538</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="14">
+        <v>1960</v>
+      </c>
+      <c r="C6" s="3">
+        <v>53.8</v>
+      </c>
+      <c r="D6" s="3">
+        <v>57.2</v>
+      </c>
+      <c r="E6" s="3">
+        <v>60.4</v>
+      </c>
+      <c r="K6" s="3">
+        <f>E6-C6</f>
+        <v>6.6000000000000014</v>
+      </c>
+      <c r="M6" s="16">
+        <f>E6/C6</f>
+        <v>1.1226765799256506</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="14">
+        <v>1970</v>
+      </c>
+      <c r="C7" s="3">
+        <v>61.7</v>
+      </c>
+      <c r="D7" s="3">
+        <v>65.7</v>
+      </c>
+      <c r="E7" s="3">
+        <v>69.7</v>
+      </c>
+      <c r="K7" s="3">
+        <f>E7-C7</f>
+        <v>8</v>
+      </c>
+      <c r="M7" s="16">
+        <f>E7/C7</f>
+        <v>1.1296596434359805</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="14">
+        <v>1980</v>
+      </c>
+      <c r="C8" s="3">
+        <v>68.8</v>
+      </c>
+      <c r="D8" s="3">
+        <v>67.400000000000006</v>
+      </c>
+      <c r="E8" s="3">
+        <v>67.400000000000006</v>
+      </c>
+      <c r="K8" s="3">
+        <f>E8-C8</f>
+        <v>-1.3999999999999915</v>
+      </c>
+      <c r="M8" s="16">
+        <f>E8/C8</f>
+        <v>0.97965116279069775</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="14">
+        <v>1990</v>
+      </c>
+      <c r="C9" s="3">
+        <v>73.400000000000006</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3">
+        <v>73</v>
+      </c>
+      <c r="K9" s="3">
+        <f>E9-C9</f>
+        <v>-0.40000000000000568</v>
+      </c>
+      <c r="M9" s="16">
+        <f>E9/C9</f>
+        <v>0.99455040871934597</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="M10" s="16"/>
+    </row>
+    <row r="11" spans="1:13" ht="18.3" x14ac:dyDescent="0.7">
+      <c r="A11" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M11" s="16"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="M12" s="16"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="C13" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="M13" s="16"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="14">
+        <v>1930</v>
+      </c>
+      <c r="C14" s="3">
+        <v>25.6</v>
+      </c>
+      <c r="D14" s="3">
+        <v>21.7</v>
+      </c>
+      <c r="E14" s="3">
+        <v>20.5</v>
+      </c>
+      <c r="K14" s="3">
+        <f>E14-C14</f>
+        <v>-5.1000000000000014</v>
+      </c>
+      <c r="M14" s="16">
+        <f t="shared" ref="M14:M16" si="0">E14/C14</f>
+        <v>0.80078125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" s="14">
+        <v>1960</v>
+      </c>
+      <c r="C15" s="3">
+        <v>42.2</v>
+      </c>
+      <c r="D15" s="3">
+        <v>47.8</v>
+      </c>
+      <c r="E15" s="3">
+        <v>52.9</v>
+      </c>
+      <c r="K15" s="3">
+        <f>E15-C15</f>
+        <v>10.699999999999996</v>
+      </c>
+      <c r="M15" s="16">
+        <f t="shared" si="0"/>
+        <v>1.2535545023696681</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" s="14">
+        <v>1970</v>
+      </c>
+      <c r="C16" s="3">
+        <v>50.1</v>
+      </c>
+      <c r="D16" s="3">
+        <v>56.4</v>
+      </c>
+      <c r="E16" s="3">
+        <v>62.6</v>
+      </c>
+      <c r="K16" s="3">
+        <f>E16-C16</f>
+        <v>12.5</v>
+      </c>
+      <c r="M16" s="16">
+        <f t="shared" si="0"/>
+        <v>1.2495009980039919</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" s="14">
+        <v>1980</v>
+      </c>
+      <c r="C17" s="3">
+        <v>60.3</v>
+      </c>
+      <c r="D17" s="3">
+        <v>65</v>
+      </c>
+      <c r="E17" s="3">
+        <v>66.900000000000006</v>
+      </c>
+      <c r="K17" s="3">
+        <f>E17-C17</f>
+        <v>6.6000000000000085</v>
+      </c>
+      <c r="M17" s="16">
+        <f t="shared" ref="M17:M18" si="1">E17/C17</f>
+        <v>1.1094527363184081</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" s="14">
+        <v>1990</v>
+      </c>
+      <c r="C18" s="3">
+        <v>65.599999999999994</v>
+      </c>
+      <c r="E18" s="3">
+        <v>71.099999999999994</v>
+      </c>
+      <c r="K18" s="3">
+        <f>E18-C18</f>
+        <v>5.5</v>
+      </c>
+      <c r="M18" s="16">
+        <f t="shared" si="1"/>
+        <v>1.0838414634146341</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="18.3" x14ac:dyDescent="0.7">
+      <c r="A20" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="C21" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" s="14">
+        <v>1930</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3">
+        <v>12.1</v>
+      </c>
+      <c r="E22" s="3">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" s="14">
+        <v>1960</v>
+      </c>
+      <c r="C23" s="3">
+        <v>29.6</v>
+      </c>
+      <c r="D23" s="3">
+        <v>35.6</v>
+      </c>
+      <c r="E23" s="3">
+        <v>41</v>
+      </c>
+      <c r="K23" s="3">
+        <f>E23-C23</f>
+        <v>11.399999999999999</v>
+      </c>
+      <c r="M23" s="16">
+        <f t="shared" ref="M23:M24" si="2">E23/C23</f>
+        <v>1.3851351351351351</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="B24" s="14">
+        <v>1970</v>
+      </c>
+      <c r="C24" s="3">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="D24" s="3">
+        <v>44.3</v>
+      </c>
+      <c r="E24" s="3">
+        <v>50.8</v>
+      </c>
+      <c r="K24" s="3">
+        <f>E24-C24</f>
+        <v>15.5</v>
+      </c>
+      <c r="M24" s="16">
+        <f t="shared" si="2"/>
+        <v>1.4390934844192635</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B25" s="14">
+        <v>1980</v>
+      </c>
+      <c r="C25" s="3">
+        <v>49.9</v>
+      </c>
+      <c r="D25" s="3">
+        <v>54.9</v>
+      </c>
+      <c r="E25" s="15">
+        <v>58</v>
+      </c>
+      <c r="K25" s="3">
+        <f>E25-C25</f>
+        <v>8.1000000000000014</v>
+      </c>
+      <c r="M25" s="16">
+        <f t="shared" ref="M25:M26" si="3">E25/C25</f>
+        <v>1.1623246492985972</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B26" s="14">
+        <v>1990</v>
+      </c>
+      <c r="C26" s="3">
+        <v>55.4</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="15">
+        <v>61.9</v>
+      </c>
+      <c r="K26" s="3">
+        <f>E26-C26</f>
+        <v>6.5</v>
+      </c>
+      <c r="M26" s="16">
+        <f t="shared" si="3"/>
+        <v>1.1173285198555958</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="B27" s="14"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="15"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+    </row>
+    <row r="29" spans="1:13" ht="18.3" x14ac:dyDescent="0.7">
+      <c r="A29" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="C30" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B31" s="14">
+        <v>1930</v>
+      </c>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="E31" s="3">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B32" s="14">
+        <v>1960</v>
+      </c>
+      <c r="C32" s="3">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="D32" s="3">
+        <v>23.3</v>
+      </c>
+      <c r="E32" s="3">
+        <v>27</v>
+      </c>
+      <c r="K32" s="3">
+        <f>E32-C32</f>
+        <v>8.3999999999999986</v>
+      </c>
+      <c r="M32" s="16">
+        <f t="shared" ref="M32:M33" si="4">E32/C32</f>
+        <v>1.4516129032258063</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="B33" s="14">
+        <v>1970</v>
+      </c>
+      <c r="C33" s="3">
+        <v>23.3</v>
+      </c>
+      <c r="D33" s="3">
+        <v>31.2</v>
+      </c>
+      <c r="E33" s="3">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="K33" s="3">
+        <f>E33-C33</f>
+        <v>12.499999999999996</v>
+      </c>
+      <c r="M33" s="16">
+        <f t="shared" si="4"/>
+        <v>1.5364806866952787</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B34" s="14">
+        <v>1980</v>
+      </c>
+      <c r="C34" s="3">
+        <v>40.9</v>
+      </c>
+      <c r="D34" s="3">
+        <v>40.4</v>
+      </c>
+      <c r="E34" s="15">
+        <v>42.7</v>
+      </c>
+      <c r="K34" s="3">
+        <f>E34-C34</f>
+        <v>1.8000000000000043</v>
+      </c>
+      <c r="M34" s="16">
+        <f t="shared" ref="M34:M35" si="5">E34/C34</f>
+        <v>1.0440097799511003</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B35" s="14">
+        <v>1990</v>
+      </c>
+      <c r="C35" s="3">
+        <v>44.4</v>
+      </c>
+      <c r="D35" s="3"/>
+      <c r="E35" s="15">
+        <v>45.7</v>
+      </c>
+      <c r="K35" s="3">
+        <f>E35-C35</f>
+        <v>1.3000000000000043</v>
+      </c>
+      <c r="M35" s="16">
+        <f t="shared" si="5"/>
+        <v>1.0292792792792793</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="18.3" x14ac:dyDescent="0.7">
+      <c r="A38" s="11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="C40" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="H40" s="27"/>
+      <c r="I40" s="27"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" t="s">
+        <v>77</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F41" s="2"/>
+      <c r="G41" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="14">
+        <v>1897</v>
+      </c>
+      <c r="E42">
+        <v>15</v>
+      </c>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="14">
+        <v>1913</v>
+      </c>
+      <c r="E43">
+        <v>18</v>
+      </c>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="14">
+        <v>1920</v>
+      </c>
+      <c r="E44">
+        <v>15</v>
+      </c>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="14">
+        <v>1926</v>
+      </c>
+      <c r="E45">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="14">
+        <v>1937</v>
+      </c>
+      <c r="C46" s="1">
+        <v>162039470</v>
+      </c>
+      <c r="D46" s="1">
+        <v>51949458</v>
+      </c>
+      <c r="E46">
+        <v>31.2</v>
+      </c>
+      <c r="G46" s="1">
+        <v>103967924</v>
+      </c>
+      <c r="H46" s="1">
+        <v>34373245</v>
+      </c>
+      <c r="I46" s="18">
+        <f>H46/G46*100</f>
+        <v>33.061394012253245</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C47" s="3">
+        <f>C46/1000000</f>
+        <v>162.03946999999999</v>
+      </c>
+      <c r="D47" s="3">
+        <v>43.7</v>
+      </c>
+      <c r="E47" s="3">
+        <f>D47/C47*100</f>
+        <v>26.968737925395587</v>
+      </c>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3">
+        <f>G46/1000000</f>
+        <v>103.967924</v>
+      </c>
+      <c r="H47" s="3">
+        <v>30</v>
+      </c>
+      <c r="I47" s="3">
+        <f>H47/G47*100</f>
+        <v>28.855053410511495</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="14">
+        <v>1939</v>
+      </c>
+      <c r="C48" s="1">
+        <v>190677890</v>
+      </c>
+      <c r="D48" s="1">
+        <v>60409216</v>
+      </c>
+      <c r="E48" s="3">
+        <f>D48/C48*100</f>
+        <v>31.681290368799448</v>
+      </c>
+      <c r="G48" s="1">
+        <v>108377210</v>
+      </c>
+      <c r="H48" s="1">
+        <v>36295552</v>
+      </c>
+      <c r="I48" s="18">
+        <f>H48/G48*100</f>
+        <v>33.490022487200036</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C49">
+        <v>167.65</v>
+      </c>
+      <c r="D49">
+        <v>47.5</v>
+      </c>
+      <c r="E49" s="3">
+        <f>D49/C49*100</f>
+        <v>28.332836266030419</v>
+      </c>
+      <c r="G49" s="18">
+        <v>106.9</v>
+      </c>
+      <c r="H49" s="18">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="I49" s="18">
+        <f>H49/G49*100</f>
+        <v>31.524789522918617</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="14">
+        <v>1959</v>
+      </c>
+      <c r="C50" s="1">
+        <v>208826650</v>
+      </c>
+      <c r="D50" s="1">
+        <v>99977695</v>
+      </c>
+      <c r="E50" s="3">
+        <f t="shared" ref="E50:E53" si="6">D50/C50*100</f>
+        <v>47.875927234383155</v>
+      </c>
+      <c r="G50" s="1">
+        <v>117534306</v>
+      </c>
+      <c r="H50" s="1">
+        <v>61611074</v>
+      </c>
+      <c r="I50" s="18">
+        <f t="shared" ref="I50:I53" si="7">H50/G50*100</f>
+        <v>52.419651841905633</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="14">
+        <v>1970</v>
+      </c>
+      <c r="C51" s="1">
+        <v>241720134</v>
+      </c>
+      <c r="D51" s="1">
+        <v>135991514</v>
+      </c>
+      <c r="E51" s="3">
+        <f t="shared" si="6"/>
+        <v>56.259903446851482</v>
+      </c>
+      <c r="G51" s="1">
+        <v>130079210</v>
+      </c>
+      <c r="H51" s="1">
+        <v>80981143</v>
+      </c>
+      <c r="I51" s="18">
+        <f t="shared" si="7"/>
+        <v>62.255254317734554</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="14">
+        <v>1979</v>
+      </c>
+      <c r="C52" s="1">
+        <v>262436227</v>
+      </c>
+      <c r="D52" s="1">
+        <v>163585914</v>
+      </c>
+      <c r="E52" s="3">
+        <f t="shared" si="6"/>
+        <v>62.333587047035245</v>
+      </c>
+      <c r="G52" s="1">
+        <v>137550949</v>
+      </c>
+      <c r="H52" s="1">
+        <v>95373867</v>
+      </c>
+      <c r="I52" s="18">
+        <f t="shared" si="7"/>
+        <v>69.337120313143018</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="14">
+        <v>1989</v>
+      </c>
+      <c r="C53" s="1">
+        <v>286731</v>
+      </c>
+      <c r="D53" s="1">
+        <v>188814</v>
+      </c>
+      <c r="E53" s="3">
+        <f t="shared" si="6"/>
+        <v>65.850570744007456</v>
+      </c>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1">
+        <v>147400</v>
+      </c>
+      <c r="H53" s="1">
+        <v>108425</v>
+      </c>
+      <c r="I53" s="18">
+        <f t="shared" si="7"/>
+        <v>73.558344640434186</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B56" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B57" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B60" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B62" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B64" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B65" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B66" t="s">
+        <v>102</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="G40:I40"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6706,16 +7282,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
     <mergeCell ref="S3:T3"/>
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="Q3:R3"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="M3:N3"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
